--- a/artfynd/A 46306-2025 artfynd.xlsx
+++ b/artfynd/A 46306-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129351432</v>
       </c>
       <c r="B2" t="n">
-        <v>90571</v>
+        <v>90572</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3651,57 +3651,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129364476</v>
+        <v>129367642</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>419720</v>
+        <v>419675</v>
       </c>
       <c r="R30" t="n">
-        <v>6787656</v>
+        <v>6787516</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3739,26 +3730,25 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129367642</v>
+        <v>129367643</v>
       </c>
       <c r="B31" t="n">
         <v>79041</v>
@@ -3793,10 +3783,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>419675</v>
+        <v>419668</v>
       </c>
       <c r="R31" t="n">
-        <v>6787516</v>
+        <v>6787515</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3855,7 +3845,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129367643</v>
+        <v>129357064</v>
       </c>
       <c r="B32" t="n">
         <v>79041</v>
@@ -3886,17 +3876,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>419668</v>
+        <v>419697</v>
       </c>
       <c r="R32" t="n">
-        <v>6787515</v>
+        <v>6787431</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3940,12 +3930,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4049,45 +4039,54 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129357064</v>
+        <v>129364476</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>419697</v>
+        <v>419720</v>
       </c>
       <c r="R34" t="n">
-        <v>6787431</v>
+        <v>6787656</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4128,28 +4127,29 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129357051</v>
+        <v>129364461</v>
       </c>
       <c r="B35" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4157,21 +4157,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4181,10 +4181,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>419703</v>
+        <v>419639</v>
       </c>
       <c r="R35" t="n">
-        <v>6787692</v>
+        <v>6787642</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4231,22 +4231,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129367618</v>
+        <v>129357051</v>
       </c>
       <c r="B36" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4254,37 +4254,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>419635</v>
+        <v>419703</v>
       </c>
       <c r="R36" t="n">
-        <v>6787658</v>
+        <v>6787692</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4328,12 +4328,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4437,10 +4437,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129364461</v>
+        <v>129367618</v>
       </c>
       <c r="B38" t="n">
-        <v>79660</v>
+        <v>78799</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4448,37 +4448,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>419639</v>
+        <v>419635</v>
       </c>
       <c r="R38" t="n">
-        <v>6787642</v>
+        <v>6787658</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4522,12 +4522,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4728,48 +4728,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129367604</v>
+        <v>129364500</v>
       </c>
       <c r="B41" t="n">
-        <v>79631</v>
+        <v>92821</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>419620</v>
+        <v>419672</v>
       </c>
       <c r="R41" t="n">
-        <v>6787769</v>
+        <v>6787747</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4813,60 +4813,60 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129364500</v>
+        <v>129367604</v>
       </c>
       <c r="B42" t="n">
-        <v>92836</v>
+        <v>79631</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>419672</v>
+        <v>419620</v>
       </c>
       <c r="R42" t="n">
-        <v>6787747</v>
+        <v>6787769</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4910,22 +4910,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129357047</v>
+        <v>129367602</v>
       </c>
       <c r="B43" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4933,37 +4933,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>419732</v>
+        <v>419592</v>
       </c>
       <c r="R43" t="n">
-        <v>6787619</v>
+        <v>6787771</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5007,22 +5007,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129357083</v>
+        <v>129364462</v>
       </c>
       <c r="B44" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5030,21 +5030,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>419799</v>
+        <v>419648</v>
       </c>
       <c r="R44" t="n">
-        <v>6787352</v>
+        <v>6787500</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5104,19 +5104,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129357122</v>
+        <v>129367649</v>
       </c>
       <c r="B45" t="n">
         <v>79041</v>
@@ -5147,17 +5147,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>419905</v>
+        <v>419830</v>
       </c>
       <c r="R45" t="n">
-        <v>6787672</v>
+        <v>6787264</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5195,26 +5195,25 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129357086</v>
+        <v>129357047</v>
       </c>
       <c r="B46" t="n">
         <v>79041</v>
@@ -5249,10 +5248,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>419825</v>
+        <v>419732</v>
       </c>
       <c r="R46" t="n">
-        <v>6787284</v>
+        <v>6787619</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5311,10 +5310,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129364462</v>
+        <v>129367650</v>
       </c>
       <c r="B47" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5322,37 +5321,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>419648</v>
+        <v>419833</v>
       </c>
       <c r="R47" t="n">
-        <v>6787500</v>
+        <v>6787235</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5396,19 +5395,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129367630</v>
+        <v>129367624</v>
       </c>
       <c r="B48" t="n">
         <v>79041</v>
@@ -5443,10 +5442,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>419783</v>
+        <v>419802</v>
       </c>
       <c r="R48" t="n">
-        <v>6787407</v>
+        <v>6787354</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5505,7 +5504,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129367649</v>
+        <v>129357122</v>
       </c>
       <c r="B49" t="n">
         <v>79041</v>
@@ -5536,17 +5535,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>419830</v>
+        <v>419905</v>
       </c>
       <c r="R49" t="n">
-        <v>6787264</v>
+        <v>6787672</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5584,25 +5583,26 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129367650</v>
+        <v>129357086</v>
       </c>
       <c r="B50" t="n">
         <v>79041</v>
@@ -5633,17 +5633,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>419833</v>
+        <v>419825</v>
       </c>
       <c r="R50" t="n">
-        <v>6787235</v>
+        <v>6787284</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5687,22 +5687,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129367602</v>
+        <v>129357083</v>
       </c>
       <c r="B51" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5710,37 +5710,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>419592</v>
+        <v>419799</v>
       </c>
       <c r="R51" t="n">
-        <v>6787771</v>
+        <v>6787352</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5784,19 +5784,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129367624</v>
+        <v>129367630</v>
       </c>
       <c r="B52" t="n">
         <v>79041</v>
@@ -5831,10 +5831,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>419802</v>
+        <v>419783</v>
       </c>
       <c r="R52" t="n">
-        <v>6787354</v>
+        <v>6787407</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5990,10 +5990,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129357089</v>
+        <v>129367603</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6001,37 +6001,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>419843</v>
+        <v>419817</v>
       </c>
       <c r="R54" t="n">
-        <v>6787218</v>
+        <v>6787314</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6075,19 +6075,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129357077</v>
+        <v>129367635</v>
       </c>
       <c r="B55" t="n">
         <v>79041</v>
@@ -6118,17 +6118,17 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>419815</v>
+        <v>419731</v>
       </c>
       <c r="R55" t="n">
-        <v>6787331</v>
+        <v>6787436</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6172,12 +6172,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6281,7 +6281,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129367635</v>
+        <v>129367629</v>
       </c>
       <c r="B57" t="n">
         <v>79041</v>
@@ -6316,10 +6316,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>419731</v>
+        <v>419786</v>
       </c>
       <c r="R57" t="n">
-        <v>6787436</v>
+        <v>6787405</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6378,7 +6378,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129367629</v>
+        <v>129357077</v>
       </c>
       <c r="B58" t="n">
         <v>79041</v>
@@ -6409,17 +6409,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>419786</v>
+        <v>419815</v>
       </c>
       <c r="R58" t="n">
-        <v>6787405</v>
+        <v>6787331</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6463,22 +6463,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129367603</v>
+        <v>129357089</v>
       </c>
       <c r="B59" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6486,37 +6486,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>419817</v>
+        <v>419843</v>
       </c>
       <c r="R59" t="n">
-        <v>6787314</v>
+        <v>6787218</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6560,60 +6560,69 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129367628</v>
+        <v>129357042</v>
       </c>
       <c r="B60" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>419795</v>
+        <v>419822</v>
       </c>
       <c r="R60" t="n">
-        <v>6787387</v>
+        <v>6787322</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6651,25 +6660,26 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129364485</v>
+        <v>129357058</v>
       </c>
       <c r="B61" t="n">
         <v>79041</v>
@@ -6704,10 +6714,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>419678</v>
+        <v>419892</v>
       </c>
       <c r="R61" t="n">
-        <v>6787476</v>
+        <v>6787687</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6754,19 +6764,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129357065</v>
+        <v>129357053</v>
       </c>
       <c r="B62" t="n">
         <v>79041</v>
@@ -6801,10 +6811,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>419776</v>
+        <v>419835</v>
       </c>
       <c r="R62" t="n">
-        <v>6787371</v>
+        <v>6787789</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6863,57 +6873,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129357042</v>
+        <v>129367628</v>
       </c>
       <c r="B63" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>419822</v>
+        <v>419795</v>
       </c>
       <c r="R63" t="n">
-        <v>6787322</v>
+        <v>6787387</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6951,26 +6952,25 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129357058</v>
+        <v>129357069</v>
       </c>
       <c r="B64" t="n">
         <v>79041</v>
@@ -7005,10 +7005,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>419892</v>
+        <v>419782</v>
       </c>
       <c r="R64" t="n">
-        <v>6787687</v>
+        <v>6787403</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7067,7 +7067,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129357053</v>
+        <v>129357065</v>
       </c>
       <c r="B65" t="n">
         <v>79041</v>
@@ -7102,10 +7102,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>419835</v>
+        <v>419776</v>
       </c>
       <c r="R65" t="n">
-        <v>6787789</v>
+        <v>6787371</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7164,7 +7164,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129357069</v>
+        <v>129364485</v>
       </c>
       <c r="B66" t="n">
         <v>79041</v>
@@ -7199,10 +7199,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>419782</v>
+        <v>419678</v>
       </c>
       <c r="R66" t="n">
-        <v>6787403</v>
+        <v>6787476</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7249,12 +7249,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7358,7 +7358,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129357046</v>
+        <v>129357081</v>
       </c>
       <c r="B68" t="n">
         <v>79041</v>
@@ -7393,10 +7393,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>419742</v>
+        <v>419810</v>
       </c>
       <c r="R68" t="n">
-        <v>6787432</v>
+        <v>6787369</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7455,7 +7455,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129357081</v>
+        <v>129357046</v>
       </c>
       <c r="B69" t="n">
         <v>79041</v>
@@ -7490,10 +7490,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>419810</v>
+        <v>419742</v>
       </c>
       <c r="R69" t="n">
-        <v>6787369</v>
+        <v>6787432</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7649,10 +7649,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129357060</v>
+        <v>129367601</v>
       </c>
       <c r="B71" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7660,37 +7660,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>419924</v>
+        <v>419818</v>
       </c>
       <c r="R71" t="n">
-        <v>6787672</v>
+        <v>6787250</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7734,19 +7734,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129357052</v>
+        <v>129357060</v>
       </c>
       <c r="B72" t="n">
         <v>79041</v>
@@ -7781,10 +7781,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>419810</v>
+        <v>419924</v>
       </c>
       <c r="R72" t="n">
-        <v>6787834</v>
+        <v>6787672</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7843,10 +7843,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129367601</v>
+        <v>129357052</v>
       </c>
       <c r="B73" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7854,37 +7854,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>419818</v>
+        <v>419810</v>
       </c>
       <c r="R73" t="n">
-        <v>6787250</v>
+        <v>6787834</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7928,12 +7928,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8037,10 +8037,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129367641</v>
+        <v>129367599</v>
       </c>
       <c r="B75" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8048,21 +8048,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8072,10 +8072,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>419590</v>
+        <v>419693</v>
       </c>
       <c r="R75" t="n">
-        <v>6787769</v>
+        <v>6787442</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8134,10 +8134,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129367599</v>
+        <v>129367641</v>
       </c>
       <c r="B76" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8145,21 +8145,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8169,10 +8169,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>419693</v>
+        <v>419590</v>
       </c>
       <c r="R76" t="n">
-        <v>6787442</v>
+        <v>6787769</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8231,10 +8231,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129367617</v>
+        <v>129367639</v>
       </c>
       <c r="B77" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8242,21 +8242,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>419617</v>
+        <v>419672</v>
       </c>
       <c r="R77" t="n">
-        <v>6787770</v>
+        <v>6787734</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8328,7 +8328,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129367639</v>
+        <v>129367626</v>
       </c>
       <c r="B78" t="n">
         <v>79041</v>
@@ -8363,10 +8363,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>419672</v>
+        <v>419797</v>
       </c>
       <c r="R78" t="n">
-        <v>6787734</v>
+        <v>6787364</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8425,10 +8425,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129367626</v>
+        <v>129367617</v>
       </c>
       <c r="B79" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8436,21 +8436,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8460,10 +8460,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>419797</v>
+        <v>419617</v>
       </c>
       <c r="R79" t="n">
-        <v>6787364</v>
+        <v>6787770</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8522,7 +8522,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129357087</v>
+        <v>129357045</v>
       </c>
       <c r="B80" t="n">
         <v>79041</v>
@@ -8557,10 +8557,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>419820</v>
+        <v>419746</v>
       </c>
       <c r="R80" t="n">
-        <v>6787283</v>
+        <v>6787424</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8619,7 +8619,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129357045</v>
+        <v>129357066</v>
       </c>
       <c r="B81" t="n">
         <v>79041</v>
@@ -8654,10 +8654,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>419746</v>
+        <v>419785</v>
       </c>
       <c r="R81" t="n">
-        <v>6787424</v>
+        <v>6787364</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8716,7 +8716,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129357066</v>
+        <v>129357087</v>
       </c>
       <c r="B82" t="n">
         <v>79041</v>
@@ -8751,10 +8751,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>419785</v>
+        <v>419820</v>
       </c>
       <c r="R82" t="n">
-        <v>6787364</v>
+        <v>6787283</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8813,10 +8813,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129357050</v>
+        <v>129357039</v>
       </c>
       <c r="B83" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8824,34 +8824,46 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>419683</v>
+        <v>419783</v>
       </c>
       <c r="R83" t="n">
-        <v>6787695</v>
+        <v>6787400</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8910,10 +8922,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129357088</v>
+        <v>129357036</v>
       </c>
       <c r="B84" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8921,21 +8933,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8945,10 +8957,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>419827</v>
+        <v>419822</v>
       </c>
       <c r="R84" t="n">
-        <v>6787267</v>
+        <v>6787802</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9007,10 +9019,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129357036</v>
+        <v>129367627</v>
       </c>
       <c r="B85" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9018,37 +9030,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>419822</v>
+        <v>419795</v>
       </c>
       <c r="R85" t="n">
-        <v>6787802</v>
+        <v>6787371</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9092,22 +9104,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129357039</v>
+        <v>129357088</v>
       </c>
       <c r="B86" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9115,46 +9127,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>419783</v>
+        <v>419827</v>
       </c>
       <c r="R86" t="n">
-        <v>6787400</v>
+        <v>6787267</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9213,7 +9213,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129367606</v>
+        <v>129367605</v>
       </c>
       <c r="B87" t="n">
         <v>79631</v>
@@ -9248,10 +9248,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>419820</v>
+        <v>419682</v>
       </c>
       <c r="R87" t="n">
-        <v>6787294</v>
+        <v>6787451</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9310,10 +9310,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129367605</v>
+        <v>129357050</v>
       </c>
       <c r="B88" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9321,37 +9321,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>419682</v>
+        <v>419683</v>
       </c>
       <c r="R88" t="n">
-        <v>6787451</v>
+        <v>6787695</v>
       </c>
       <c r="S88" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9395,19 +9395,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129367600</v>
+        <v>129367598</v>
       </c>
       <c r="B89" t="n">
         <v>79660</v>
@@ -9442,10 +9442,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>419801</v>
+        <v>419671</v>
       </c>
       <c r="R89" t="n">
-        <v>6787284</v>
+        <v>6787459</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9504,7 +9504,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129367598</v>
+        <v>129367600</v>
       </c>
       <c r="B90" t="n">
         <v>79660</v>
@@ -9539,10 +9539,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>419671</v>
+        <v>419801</v>
       </c>
       <c r="R90" t="n">
-        <v>6787459</v>
+        <v>6787284</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -9601,10 +9601,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129367645</v>
+        <v>129367606</v>
       </c>
       <c r="B91" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9612,21 +9612,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9636,10 +9636,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>419775</v>
+        <v>419820</v>
       </c>
       <c r="R91" t="n">
-        <v>6787376</v>
+        <v>6787294</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -9698,7 +9698,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129367627</v>
+        <v>129367645</v>
       </c>
       <c r="B92" t="n">
         <v>79041</v>
@@ -9733,10 +9733,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>419795</v>
+        <v>419775</v>
       </c>
       <c r="R92" t="n">
-        <v>6787371</v>
+        <v>6787376</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -9892,7 +9892,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129367647</v>
+        <v>129357073</v>
       </c>
       <c r="B94" t="n">
         <v>79041</v>
@@ -9923,17 +9923,17 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>419817</v>
+        <v>419806</v>
       </c>
       <c r="R94" t="n">
-        <v>6787255</v>
+        <v>6787347</v>
       </c>
       <c r="S94" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9977,19 +9977,19 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129357073</v>
+        <v>129357079</v>
       </c>
       <c r="B95" t="n">
         <v>79041</v>
@@ -10024,10 +10024,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>419806</v>
+        <v>419814</v>
       </c>
       <c r="R95" t="n">
-        <v>6787347</v>
+        <v>6787354</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10086,10 +10086,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129357079</v>
+        <v>129364482</v>
       </c>
       <c r="B96" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10097,21 +10097,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10121,10 +10121,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>419814</v>
+        <v>419803</v>
       </c>
       <c r="R96" t="n">
-        <v>6787354</v>
+        <v>6787361</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10171,19 +10171,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129357056</v>
+        <v>129367647</v>
       </c>
       <c r="B97" t="n">
         <v>79041</v>
@@ -10214,17 +10214,17 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>419863</v>
+        <v>419817</v>
       </c>
       <c r="R97" t="n">
-        <v>6787786</v>
+        <v>6787255</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10268,22 +10268,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129364482</v>
+        <v>129357056</v>
       </c>
       <c r="B98" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10291,21 +10291,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10315,10 +10315,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>419803</v>
+        <v>419863</v>
       </c>
       <c r="R98" t="n">
-        <v>6787361</v>
+        <v>6787786</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10365,12 +10365,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -10574,7 +10574,7 @@
         <v>129364498</v>
       </c>
       <c r="B101" t="n">
-        <v>92836</v>
+        <v>92821</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10668,10 +10668,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129357044</v>
+        <v>129367659</v>
       </c>
       <c r="B102" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10679,37 +10679,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>419817</v>
+        <v>419692</v>
       </c>
       <c r="R102" t="n">
-        <v>6787353</v>
+        <v>6787475</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10753,22 +10753,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129367636</v>
+        <v>129357044</v>
       </c>
       <c r="B103" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10776,37 +10776,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>419729</v>
+        <v>419817</v>
       </c>
       <c r="R103" t="n">
-        <v>6787620</v>
+        <v>6787353</v>
       </c>
       <c r="S103" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10850,19 +10850,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129367659</v>
+        <v>129367636</v>
       </c>
       <c r="B104" t="n">
         <v>79041</v>
@@ -10897,10 +10897,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>419692</v>
+        <v>419729</v>
       </c>
       <c r="R104" t="n">
-        <v>6787475</v>
+        <v>6787620</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -10959,7 +10959,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129357061</v>
+        <v>129364488</v>
       </c>
       <c r="B105" t="n">
         <v>79041</v>
@@ -10994,10 +10994,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>419929</v>
+        <v>419829</v>
       </c>
       <c r="R105" t="n">
-        <v>6787653</v>
+        <v>6787260</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11044,12 +11044,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -11153,7 +11153,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129367644</v>
+        <v>129357061</v>
       </c>
       <c r="B107" t="n">
         <v>79041</v>
@@ -11184,17 +11184,17 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>419667</v>
+        <v>419929</v>
       </c>
       <c r="R107" t="n">
-        <v>6787466</v>
+        <v>6787653</v>
       </c>
       <c r="S107" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11238,19 +11238,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129364488</v>
+        <v>129367644</v>
       </c>
       <c r="B108" t="n">
         <v>79041</v>
@@ -11281,17 +11281,17 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>419829</v>
+        <v>419667</v>
       </c>
       <c r="R108" t="n">
-        <v>6787260</v>
+        <v>6787466</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11335,57 +11335,66 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129357085</v>
+        <v>129364478</v>
       </c>
       <c r="B109" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>419821</v>
+        <v>419796</v>
       </c>
       <c r="R109" t="n">
-        <v>6787310</v>
+        <v>6787321</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11426,25 +11435,26 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129357063</v>
+        <v>129367638</v>
       </c>
       <c r="B110" t="n">
         <v>79041</v>
@@ -11475,17 +11485,17 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>419686</v>
+        <v>419681</v>
       </c>
       <c r="R110" t="n">
-        <v>6787449</v>
+        <v>6787728</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11529,19 +11539,19 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129357072</v>
+        <v>129357054</v>
       </c>
       <c r="B111" t="n">
         <v>79041</v>
@@ -11576,10 +11586,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>419808</v>
+        <v>419849</v>
       </c>
       <c r="R111" t="n">
-        <v>6787365</v>
+        <v>6787800</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11735,7 +11745,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129357054</v>
+        <v>129357085</v>
       </c>
       <c r="B113" t="n">
         <v>79041</v>
@@ -11770,10 +11780,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>419849</v>
+        <v>419821</v>
       </c>
       <c r="R113" t="n">
-        <v>6787800</v>
+        <v>6787310</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11832,57 +11842,48 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129364478</v>
+        <v>129367637</v>
       </c>
       <c r="B114" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>419796</v>
+        <v>419724</v>
       </c>
       <c r="R114" t="n">
-        <v>6787321</v>
+        <v>6787653</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11920,26 +11921,25 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129367637</v>
+        <v>129357072</v>
       </c>
       <c r="B115" t="n">
         <v>79041</v>
@@ -11970,17 +11970,17 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>419724</v>
+        <v>419808</v>
       </c>
       <c r="R115" t="n">
-        <v>6787653</v>
+        <v>6787365</v>
       </c>
       <c r="S115" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12024,19 +12024,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129367638</v>
+        <v>129357063</v>
       </c>
       <c r="B116" t="n">
         <v>79041</v>
@@ -12067,17 +12067,17 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>419681</v>
+        <v>419686</v>
       </c>
       <c r="R116" t="n">
-        <v>6787728</v>
+        <v>6787449</v>
       </c>
       <c r="S116" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12121,22 +12121,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129357062</v>
+        <v>129364466</v>
       </c>
       <c r="B117" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12144,21 +12144,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12168,10 +12168,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>419682</v>
+        <v>419796</v>
       </c>
       <c r="R117" t="n">
-        <v>6787459</v>
+        <v>6787321</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12218,22 +12218,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129367633</v>
+        <v>129364468</v>
       </c>
       <c r="B118" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12241,37 +12241,37 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>419775</v>
+        <v>419802</v>
       </c>
       <c r="R118" t="n">
-        <v>6787415</v>
+        <v>6787354</v>
       </c>
       <c r="S118" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12315,22 +12315,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129364468</v>
+        <v>129367633</v>
       </c>
       <c r="B119" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12338,37 +12338,37 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>419802</v>
+        <v>419775</v>
       </c>
       <c r="R119" t="n">
-        <v>6787354</v>
+        <v>6787415</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12412,22 +12412,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129364466</v>
+        <v>129357062</v>
       </c>
       <c r="B120" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12435,21 +12435,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12459,10 +12459,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>419796</v>
+        <v>419682</v>
       </c>
       <c r="R120" t="n">
-        <v>6787321</v>
+        <v>6787459</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12509,19 +12509,19 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129357068</v>
+        <v>129357049</v>
       </c>
       <c r="B121" t="n">
         <v>79041</v>
@@ -12556,10 +12556,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>419749</v>
+        <v>419707</v>
       </c>
       <c r="R121" t="n">
-        <v>6787397</v>
+        <v>6787641</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12618,7 +12618,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129357049</v>
+        <v>129364487</v>
       </c>
       <c r="B122" t="n">
         <v>79041</v>
@@ -12653,10 +12653,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>419707</v>
+        <v>419795</v>
       </c>
       <c r="R122" t="n">
-        <v>6787641</v>
+        <v>6787306</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12703,22 +12703,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129357037</v>
+        <v>129367640</v>
       </c>
       <c r="B123" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12726,37 +12726,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>419822</v>
+        <v>419596</v>
       </c>
       <c r="R123" t="n">
-        <v>6787799</v>
+        <v>6787765</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -12800,12 +12800,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
@@ -12909,7 +12909,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129364487</v>
+        <v>129357068</v>
       </c>
       <c r="B125" t="n">
         <v>79041</v>
@@ -12944,10 +12944,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>419795</v>
+        <v>419749</v>
       </c>
       <c r="R125" t="n">
-        <v>6787306</v>
+        <v>6787397</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12994,22 +12994,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129367640</v>
+        <v>129357037</v>
       </c>
       <c r="B126" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13017,37 +13017,37 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>419596</v>
+        <v>419822</v>
       </c>
       <c r="R126" t="n">
-        <v>6787765</v>
+        <v>6787799</v>
       </c>
       <c r="S126" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13091,19 +13091,19 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129357074</v>
+        <v>129367625</v>
       </c>
       <c r="B127" t="n">
         <v>79041</v>
@@ -13134,17 +13134,17 @@
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>419796</v>
+        <v>419800</v>
       </c>
       <c r="R127" t="n">
-        <v>6787322</v>
+        <v>6787361</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13188,19 +13188,19 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129357055</v>
+        <v>129357074</v>
       </c>
       <c r="B128" t="n">
         <v>79041</v>
@@ -13235,10 +13235,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>419856</v>
+        <v>419796</v>
       </c>
       <c r="R128" t="n">
-        <v>6787798</v>
+        <v>6787322</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13297,7 +13297,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129367625</v>
+        <v>129357055</v>
       </c>
       <c r="B129" t="n">
         <v>79041</v>
@@ -13328,17 +13328,17 @@
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>419800</v>
+        <v>419856</v>
       </c>
       <c r="R129" t="n">
-        <v>6787361</v>
+        <v>6787798</v>
       </c>
       <c r="S129" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13382,12 +13382,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>

--- a/artfynd/A 46306-2025 artfynd.xlsx
+++ b/artfynd/A 46306-2025 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129351428</v>
+        <v>129351453</v>
       </c>
       <c r="B4" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,7 +927,7 @@
         <v>419742</v>
       </c>
       <c r="R4" t="n">
-        <v>6787389</v>
+        <v>6787381</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129351453</v>
+        <v>129351428</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1034,7 +1034,7 @@
         <v>419742</v>
       </c>
       <c r="R5" t="n">
-        <v>6787381</v>
+        <v>6787389</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129351441</v>
+        <v>129351479</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>78707</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>419804</v>
+        <v>419670</v>
       </c>
       <c r="R15" t="n">
-        <v>6787364</v>
+        <v>6787628</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129351436</v>
+        <v>129351441</v>
       </c>
       <c r="B16" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>419772</v>
+        <v>419804</v>
       </c>
       <c r="R16" t="n">
-        <v>6787332</v>
+        <v>6787364</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129351479</v>
+        <v>129351436</v>
       </c>
       <c r="B17" t="n">
-        <v>78707</v>
+        <v>78798</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>419670</v>
+        <v>419772</v>
       </c>
       <c r="R17" t="n">
-        <v>6787628</v>
+        <v>6787332</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129351480</v>
+        <v>129351431</v>
       </c>
       <c r="B21" t="n">
-        <v>78707</v>
+        <v>79631</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>419635</v>
+        <v>419608</v>
       </c>
       <c r="R21" t="n">
-        <v>6787627</v>
+        <v>6787699</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129351431</v>
+        <v>129351480</v>
       </c>
       <c r="B22" t="n">
-        <v>79631</v>
+        <v>78707</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,21 +2826,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>419608</v>
+        <v>419635</v>
       </c>
       <c r="R22" t="n">
-        <v>6787699</v>
+        <v>6787627</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3243,10 +3243,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129351442</v>
+        <v>129351427</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3254,21 +3254,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>419761</v>
+        <v>419606</v>
       </c>
       <c r="R26" t="n">
-        <v>6787419</v>
+        <v>6787701</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129351427</v>
+        <v>129351442</v>
       </c>
       <c r="B27" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3361,21 +3361,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>419606</v>
+        <v>419761</v>
       </c>
       <c r="R27" t="n">
-        <v>6787701</v>
+        <v>6787419</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3748,7 +3748,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129367643</v>
+        <v>129357064</v>
       </c>
       <c r="B31" t="n">
         <v>79041</v>
@@ -3779,17 +3779,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>419668</v>
+        <v>419697</v>
       </c>
       <c r="R31" t="n">
-        <v>6787515</v>
+        <v>6787431</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3833,19 +3833,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129357064</v>
+        <v>129367643</v>
       </c>
       <c r="B32" t="n">
         <v>79041</v>
@@ -3876,17 +3876,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>419697</v>
+        <v>419668</v>
       </c>
       <c r="R32" t="n">
-        <v>6787431</v>
+        <v>6787515</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3930,12 +3930,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4146,10 +4146,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129364461</v>
+        <v>129357051</v>
       </c>
       <c r="B35" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4157,21 +4157,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4181,10 +4181,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>419639</v>
+        <v>419703</v>
       </c>
       <c r="R35" t="n">
-        <v>6787642</v>
+        <v>6787692</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4231,22 +4231,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129357051</v>
+        <v>129364461</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4254,21 +4254,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4278,10 +4278,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>419703</v>
+        <v>419639</v>
       </c>
       <c r="R36" t="n">
-        <v>6787692</v>
+        <v>6787642</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4328,12 +4328,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4534,32 +4534,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129357067</v>
+        <v>129364500</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>92822</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4569,10 +4569,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>419791</v>
+        <v>419672</v>
       </c>
       <c r="R39" t="n">
-        <v>6787358</v>
+        <v>6787747</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4619,19 +4619,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129357075</v>
+        <v>129357067</v>
       </c>
       <c r="B40" t="n">
         <v>79041</v>
@@ -4666,10 +4666,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>419809</v>
+        <v>419791</v>
       </c>
       <c r="R40" t="n">
-        <v>6787307</v>
+        <v>6787358</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4728,32 +4728,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129364500</v>
+        <v>129357075</v>
       </c>
       <c r="B41" t="n">
-        <v>92821</v>
+        <v>79041</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4763,10 +4763,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>419672</v>
+        <v>419809</v>
       </c>
       <c r="R41" t="n">
-        <v>6787747</v>
+        <v>6787307</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4813,12 +4813,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4922,10 +4922,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129367602</v>
+        <v>129367649</v>
       </c>
       <c r="B43" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4933,21 +4933,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>419592</v>
+        <v>419830</v>
       </c>
       <c r="R43" t="n">
-        <v>6787771</v>
+        <v>6787264</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5019,10 +5019,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129364462</v>
+        <v>129357047</v>
       </c>
       <c r="B44" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5030,21 +5030,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>419648</v>
+        <v>419732</v>
       </c>
       <c r="R44" t="n">
-        <v>6787500</v>
+        <v>6787619</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5104,19 +5104,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129367649</v>
+        <v>129367624</v>
       </c>
       <c r="B45" t="n">
         <v>79041</v>
@@ -5151,10 +5151,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>419830</v>
+        <v>419802</v>
       </c>
       <c r="R45" t="n">
-        <v>6787264</v>
+        <v>6787354</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5213,7 +5213,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129357047</v>
+        <v>129357086</v>
       </c>
       <c r="B46" t="n">
         <v>79041</v>
@@ -5248,10 +5248,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>419732</v>
+        <v>419825</v>
       </c>
       <c r="R46" t="n">
-        <v>6787619</v>
+        <v>6787284</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5310,10 +5310,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129367650</v>
+        <v>129367602</v>
       </c>
       <c r="B47" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5321,21 +5321,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>419833</v>
+        <v>419592</v>
       </c>
       <c r="R47" t="n">
-        <v>6787235</v>
+        <v>6787771</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5407,7 +5407,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129367624</v>
+        <v>129367650</v>
       </c>
       <c r="B48" t="n">
         <v>79041</v>
@@ -5442,10 +5442,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>419802</v>
+        <v>419833</v>
       </c>
       <c r="R48" t="n">
-        <v>6787354</v>
+        <v>6787235</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5504,10 +5504,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129357122</v>
+        <v>129364462</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5515,21 +5515,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5539,10 +5539,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>419905</v>
+        <v>419648</v>
       </c>
       <c r="R49" t="n">
-        <v>6787672</v>
+        <v>6787500</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5583,26 +5583,25 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129357086</v>
+        <v>129357122</v>
       </c>
       <c r="B50" t="n">
         <v>79041</v>
@@ -5637,10 +5636,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>419825</v>
+        <v>419905</v>
       </c>
       <c r="R50" t="n">
-        <v>6787284</v>
+        <v>6787672</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5681,6 +5680,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5893,10 +5893,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129364464</v>
+        <v>129357078</v>
       </c>
       <c r="B53" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5904,21 +5904,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>419679</v>
+        <v>419813</v>
       </c>
       <c r="R53" t="n">
-        <v>6787475</v>
+        <v>6787347</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5978,22 +5978,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129367603</v>
+        <v>129367635</v>
       </c>
       <c r="B54" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6001,21 +6001,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>419817</v>
+        <v>419731</v>
       </c>
       <c r="R54" t="n">
-        <v>6787314</v>
+        <v>6787436</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6087,10 +6087,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129367635</v>
+        <v>129364464</v>
       </c>
       <c r="B55" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6098,37 +6098,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>419731</v>
+        <v>419679</v>
       </c>
       <c r="R55" t="n">
-        <v>6787436</v>
+        <v>6787475</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6172,19 +6172,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129357078</v>
+        <v>129367629</v>
       </c>
       <c r="B56" t="n">
         <v>79041</v>
@@ -6215,17 +6215,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>419813</v>
+        <v>419786</v>
       </c>
       <c r="R56" t="n">
-        <v>6787347</v>
+        <v>6787405</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6269,19 +6269,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129367629</v>
+        <v>129357077</v>
       </c>
       <c r="B57" t="n">
         <v>79041</v>
@@ -6312,17 +6312,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>419786</v>
+        <v>419815</v>
       </c>
       <c r="R57" t="n">
-        <v>6787405</v>
+        <v>6787331</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6366,19 +6366,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129357077</v>
+        <v>129357089</v>
       </c>
       <c r="B58" t="n">
         <v>79041</v>
@@ -6413,10 +6413,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>419815</v>
+        <v>419843</v>
       </c>
       <c r="R58" t="n">
-        <v>6787331</v>
+        <v>6787218</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6475,10 +6475,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129357089</v>
+        <v>129367603</v>
       </c>
       <c r="B59" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6486,37 +6486,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>419843</v>
+        <v>419817</v>
       </c>
       <c r="R59" t="n">
-        <v>6787218</v>
+        <v>6787314</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6560,66 +6560,57 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129357042</v>
+        <v>129357058</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>419822</v>
+        <v>419892</v>
       </c>
       <c r="R60" t="n">
-        <v>6787322</v>
+        <v>6787687</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6660,7 +6651,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6679,7 +6669,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129357058</v>
+        <v>129357069</v>
       </c>
       <c r="B61" t="n">
         <v>79041</v>
@@ -6714,10 +6704,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>419892</v>
+        <v>419782</v>
       </c>
       <c r="R61" t="n">
-        <v>6787687</v>
+        <v>6787403</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6776,7 +6766,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129357053</v>
+        <v>129364485</v>
       </c>
       <c r="B62" t="n">
         <v>79041</v>
@@ -6811,10 +6801,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>419835</v>
+        <v>419678</v>
       </c>
       <c r="R62" t="n">
-        <v>6787789</v>
+        <v>6787476</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6861,19 +6851,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129367628</v>
+        <v>129357053</v>
       </c>
       <c r="B63" t="n">
         <v>79041</v>
@@ -6904,17 +6894,17 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>419795</v>
+        <v>419835</v>
       </c>
       <c r="R63" t="n">
-        <v>6787387</v>
+        <v>6787789</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6958,19 +6948,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129357069</v>
+        <v>129367628</v>
       </c>
       <c r="B64" t="n">
         <v>79041</v>
@@ -7001,17 +6991,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>419782</v>
+        <v>419795</v>
       </c>
       <c r="R64" t="n">
-        <v>6787403</v>
+        <v>6787387</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7055,12 +7045,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7164,45 +7154,54 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129364485</v>
+        <v>129357042</v>
       </c>
       <c r="B66" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>419678</v>
+        <v>419822</v>
       </c>
       <c r="R66" t="n">
-        <v>6787476</v>
+        <v>6787322</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7243,18 +7242,19 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7358,7 +7358,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129357081</v>
+        <v>129357046</v>
       </c>
       <c r="B68" t="n">
         <v>79041</v>
@@ -7393,10 +7393,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>419810</v>
+        <v>419742</v>
       </c>
       <c r="R68" t="n">
-        <v>6787369</v>
+        <v>6787432</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7455,7 +7455,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129357046</v>
+        <v>129357081</v>
       </c>
       <c r="B69" t="n">
         <v>79041</v>
@@ -7490,10 +7490,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>419742</v>
+        <v>419810</v>
       </c>
       <c r="R69" t="n">
-        <v>6787432</v>
+        <v>6787369</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7649,10 +7649,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129367601</v>
+        <v>129357060</v>
       </c>
       <c r="B71" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7660,37 +7660,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>419818</v>
+        <v>419924</v>
       </c>
       <c r="R71" t="n">
-        <v>6787250</v>
+        <v>6787672</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7734,19 +7734,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129357060</v>
+        <v>129357052</v>
       </c>
       <c r="B72" t="n">
         <v>79041</v>
@@ -7781,10 +7781,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>419924</v>
+        <v>419810</v>
       </c>
       <c r="R72" t="n">
-        <v>6787672</v>
+        <v>6787834</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7843,10 +7843,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129357052</v>
+        <v>129367601</v>
       </c>
       <c r="B73" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7854,37 +7854,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>419810</v>
+        <v>419818</v>
       </c>
       <c r="R73" t="n">
-        <v>6787834</v>
+        <v>6787250</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7928,22 +7928,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129364502</v>
+        <v>129367639</v>
       </c>
       <c r="B74" t="n">
-        <v>78049</v>
+        <v>79041</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7951,37 +7951,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>419821</v>
+        <v>419672</v>
       </c>
       <c r="R74" t="n">
-        <v>6787289</v>
+        <v>6787734</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8025,22 +8025,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129367599</v>
+        <v>129367626</v>
       </c>
       <c r="B75" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8048,21 +8048,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8072,10 +8072,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>419693</v>
+        <v>419797</v>
       </c>
       <c r="R75" t="n">
-        <v>6787442</v>
+        <v>6787364</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8231,10 +8231,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129367639</v>
+        <v>129367599</v>
       </c>
       <c r="B77" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8242,21 +8242,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>419672</v>
+        <v>419693</v>
       </c>
       <c r="R77" t="n">
-        <v>6787734</v>
+        <v>6787442</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8328,10 +8328,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129367626</v>
+        <v>129367617</v>
       </c>
       <c r="B78" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8339,21 +8339,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8363,10 +8363,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>419797</v>
+        <v>419617</v>
       </c>
       <c r="R78" t="n">
-        <v>6787364</v>
+        <v>6787770</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8425,10 +8425,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129367617</v>
+        <v>129364502</v>
       </c>
       <c r="B79" t="n">
-        <v>78799</v>
+        <v>78049</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8436,37 +8436,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>419617</v>
+        <v>419821</v>
       </c>
       <c r="R79" t="n">
-        <v>6787770</v>
+        <v>6787289</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8510,12 +8510,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8813,10 +8813,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129357039</v>
+        <v>129367645</v>
       </c>
       <c r="B83" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8824,49 +8824,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>419783</v>
+        <v>419775</v>
       </c>
       <c r="R83" t="n">
-        <v>6787400</v>
+        <v>6787376</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8910,12 +8898,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -9019,7 +9007,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129367627</v>
+        <v>129357050</v>
       </c>
       <c r="B85" t="n">
         <v>79041</v>
@@ -9050,17 +9038,17 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>419795</v>
+        <v>419683</v>
       </c>
       <c r="R85" t="n">
-        <v>6787371</v>
+        <v>6787695</v>
       </c>
       <c r="S85" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9104,19 +9092,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129357088</v>
+        <v>129367627</v>
       </c>
       <c r="B86" t="n">
         <v>79041</v>
@@ -9147,17 +9135,17 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>419827</v>
+        <v>419795</v>
       </c>
       <c r="R86" t="n">
-        <v>6787267</v>
+        <v>6787371</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9201,22 +9189,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129367605</v>
+        <v>129367598</v>
       </c>
       <c r="B87" t="n">
-        <v>79631</v>
+        <v>79660</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9224,21 +9212,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9248,10 +9236,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>419682</v>
+        <v>419671</v>
       </c>
       <c r="R87" t="n">
-        <v>6787451</v>
+        <v>6787459</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9310,7 +9298,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129357050</v>
+        <v>129357088</v>
       </c>
       <c r="B88" t="n">
         <v>79041</v>
@@ -9345,10 +9333,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>419683</v>
+        <v>419827</v>
       </c>
       <c r="R88" t="n">
-        <v>6787695</v>
+        <v>6787267</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9407,7 +9395,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129367598</v>
+        <v>129367600</v>
       </c>
       <c r="B89" t="n">
         <v>79660</v>
@@ -9442,10 +9430,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>419671</v>
+        <v>419801</v>
       </c>
       <c r="R89" t="n">
-        <v>6787459</v>
+        <v>6787284</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9504,10 +9492,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129367600</v>
+        <v>129367605</v>
       </c>
       <c r="B90" t="n">
-        <v>79660</v>
+        <v>79631</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9515,21 +9503,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9539,10 +9527,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>419801</v>
+        <v>419682</v>
       </c>
       <c r="R90" t="n">
-        <v>6787284</v>
+        <v>6787451</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -9698,10 +9686,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129367645</v>
+        <v>129357039</v>
       </c>
       <c r="B92" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9709,37 +9697,49 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>419775</v>
+        <v>419783</v>
       </c>
       <c r="R92" t="n">
-        <v>6787376</v>
+        <v>6787400</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9783,19 +9783,19 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129367631</v>
+        <v>129357073</v>
       </c>
       <c r="B93" t="n">
         <v>79041</v>
@@ -9826,17 +9826,17 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>419777</v>
+        <v>419806</v>
       </c>
       <c r="R93" t="n">
-        <v>6787409</v>
+        <v>6787347</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9880,19 +9880,19 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129357073</v>
+        <v>129357079</v>
       </c>
       <c r="B94" t="n">
         <v>79041</v>
@@ -9927,10 +9927,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>419806</v>
+        <v>419814</v>
       </c>
       <c r="R94" t="n">
-        <v>6787347</v>
+        <v>6787354</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9989,10 +9989,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129357079</v>
+        <v>129364482</v>
       </c>
       <c r="B95" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10000,21 +10000,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10024,10 +10024,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>419814</v>
+        <v>419803</v>
       </c>
       <c r="R95" t="n">
-        <v>6787354</v>
+        <v>6787361</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10074,19 +10074,19 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129364482</v>
+        <v>129364480</v>
       </c>
       <c r="B96" t="n">
         <v>78798</v>
@@ -10121,10 +10121,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>419803</v>
+        <v>419678</v>
       </c>
       <c r="R96" t="n">
-        <v>6787361</v>
+        <v>6787641</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10183,7 +10183,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129367647</v>
+        <v>129367631</v>
       </c>
       <c r="B97" t="n">
         <v>79041</v>
@@ -10218,10 +10218,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>419817</v>
+        <v>419777</v>
       </c>
       <c r="R97" t="n">
-        <v>6787255</v>
+        <v>6787409</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -10280,7 +10280,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129357056</v>
+        <v>129367647</v>
       </c>
       <c r="B98" t="n">
         <v>79041</v>
@@ -10311,17 +10311,17 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>419863</v>
+        <v>419817</v>
       </c>
       <c r="R98" t="n">
-        <v>6787786</v>
+        <v>6787255</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10365,22 +10365,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129364480</v>
+        <v>129357056</v>
       </c>
       <c r="B99" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10388,21 +10388,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10412,10 +10412,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>419678</v>
+        <v>419863</v>
       </c>
       <c r="R99" t="n">
-        <v>6787641</v>
+        <v>6787786</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10462,44 +10462,44 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129357076</v>
+        <v>129364498</v>
       </c>
       <c r="B100" t="n">
-        <v>79041</v>
+        <v>92822</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10509,10 +10509,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>419818</v>
+        <v>419705</v>
       </c>
       <c r="R100" t="n">
-        <v>6787293</v>
+        <v>6787663</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10559,44 +10559,44 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129364498</v>
+        <v>129357076</v>
       </c>
       <c r="B101" t="n">
-        <v>92821</v>
+        <v>79041</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10606,10 +10606,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>419705</v>
+        <v>419818</v>
       </c>
       <c r="R101" t="n">
-        <v>6787663</v>
+        <v>6787293</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10656,19 +10656,19 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129367659</v>
+        <v>129367636</v>
       </c>
       <c r="B102" t="n">
         <v>79041</v>
@@ -10703,10 +10703,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>419692</v>
+        <v>419729</v>
       </c>
       <c r="R102" t="n">
-        <v>6787475</v>
+        <v>6787620</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -10765,10 +10765,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129357044</v>
+        <v>129367659</v>
       </c>
       <c r="B103" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10776,37 +10776,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>419817</v>
+        <v>419692</v>
       </c>
       <c r="R103" t="n">
-        <v>6787353</v>
+        <v>6787475</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10850,22 +10850,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129367636</v>
+        <v>129357044</v>
       </c>
       <c r="B104" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10873,37 +10873,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>419729</v>
+        <v>419817</v>
       </c>
       <c r="R104" t="n">
-        <v>6787620</v>
+        <v>6787353</v>
       </c>
       <c r="S104" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10947,19 +10947,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129364488</v>
+        <v>129357057</v>
       </c>
       <c r="B105" t="n">
         <v>79041</v>
@@ -10994,10 +10994,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>419829</v>
+        <v>419865</v>
       </c>
       <c r="R105" t="n">
-        <v>6787260</v>
+        <v>6787760</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11044,19 +11044,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129357057</v>
+        <v>129367644</v>
       </c>
       <c r="B106" t="n">
         <v>79041</v>
@@ -11087,17 +11087,17 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>419865</v>
+        <v>419667</v>
       </c>
       <c r="R106" t="n">
-        <v>6787760</v>
+        <v>6787466</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11141,19 +11141,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129357061</v>
+        <v>129364488</v>
       </c>
       <c r="B107" t="n">
         <v>79041</v>
@@ -11188,10 +11188,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>419929</v>
+        <v>419829</v>
       </c>
       <c r="R107" t="n">
-        <v>6787653</v>
+        <v>6787260</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11238,19 +11238,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129367644</v>
+        <v>129357061</v>
       </c>
       <c r="B108" t="n">
         <v>79041</v>
@@ -11281,17 +11281,17 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>419667</v>
+        <v>419929</v>
       </c>
       <c r="R108" t="n">
-        <v>6787466</v>
+        <v>6787653</v>
       </c>
       <c r="S108" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11335,12 +11335,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -11454,7 +11454,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129367638</v>
+        <v>129357070</v>
       </c>
       <c r="B110" t="n">
         <v>79041</v>
@@ -11485,17 +11485,17 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>419681</v>
+        <v>419795</v>
       </c>
       <c r="R110" t="n">
-        <v>6787728</v>
+        <v>6787392</v>
       </c>
       <c r="S110" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11539,19 +11539,19 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129357054</v>
+        <v>129357085</v>
       </c>
       <c r="B111" t="n">
         <v>79041</v>
@@ -11586,10 +11586,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>419849</v>
+        <v>419821</v>
       </c>
       <c r="R111" t="n">
-        <v>6787800</v>
+        <v>6787310</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11648,7 +11648,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129357070</v>
+        <v>129367637</v>
       </c>
       <c r="B112" t="n">
         <v>79041</v>
@@ -11679,17 +11679,17 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>419795</v>
+        <v>419724</v>
       </c>
       <c r="R112" t="n">
-        <v>6787392</v>
+        <v>6787653</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11733,19 +11733,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129357085</v>
+        <v>129367638</v>
       </c>
       <c r="B113" t="n">
         <v>79041</v>
@@ -11776,17 +11776,17 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>419821</v>
+        <v>419681</v>
       </c>
       <c r="R113" t="n">
-        <v>6787310</v>
+        <v>6787728</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11830,19 +11830,19 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129367637</v>
+        <v>129357054</v>
       </c>
       <c r="B114" t="n">
         <v>79041</v>
@@ -11873,17 +11873,17 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>419724</v>
+        <v>419849</v>
       </c>
       <c r="R114" t="n">
-        <v>6787653</v>
+        <v>6787800</v>
       </c>
       <c r="S114" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11927,12 +11927,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -12133,10 +12133,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129364466</v>
+        <v>129367633</v>
       </c>
       <c r="B117" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12144,37 +12144,37 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>419796</v>
+        <v>419775</v>
       </c>
       <c r="R117" t="n">
-        <v>6787321</v>
+        <v>6787415</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12218,12 +12218,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -12327,10 +12327,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129367633</v>
+        <v>129364466</v>
       </c>
       <c r="B119" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12338,37 +12338,37 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>419775</v>
+        <v>419796</v>
       </c>
       <c r="R119" t="n">
-        <v>6787415</v>
+        <v>6787321</v>
       </c>
       <c r="S119" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12412,12 +12412,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
@@ -12812,10 +12812,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129357043</v>
+        <v>129357068</v>
       </c>
       <c r="B124" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12823,21 +12823,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12847,10 +12847,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>419806</v>
+        <v>419749</v>
       </c>
       <c r="R124" t="n">
-        <v>6787355</v>
+        <v>6787397</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12909,10 +12909,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129357068</v>
+        <v>129357043</v>
       </c>
       <c r="B125" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12920,21 +12920,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12944,10 +12944,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>419749</v>
+        <v>419806</v>
       </c>
       <c r="R125" t="n">
-        <v>6787397</v>
+        <v>6787355</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>

--- a/artfynd/A 46306-2025 artfynd.xlsx
+++ b/artfynd/A 46306-2025 artfynd.xlsx
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129351435</v>
+        <v>129351446</v>
       </c>
       <c r="B13" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>419754</v>
+        <v>419743</v>
       </c>
       <c r="R13" t="n">
-        <v>6787358</v>
+        <v>6787432</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129351446</v>
+        <v>129351435</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>419743</v>
+        <v>419754</v>
       </c>
       <c r="R14" t="n">
-        <v>6787432</v>
+        <v>6787358</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129351479</v>
+        <v>129351436</v>
       </c>
       <c r="B15" t="n">
-        <v>78707</v>
+        <v>78798</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>419670</v>
+        <v>419772</v>
       </c>
       <c r="R15" t="n">
-        <v>6787628</v>
+        <v>6787332</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129351436</v>
+        <v>129351479</v>
       </c>
       <c r="B17" t="n">
-        <v>78798</v>
+        <v>78707</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>419772</v>
+        <v>419670</v>
       </c>
       <c r="R17" t="n">
-        <v>6787332</v>
+        <v>6787628</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129351431</v>
+        <v>129351480</v>
       </c>
       <c r="B21" t="n">
-        <v>79631</v>
+        <v>78707</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>419608</v>
+        <v>419635</v>
       </c>
       <c r="R21" t="n">
-        <v>6787699</v>
+        <v>6787627</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129351480</v>
+        <v>129351431</v>
       </c>
       <c r="B22" t="n">
-        <v>78707</v>
+        <v>79631</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,21 +2826,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>419635</v>
+        <v>419608</v>
       </c>
       <c r="R22" t="n">
-        <v>6787627</v>
+        <v>6787699</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3136,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129351434</v>
+        <v>129351442</v>
       </c>
       <c r="B25" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3147,21 +3147,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>419726</v>
+        <v>419761</v>
       </c>
       <c r="R25" t="n">
-        <v>6787666</v>
+        <v>6787419</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,10 +3243,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129351427</v>
+        <v>129351434</v>
       </c>
       <c r="B26" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3254,21 +3254,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>419606</v>
+        <v>419726</v>
       </c>
       <c r="R26" t="n">
-        <v>6787701</v>
+        <v>6787666</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129351442</v>
+        <v>129351427</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3361,21 +3361,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>419761</v>
+        <v>419606</v>
       </c>
       <c r="R27" t="n">
-        <v>6787419</v>
+        <v>6787701</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,10 +3457,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129357130</v>
+        <v>129367646</v>
       </c>
       <c r="B28" t="n">
-        <v>78049</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3468,37 +3468,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>419740</v>
+        <v>419784</v>
       </c>
       <c r="R28" t="n">
-        <v>6787448</v>
+        <v>6787357</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3542,22 +3542,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129367646</v>
+        <v>129357130</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>78049</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3565,37 +3565,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>419784</v>
+        <v>419740</v>
       </c>
       <c r="R29" t="n">
-        <v>6787357</v>
+        <v>6787448</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3639,60 +3639,69 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129367642</v>
+        <v>129364476</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>419675</v>
+        <v>419720</v>
       </c>
       <c r="R30" t="n">
-        <v>6787516</v>
+        <v>6787656</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3730,25 +3739,26 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129357064</v>
+        <v>129367642</v>
       </c>
       <c r="B31" t="n">
         <v>79041</v>
@@ -3779,17 +3789,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>419697</v>
+        <v>419675</v>
       </c>
       <c r="R31" t="n">
-        <v>6787431</v>
+        <v>6787516</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3833,19 +3843,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129367643</v>
+        <v>129357064</v>
       </c>
       <c r="B32" t="n">
         <v>79041</v>
@@ -3876,17 +3886,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>419668</v>
+        <v>419697</v>
       </c>
       <c r="R32" t="n">
-        <v>6787515</v>
+        <v>6787431</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3930,12 +3940,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4039,57 +4049,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129364476</v>
+        <v>129367643</v>
       </c>
       <c r="B34" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>419720</v>
+        <v>419668</v>
       </c>
       <c r="R34" t="n">
-        <v>6787656</v>
+        <v>6787515</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4127,19 +4128,18 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4243,10 +4243,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129364461</v>
+        <v>129367648</v>
       </c>
       <c r="B36" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4254,37 +4254,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>419639</v>
+        <v>419821</v>
       </c>
       <c r="R36" t="n">
-        <v>6787642</v>
+        <v>6787260</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4328,22 +4328,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129367648</v>
+        <v>129364461</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4351,37 +4351,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>419821</v>
+        <v>419639</v>
       </c>
       <c r="R37" t="n">
-        <v>6787260</v>
+        <v>6787642</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4425,12 +4425,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -5116,7 +5116,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129367624</v>
+        <v>129367650</v>
       </c>
       <c r="B45" t="n">
         <v>79041</v>
@@ -5151,10 +5151,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>419802</v>
+        <v>419833</v>
       </c>
       <c r="R45" t="n">
-        <v>6787354</v>
+        <v>6787235</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5213,7 +5213,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129357086</v>
+        <v>129357122</v>
       </c>
       <c r="B46" t="n">
         <v>79041</v>
@@ -5248,10 +5248,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>419825</v>
+        <v>419905</v>
       </c>
       <c r="R46" t="n">
-        <v>6787284</v>
+        <v>6787672</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5292,6 +5292,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5310,10 +5311,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129367602</v>
+        <v>129357086</v>
       </c>
       <c r="B47" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5321,37 +5322,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>419592</v>
+        <v>419825</v>
       </c>
       <c r="R47" t="n">
-        <v>6787771</v>
+        <v>6787284</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5395,19 +5396,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129367650</v>
+        <v>129357083</v>
       </c>
       <c r="B48" t="n">
         <v>79041</v>
@@ -5438,17 +5439,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>419833</v>
+        <v>419799</v>
       </c>
       <c r="R48" t="n">
-        <v>6787235</v>
+        <v>6787352</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5492,22 +5493,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129364462</v>
+        <v>129367630</v>
       </c>
       <c r="B49" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5515,37 +5516,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>419648</v>
+        <v>419783</v>
       </c>
       <c r="R49" t="n">
-        <v>6787500</v>
+        <v>6787407</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5589,22 +5590,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129357122</v>
+        <v>129367602</v>
       </c>
       <c r="B50" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5612,37 +5613,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>419905</v>
+        <v>419592</v>
       </c>
       <c r="R50" t="n">
-        <v>6787672</v>
+        <v>6787771</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5680,29 +5681,28 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129357083</v>
+        <v>129364462</v>
       </c>
       <c r="B51" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5710,21 +5710,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5734,10 +5734,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>419799</v>
+        <v>419648</v>
       </c>
       <c r="R51" t="n">
-        <v>6787352</v>
+        <v>6787500</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5784,19 +5784,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129367630</v>
+        <v>129367624</v>
       </c>
       <c r="B52" t="n">
         <v>79041</v>
@@ -5831,10 +5831,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>419783</v>
+        <v>419802</v>
       </c>
       <c r="R52" t="n">
-        <v>6787407</v>
+        <v>6787354</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5893,7 +5893,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129357078</v>
+        <v>129367635</v>
       </c>
       <c r="B53" t="n">
         <v>79041</v>
@@ -5924,17 +5924,17 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>419813</v>
+        <v>419731</v>
       </c>
       <c r="R53" t="n">
-        <v>6787347</v>
+        <v>6787436</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5978,19 +5978,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129367635</v>
+        <v>129357078</v>
       </c>
       <c r="B54" t="n">
         <v>79041</v>
@@ -6021,17 +6021,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>419731</v>
+        <v>419813</v>
       </c>
       <c r="R54" t="n">
-        <v>6787436</v>
+        <v>6787347</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6075,22 +6075,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129364464</v>
+        <v>129357077</v>
       </c>
       <c r="B55" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6098,21 +6098,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6122,10 +6122,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>419679</v>
+        <v>419815</v>
       </c>
       <c r="R55" t="n">
-        <v>6787475</v>
+        <v>6787331</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6172,19 +6172,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129367629</v>
+        <v>129357089</v>
       </c>
       <c r="B56" t="n">
         <v>79041</v>
@@ -6215,17 +6215,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>419786</v>
+        <v>419843</v>
       </c>
       <c r="R56" t="n">
-        <v>6787405</v>
+        <v>6787218</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6269,22 +6269,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129357077</v>
+        <v>129364464</v>
       </c>
       <c r="B57" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6292,21 +6292,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6316,10 +6316,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>419815</v>
+        <v>419679</v>
       </c>
       <c r="R57" t="n">
-        <v>6787331</v>
+        <v>6787475</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6366,19 +6366,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129357089</v>
+        <v>129367629</v>
       </c>
       <c r="B58" t="n">
         <v>79041</v>
@@ -6409,17 +6409,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>419843</v>
+        <v>419786</v>
       </c>
       <c r="R58" t="n">
-        <v>6787218</v>
+        <v>6787405</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6463,12 +6463,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6572,7 +6572,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129357058</v>
+        <v>129367628</v>
       </c>
       <c r="B60" t="n">
         <v>79041</v>
@@ -6603,17 +6603,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>419892</v>
+        <v>419795</v>
       </c>
       <c r="R60" t="n">
-        <v>6787687</v>
+        <v>6787387</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6657,19 +6657,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129357069</v>
+        <v>129357058</v>
       </c>
       <c r="B61" t="n">
         <v>79041</v>
@@ -6704,10 +6704,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>419782</v>
+        <v>419892</v>
       </c>
       <c r="R61" t="n">
-        <v>6787403</v>
+        <v>6787687</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6766,7 +6766,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129364485</v>
+        <v>129357053</v>
       </c>
       <c r="B62" t="n">
         <v>79041</v>
@@ -6801,10 +6801,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>419678</v>
+        <v>419835</v>
       </c>
       <c r="R62" t="n">
-        <v>6787476</v>
+        <v>6787789</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6851,19 +6851,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129357053</v>
+        <v>129357069</v>
       </c>
       <c r="B63" t="n">
         <v>79041</v>
@@ -6898,10 +6898,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>419835</v>
+        <v>419782</v>
       </c>
       <c r="R63" t="n">
-        <v>6787789</v>
+        <v>6787403</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6960,7 +6960,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129367628</v>
+        <v>129357065</v>
       </c>
       <c r="B64" t="n">
         <v>79041</v>
@@ -6991,17 +6991,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>419795</v>
+        <v>419776</v>
       </c>
       <c r="R64" t="n">
-        <v>6787387</v>
+        <v>6787371</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7045,19 +7045,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129357065</v>
+        <v>129364485</v>
       </c>
       <c r="B65" t="n">
         <v>79041</v>
@@ -7092,10 +7092,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>419776</v>
+        <v>419678</v>
       </c>
       <c r="R65" t="n">
-        <v>6787371</v>
+        <v>6787476</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7142,12 +7142,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7358,7 +7358,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129357046</v>
+        <v>129357081</v>
       </c>
       <c r="B68" t="n">
         <v>79041</v>
@@ -7393,10 +7393,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>419742</v>
+        <v>419810</v>
       </c>
       <c r="R68" t="n">
-        <v>6787432</v>
+        <v>6787369</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7455,7 +7455,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129357081</v>
+        <v>129357046</v>
       </c>
       <c r="B69" t="n">
         <v>79041</v>
@@ -7490,10 +7490,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>419810</v>
+        <v>419742</v>
       </c>
       <c r="R69" t="n">
-        <v>6787369</v>
+        <v>6787432</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7649,10 +7649,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129357060</v>
+        <v>129367601</v>
       </c>
       <c r="B71" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7660,37 +7660,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>419924</v>
+        <v>419818</v>
       </c>
       <c r="R71" t="n">
-        <v>6787672</v>
+        <v>6787250</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7734,19 +7734,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129357052</v>
+        <v>129357060</v>
       </c>
       <c r="B72" t="n">
         <v>79041</v>
@@ -7781,10 +7781,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>419810</v>
+        <v>419924</v>
       </c>
       <c r="R72" t="n">
-        <v>6787834</v>
+        <v>6787672</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7843,10 +7843,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129367601</v>
+        <v>129357052</v>
       </c>
       <c r="B73" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7854,37 +7854,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>419818</v>
+        <v>419810</v>
       </c>
       <c r="R73" t="n">
-        <v>6787250</v>
+        <v>6787834</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7928,19 +7928,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129367639</v>
+        <v>129367641</v>
       </c>
       <c r="B74" t="n">
         <v>79041</v>
@@ -7975,10 +7975,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>419672</v>
+        <v>419590</v>
       </c>
       <c r="R74" t="n">
-        <v>6787734</v>
+        <v>6787769</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8037,7 +8037,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129367626</v>
+        <v>129367639</v>
       </c>
       <c r="B75" t="n">
         <v>79041</v>
@@ -8072,10 +8072,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>419797</v>
+        <v>419672</v>
       </c>
       <c r="R75" t="n">
-        <v>6787364</v>
+        <v>6787734</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8134,7 +8134,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129367641</v>
+        <v>129367626</v>
       </c>
       <c r="B76" t="n">
         <v>79041</v>
@@ -8169,10 +8169,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>419590</v>
+        <v>419797</v>
       </c>
       <c r="R76" t="n">
-        <v>6787769</v>
+        <v>6787364</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8231,10 +8231,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129367599</v>
+        <v>129364502</v>
       </c>
       <c r="B77" t="n">
-        <v>79660</v>
+        <v>78049</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8242,37 +8242,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>419693</v>
+        <v>419821</v>
       </c>
       <c r="R77" t="n">
-        <v>6787442</v>
+        <v>6787289</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8316,22 +8316,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129367617</v>
+        <v>129367599</v>
       </c>
       <c r="B78" t="n">
-        <v>78799</v>
+        <v>79660</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8339,21 +8339,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8363,10 +8363,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>419617</v>
+        <v>419693</v>
       </c>
       <c r="R78" t="n">
-        <v>6787770</v>
+        <v>6787442</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8425,10 +8425,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129364502</v>
+        <v>129367617</v>
       </c>
       <c r="B79" t="n">
-        <v>78049</v>
+        <v>78799</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8436,37 +8436,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>419821</v>
+        <v>419617</v>
       </c>
       <c r="R79" t="n">
-        <v>6787289</v>
+        <v>6787770</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8510,12 +8510,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8910,10 +8910,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129357036</v>
+        <v>129357050</v>
       </c>
       <c r="B84" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8921,21 +8921,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8945,10 +8945,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>419822</v>
+        <v>419683</v>
       </c>
       <c r="R84" t="n">
-        <v>6787802</v>
+        <v>6787695</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9007,7 +9007,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129357050</v>
+        <v>129367627</v>
       </c>
       <c r="B85" t="n">
         <v>79041</v>
@@ -9038,17 +9038,17 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>419683</v>
+        <v>419795</v>
       </c>
       <c r="R85" t="n">
-        <v>6787695</v>
+        <v>6787371</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9092,19 +9092,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129367627</v>
+        <v>129357088</v>
       </c>
       <c r="B86" t="n">
         <v>79041</v>
@@ -9135,17 +9135,17 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>419795</v>
+        <v>419827</v>
       </c>
       <c r="R86" t="n">
-        <v>6787371</v>
+        <v>6787267</v>
       </c>
       <c r="S86" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9189,19 +9189,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129367598</v>
+        <v>129357036</v>
       </c>
       <c r="B87" t="n">
         <v>79660</v>
@@ -9232,17 +9232,17 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>419671</v>
+        <v>419822</v>
       </c>
       <c r="R87" t="n">
-        <v>6787459</v>
+        <v>6787802</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9286,22 +9286,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129357088</v>
+        <v>129367598</v>
       </c>
       <c r="B88" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9309,37 +9309,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>419827</v>
+        <v>419671</v>
       </c>
       <c r="R88" t="n">
-        <v>6787267</v>
+        <v>6787459</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9383,12 +9383,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -9492,10 +9492,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129367605</v>
+        <v>129357039</v>
       </c>
       <c r="B90" t="n">
-        <v>79631</v>
+        <v>57724</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9503,37 +9503,49 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>419682</v>
+        <v>419783</v>
       </c>
       <c r="R90" t="n">
-        <v>6787451</v>
+        <v>6787400</v>
       </c>
       <c r="S90" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9577,19 +9589,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129367606</v>
+        <v>129367605</v>
       </c>
       <c r="B91" t="n">
         <v>79631</v>
@@ -9624,10 +9636,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>419820</v>
+        <v>419682</v>
       </c>
       <c r="R91" t="n">
-        <v>6787294</v>
+        <v>6787451</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -9686,10 +9698,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129357039</v>
+        <v>129367606</v>
       </c>
       <c r="B92" t="n">
-        <v>57724</v>
+        <v>79631</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9697,49 +9709,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>419783</v>
+        <v>419820</v>
       </c>
       <c r="R92" t="n">
-        <v>6787400</v>
+        <v>6787294</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9783,12 +9783,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -9989,10 +9989,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129364482</v>
+        <v>129367647</v>
       </c>
       <c r="B95" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10000,37 +10000,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>419803</v>
+        <v>419817</v>
       </c>
       <c r="R95" t="n">
-        <v>6787361</v>
+        <v>6787255</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10074,22 +10074,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129364480</v>
+        <v>129357056</v>
       </c>
       <c r="B96" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10097,21 +10097,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10121,10 +10121,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>419678</v>
+        <v>419863</v>
       </c>
       <c r="R96" t="n">
-        <v>6787641</v>
+        <v>6787786</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10171,12 +10171,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -10280,10 +10280,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129367647</v>
+        <v>129364482</v>
       </c>
       <c r="B98" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10291,37 +10291,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>419817</v>
+        <v>419803</v>
       </c>
       <c r="R98" t="n">
-        <v>6787255</v>
+        <v>6787361</v>
       </c>
       <c r="S98" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10365,22 +10365,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129357056</v>
+        <v>129364480</v>
       </c>
       <c r="B99" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10388,21 +10388,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10412,10 +10412,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>419863</v>
+        <v>419678</v>
       </c>
       <c r="R99" t="n">
-        <v>6787786</v>
+        <v>6787641</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10462,12 +10462,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -10668,7 +10668,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129367636</v>
+        <v>129367659</v>
       </c>
       <c r="B102" t="n">
         <v>79041</v>
@@ -10703,10 +10703,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>419729</v>
+        <v>419692</v>
       </c>
       <c r="R102" t="n">
-        <v>6787620</v>
+        <v>6787475</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -10765,10 +10765,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129367659</v>
+        <v>129357044</v>
       </c>
       <c r="B103" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10776,37 +10776,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>419692</v>
+        <v>419817</v>
       </c>
       <c r="R103" t="n">
-        <v>6787475</v>
+        <v>6787353</v>
       </c>
       <c r="S103" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10850,22 +10850,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129357044</v>
+        <v>129367636</v>
       </c>
       <c r="B104" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10873,37 +10873,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>419817</v>
+        <v>419729</v>
       </c>
       <c r="R104" t="n">
-        <v>6787353</v>
+        <v>6787620</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10947,19 +10947,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129357057</v>
+        <v>129364488</v>
       </c>
       <c r="B105" t="n">
         <v>79041</v>
@@ -10994,10 +10994,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>419865</v>
+        <v>419829</v>
       </c>
       <c r="R105" t="n">
-        <v>6787760</v>
+        <v>6787260</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11044,19 +11044,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129367644</v>
+        <v>129357057</v>
       </c>
       <c r="B106" t="n">
         <v>79041</v>
@@ -11087,17 +11087,17 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>419667</v>
+        <v>419865</v>
       </c>
       <c r="R106" t="n">
-        <v>6787466</v>
+        <v>6787760</v>
       </c>
       <c r="S106" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11141,19 +11141,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129364488</v>
+        <v>129357061</v>
       </c>
       <c r="B107" t="n">
         <v>79041</v>
@@ -11188,10 +11188,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>419829</v>
+        <v>419929</v>
       </c>
       <c r="R107" t="n">
-        <v>6787260</v>
+        <v>6787653</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11238,19 +11238,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129357061</v>
+        <v>129367644</v>
       </c>
       <c r="B108" t="n">
         <v>79041</v>
@@ -11281,17 +11281,17 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>419929</v>
+        <v>419667</v>
       </c>
       <c r="R108" t="n">
-        <v>6787653</v>
+        <v>6787466</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11335,12 +11335,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -11454,7 +11454,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129357070</v>
+        <v>129367638</v>
       </c>
       <c r="B110" t="n">
         <v>79041</v>
@@ -11485,17 +11485,17 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>419795</v>
+        <v>419681</v>
       </c>
       <c r="R110" t="n">
-        <v>6787392</v>
+        <v>6787728</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11539,19 +11539,19 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129357085</v>
+        <v>129357054</v>
       </c>
       <c r="B111" t="n">
         <v>79041</v>
@@ -11586,10 +11586,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>419821</v>
+        <v>419849</v>
       </c>
       <c r="R111" t="n">
-        <v>6787310</v>
+        <v>6787800</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11648,7 +11648,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129367637</v>
+        <v>129357070</v>
       </c>
       <c r="B112" t="n">
         <v>79041</v>
@@ -11679,17 +11679,17 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>419724</v>
+        <v>419795</v>
       </c>
       <c r="R112" t="n">
-        <v>6787653</v>
+        <v>6787392</v>
       </c>
       <c r="S112" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11733,19 +11733,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129367638</v>
+        <v>129357085</v>
       </c>
       <c r="B113" t="n">
         <v>79041</v>
@@ -11776,17 +11776,17 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>419681</v>
+        <v>419821</v>
       </c>
       <c r="R113" t="n">
-        <v>6787728</v>
+        <v>6787310</v>
       </c>
       <c r="S113" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11830,19 +11830,19 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129357054</v>
+        <v>129367637</v>
       </c>
       <c r="B114" t="n">
         <v>79041</v>
@@ -11873,17 +11873,17 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>419849</v>
+        <v>419724</v>
       </c>
       <c r="R114" t="n">
-        <v>6787800</v>
+        <v>6787653</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11927,12 +11927,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -12230,10 +12230,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129364468</v>
+        <v>129357062</v>
       </c>
       <c r="B118" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12241,21 +12241,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12265,10 +12265,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>419802</v>
+        <v>419682</v>
       </c>
       <c r="R118" t="n">
-        <v>6787354</v>
+        <v>6787459</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12315,19 +12315,19 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129364466</v>
+        <v>129364468</v>
       </c>
       <c r="B119" t="n">
         <v>79660</v>
@@ -12362,10 +12362,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>419796</v>
+        <v>419802</v>
       </c>
       <c r="R119" t="n">
-        <v>6787321</v>
+        <v>6787354</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12424,10 +12424,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129357062</v>
+        <v>129364466</v>
       </c>
       <c r="B120" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12435,21 +12435,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12459,10 +12459,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>419682</v>
+        <v>419796</v>
       </c>
       <c r="R120" t="n">
-        <v>6787459</v>
+        <v>6787321</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12509,19 +12509,19 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129357049</v>
+        <v>129367640</v>
       </c>
       <c r="B121" t="n">
         <v>79041</v>
@@ -12552,17 +12552,17 @@
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>419707</v>
+        <v>419596</v>
       </c>
       <c r="R121" t="n">
-        <v>6787641</v>
+        <v>6787765</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -12606,19 +12606,19 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129364487</v>
+        <v>129357068</v>
       </c>
       <c r="B122" t="n">
         <v>79041</v>
@@ -12653,10 +12653,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>419795</v>
+        <v>419749</v>
       </c>
       <c r="R122" t="n">
-        <v>6787306</v>
+        <v>6787397</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12703,22 +12703,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129367640</v>
+        <v>129357043</v>
       </c>
       <c r="B123" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12726,37 +12726,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>419596</v>
+        <v>419806</v>
       </c>
       <c r="R123" t="n">
-        <v>6787765</v>
+        <v>6787355</v>
       </c>
       <c r="S123" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -12800,19 +12800,19 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129357068</v>
+        <v>129357049</v>
       </c>
       <c r="B124" t="n">
         <v>79041</v>
@@ -12847,10 +12847,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>419749</v>
+        <v>419707</v>
       </c>
       <c r="R124" t="n">
-        <v>6787397</v>
+        <v>6787641</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12909,10 +12909,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129357043</v>
+        <v>129364487</v>
       </c>
       <c r="B125" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12920,21 +12920,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12944,10 +12944,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>419806</v>
+        <v>419795</v>
       </c>
       <c r="R125" t="n">
-        <v>6787355</v>
+        <v>6787306</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12994,12 +12994,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>

--- a/artfynd/A 46306-2025 artfynd.xlsx
+++ b/artfynd/A 46306-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129351432</v>
       </c>
       <c r="B2" t="n">
-        <v>90572</v>
+        <v>90575</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129351454</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129351453</v>
+        <v>129351428</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,7 +927,7 @@
         <v>419742</v>
       </c>
       <c r="R4" t="n">
-        <v>6787381</v>
+        <v>6787389</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129351428</v>
+        <v>129351453</v>
       </c>
       <c r="B5" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1034,7 +1034,7 @@
         <v>419742</v>
       </c>
       <c r="R5" t="n">
-        <v>6787389</v>
+        <v>6787381</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1106,7 @@
         <v>129351478</v>
       </c>
       <c r="B6" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>129351430</v>
       </c>
       <c r="B7" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129351437</v>
       </c>
       <c r="B8" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>129351444</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>129351449</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>129351443</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>129351447</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129351446</v>
+        <v>129351435</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>78800</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>419743</v>
+        <v>419754</v>
       </c>
       <c r="R13" t="n">
-        <v>6787432</v>
+        <v>6787358</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129351435</v>
+        <v>129351446</v>
       </c>
       <c r="B14" t="n">
-        <v>78798</v>
+        <v>79043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>419754</v>
+        <v>419743</v>
       </c>
       <c r="R14" t="n">
-        <v>6787358</v>
+        <v>6787432</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129351436</v>
+        <v>129351479</v>
       </c>
       <c r="B15" t="n">
-        <v>78798</v>
+        <v>78709</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>419772</v>
+        <v>419670</v>
       </c>
       <c r="R15" t="n">
-        <v>6787332</v>
+        <v>6787628</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2176,7 +2176,7 @@
         <v>129351441</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129351479</v>
+        <v>129351436</v>
       </c>
       <c r="B17" t="n">
-        <v>78707</v>
+        <v>78800</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>419670</v>
+        <v>419772</v>
       </c>
       <c r="R17" t="n">
-        <v>6787628</v>
+        <v>6787332</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2390,7 +2390,7 @@
         <v>129351448</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>129351450</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>129351429</v>
       </c>
       <c r="B20" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>129351480</v>
       </c>
       <c r="B21" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>129351431</v>
       </c>
       <c r="B22" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>129351445</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>129351452</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129351442</v>
+        <v>129351434</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>78800</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3147,21 +3147,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>419761</v>
+        <v>419726</v>
       </c>
       <c r="R25" t="n">
-        <v>6787419</v>
+        <v>6787666</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,10 +3243,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129351434</v>
+        <v>129351427</v>
       </c>
       <c r="B26" t="n">
-        <v>78798</v>
+        <v>79662</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3254,21 +3254,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>419726</v>
+        <v>419606</v>
       </c>
       <c r="R26" t="n">
-        <v>6787666</v>
+        <v>6787701</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129351427</v>
+        <v>129351442</v>
       </c>
       <c r="B27" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3361,21 +3361,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>419606</v>
+        <v>419761</v>
       </c>
       <c r="R27" t="n">
-        <v>6787701</v>
+        <v>6787419</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3460,7 +3460,7 @@
         <v>129367646</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>129357130</v>
       </c>
       <c r="B29" t="n">
-        <v>78049</v>
+        <v>78051</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3651,57 +3651,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129364476</v>
+        <v>129367643</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>419720</v>
+        <v>419668</v>
       </c>
       <c r="R30" t="n">
-        <v>6787656</v>
+        <v>6787515</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3739,29 +3730,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129367642</v>
+        <v>129357064</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3789,17 +3779,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>419675</v>
+        <v>419697</v>
       </c>
       <c r="R31" t="n">
-        <v>6787516</v>
+        <v>6787431</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3843,22 +3833,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129357064</v>
+        <v>129357082</v>
       </c>
       <c r="B32" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3890,10 +3880,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>419697</v>
+        <v>419807</v>
       </c>
       <c r="R32" t="n">
-        <v>6787431</v>
+        <v>6787361</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3952,10 +3942,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129357082</v>
+        <v>129367642</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3983,17 +3973,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>419807</v>
+        <v>419675</v>
       </c>
       <c r="R33" t="n">
-        <v>6787361</v>
+        <v>6787516</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4037,60 +4027,69 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129367643</v>
+        <v>129364476</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>419668</v>
+        <v>419720</v>
       </c>
       <c r="R34" t="n">
-        <v>6787515</v>
+        <v>6787656</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4128,18 +4127,19 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4149,7 +4149,7 @@
         <v>129357051</v>
       </c>
       <c r="B35" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>129367648</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>129364461</v>
       </c>
       <c r="B37" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>129367618</v>
       </c>
       <c r="B38" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>129364500</v>
       </c>
       <c r="B39" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4634,7 +4634,7 @@
         <v>129357067</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>129357075</v>
       </c>
       <c r="B41" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>129367604</v>
       </c>
       <c r="B42" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4922,10 +4922,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129367649</v>
+        <v>129367602</v>
       </c>
       <c r="B43" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4933,21 +4933,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>419830</v>
+        <v>419592</v>
       </c>
       <c r="R43" t="n">
-        <v>6787264</v>
+        <v>6787771</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5019,10 +5019,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129357047</v>
+        <v>129367649</v>
       </c>
       <c r="B44" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5050,17 +5050,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>419732</v>
+        <v>419830</v>
       </c>
       <c r="R44" t="n">
-        <v>6787619</v>
+        <v>6787264</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5104,12 +5104,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5119,7 +5119,7 @@
         <v>129367650</v>
       </c>
       <c r="B45" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5213,10 +5213,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129357122</v>
+        <v>129364462</v>
       </c>
       <c r="B46" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5224,21 +5224,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5248,10 +5248,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>419905</v>
+        <v>419648</v>
       </c>
       <c r="R46" t="n">
-        <v>6787672</v>
+        <v>6787500</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5292,29 +5292,28 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129357086</v>
+        <v>129357047</v>
       </c>
       <c r="B47" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5346,10 +5345,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>419825</v>
+        <v>419732</v>
       </c>
       <c r="R47" t="n">
-        <v>6787284</v>
+        <v>6787619</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5408,10 +5407,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129357083</v>
+        <v>129367624</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5439,17 +5438,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>419799</v>
+        <v>419802</v>
       </c>
       <c r="R48" t="n">
-        <v>6787352</v>
+        <v>6787354</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5493,22 +5492,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129367630</v>
+        <v>129357122</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5536,17 +5535,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>419783</v>
+        <v>419905</v>
       </c>
       <c r="R49" t="n">
-        <v>6787407</v>
+        <v>6787672</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5584,28 +5583,29 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129367602</v>
+        <v>129357086</v>
       </c>
       <c r="B50" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5613,37 +5613,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>419592</v>
+        <v>419825</v>
       </c>
       <c r="R50" t="n">
-        <v>6787771</v>
+        <v>6787284</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5687,22 +5687,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129364462</v>
+        <v>129357083</v>
       </c>
       <c r="B51" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5710,21 +5710,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5734,10 +5734,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>419648</v>
+        <v>419799</v>
       </c>
       <c r="R51" t="n">
-        <v>6787500</v>
+        <v>6787352</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5784,22 +5784,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129367624</v>
+        <v>129367630</v>
       </c>
       <c r="B52" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5831,10 +5831,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>419802</v>
+        <v>419783</v>
       </c>
       <c r="R52" t="n">
-        <v>6787354</v>
+        <v>6787407</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5896,7 +5896,7 @@
         <v>129367635</v>
       </c>
       <c r="B53" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5990,10 +5990,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129357078</v>
+        <v>129364464</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6001,21 +6001,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>419813</v>
+        <v>419679</v>
       </c>
       <c r="R54" t="n">
-        <v>6787347</v>
+        <v>6787475</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6075,22 +6075,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129357077</v>
+        <v>129367603</v>
       </c>
       <c r="B55" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6098,37 +6098,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>419815</v>
+        <v>419817</v>
       </c>
       <c r="R55" t="n">
-        <v>6787331</v>
+        <v>6787314</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6172,22 +6172,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129357089</v>
+        <v>129357078</v>
       </c>
       <c r="B56" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6219,10 +6219,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>419843</v>
+        <v>419813</v>
       </c>
       <c r="R56" t="n">
-        <v>6787218</v>
+        <v>6787347</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6281,10 +6281,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129364464</v>
+        <v>129367629</v>
       </c>
       <c r="B57" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6292,37 +6292,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>419679</v>
+        <v>419786</v>
       </c>
       <c r="R57" t="n">
-        <v>6787475</v>
+        <v>6787405</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6366,22 +6366,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129367629</v>
+        <v>129357077</v>
       </c>
       <c r="B58" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6409,17 +6409,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>419786</v>
+        <v>419815</v>
       </c>
       <c r="R58" t="n">
-        <v>6787405</v>
+        <v>6787331</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6463,22 +6463,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129367603</v>
+        <v>129357089</v>
       </c>
       <c r="B59" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6486,37 +6486,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>419817</v>
+        <v>419843</v>
       </c>
       <c r="R59" t="n">
-        <v>6787314</v>
+        <v>6787218</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6560,60 +6560,69 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129367628</v>
+        <v>129357042</v>
       </c>
       <c r="B60" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>419795</v>
+        <v>419822</v>
       </c>
       <c r="R60" t="n">
-        <v>6787387</v>
+        <v>6787322</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6651,18 +6660,19 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6672,7 +6682,7 @@
         <v>129357058</v>
       </c>
       <c r="B61" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6769,7 +6779,7 @@
         <v>129357053</v>
       </c>
       <c r="B62" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6866,7 +6876,7 @@
         <v>129357069</v>
       </c>
       <c r="B63" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6963,7 +6973,7 @@
         <v>129357065</v>
       </c>
       <c r="B64" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7060,7 +7070,7 @@
         <v>129364485</v>
       </c>
       <c r="B65" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7154,57 +7164,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129357042</v>
+        <v>129367628</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>419822</v>
+        <v>419795</v>
       </c>
       <c r="R66" t="n">
-        <v>6787322</v>
+        <v>6787387</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7242,19 +7243,18 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7264,7 +7264,7 @@
         <v>129357084</v>
       </c>
       <c r="B67" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>129357081</v>
       </c>
       <c r="B68" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>129357046</v>
       </c>
       <c r="B69" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>129357080</v>
       </c>
       <c r="B70" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>129367601</v>
       </c>
       <c r="B71" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>129357060</v>
       </c>
       <c r="B72" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>129357052</v>
       </c>
       <c r="B73" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         <v>129367641</v>
       </c>
       <c r="B74" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8037,10 +8037,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129367639</v>
+        <v>129364502</v>
       </c>
       <c r="B75" t="n">
-        <v>79041</v>
+        <v>78051</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8048,37 +8048,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>419672</v>
+        <v>419821</v>
       </c>
       <c r="R75" t="n">
-        <v>6787734</v>
+        <v>6787289</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8122,22 +8122,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129367626</v>
+        <v>129367599</v>
       </c>
       <c r="B76" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8145,21 +8145,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8169,10 +8169,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>419797</v>
+        <v>419693</v>
       </c>
       <c r="R76" t="n">
-        <v>6787364</v>
+        <v>6787442</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8231,10 +8231,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129364502</v>
+        <v>129367639</v>
       </c>
       <c r="B77" t="n">
-        <v>78049</v>
+        <v>79043</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8242,37 +8242,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>419821</v>
+        <v>419672</v>
       </c>
       <c r="R77" t="n">
-        <v>6787289</v>
+        <v>6787734</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8316,22 +8316,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129367599</v>
+        <v>129367626</v>
       </c>
       <c r="B78" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8339,21 +8339,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8363,10 +8363,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>419693</v>
+        <v>419797</v>
       </c>
       <c r="R78" t="n">
-        <v>6787442</v>
+        <v>6787364</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8428,7 +8428,7 @@
         <v>129367617</v>
       </c>
       <c r="B79" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8525,7 +8525,7 @@
         <v>129357045</v>
       </c>
       <c r="B80" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>129357066</v>
       </c>
       <c r="B81" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>129357087</v>
       </c>
       <c r="B82" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8813,10 +8813,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129367645</v>
+        <v>129357050</v>
       </c>
       <c r="B83" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8844,17 +8844,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>419775</v>
+        <v>419683</v>
       </c>
       <c r="R83" t="n">
-        <v>6787376</v>
+        <v>6787695</v>
       </c>
       <c r="S83" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8898,22 +8898,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129357050</v>
+        <v>129357088</v>
       </c>
       <c r="B84" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8945,10 +8945,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>419683</v>
+        <v>419827</v>
       </c>
       <c r="R84" t="n">
-        <v>6787695</v>
+        <v>6787267</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9007,10 +9007,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129367627</v>
+        <v>129367605</v>
       </c>
       <c r="B85" t="n">
-        <v>79041</v>
+        <v>79633</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9018,21 +9018,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9042,10 +9042,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>419795</v>
+        <v>419682</v>
       </c>
       <c r="R85" t="n">
-        <v>6787371</v>
+        <v>6787451</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9104,10 +9104,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129357088</v>
+        <v>129367606</v>
       </c>
       <c r="B86" t="n">
-        <v>79041</v>
+        <v>79633</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9115,37 +9115,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>419827</v>
+        <v>419820</v>
       </c>
       <c r="R86" t="n">
-        <v>6787267</v>
+        <v>6787294</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9189,22 +9189,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129357036</v>
+        <v>129357039</v>
       </c>
       <c r="B87" t="n">
-        <v>79660</v>
+        <v>57724</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9212,34 +9212,46 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>419822</v>
+        <v>419783</v>
       </c>
       <c r="R87" t="n">
-        <v>6787802</v>
+        <v>6787400</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9298,10 +9310,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129367598</v>
+        <v>129357036</v>
       </c>
       <c r="B88" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9329,17 +9341,17 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>419671</v>
+        <v>419822</v>
       </c>
       <c r="R88" t="n">
-        <v>6787459</v>
+        <v>6787802</v>
       </c>
       <c r="S88" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9383,22 +9395,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129367600</v>
+        <v>129367645</v>
       </c>
       <c r="B89" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9406,21 +9418,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9430,10 +9442,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>419801</v>
+        <v>419775</v>
       </c>
       <c r="R89" t="n">
-        <v>6787284</v>
+        <v>6787376</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9492,10 +9504,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129357039</v>
+        <v>129367627</v>
       </c>
       <c r="B90" t="n">
-        <v>57724</v>
+        <v>79043</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9503,49 +9515,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>419783</v>
+        <v>419795</v>
       </c>
       <c r="R90" t="n">
-        <v>6787400</v>
+        <v>6787371</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9589,22 +9589,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129367605</v>
+        <v>129367598</v>
       </c>
       <c r="B91" t="n">
-        <v>79631</v>
+        <v>79662</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9612,21 +9612,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9636,10 +9636,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>419682</v>
+        <v>419671</v>
       </c>
       <c r="R91" t="n">
-        <v>6787451</v>
+        <v>6787459</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -9698,10 +9698,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129367606</v>
+        <v>129367600</v>
       </c>
       <c r="B92" t="n">
-        <v>79631</v>
+        <v>79662</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9709,21 +9709,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9733,10 +9733,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>419820</v>
+        <v>419801</v>
       </c>
       <c r="R92" t="n">
-        <v>6787294</v>
+        <v>6787284</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -9798,7 +9798,7 @@
         <v>129357073</v>
       </c>
       <c r="B93" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>129357079</v>
       </c>
       <c r="B94" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9989,10 +9989,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129367647</v>
+        <v>129357056</v>
       </c>
       <c r="B95" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10020,17 +10020,17 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>419817</v>
+        <v>419863</v>
       </c>
       <c r="R95" t="n">
-        <v>6787255</v>
+        <v>6787786</v>
       </c>
       <c r="S95" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10074,22 +10074,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129357056</v>
+        <v>129367631</v>
       </c>
       <c r="B96" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10117,17 +10117,17 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>419863</v>
+        <v>419777</v>
       </c>
       <c r="R96" t="n">
-        <v>6787786</v>
+        <v>6787409</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10171,22 +10171,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129367631</v>
+        <v>129364482</v>
       </c>
       <c r="B97" t="n">
-        <v>79041</v>
+        <v>78800</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10194,37 +10194,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>419777</v>
+        <v>419803</v>
       </c>
       <c r="R97" t="n">
-        <v>6787409</v>
+        <v>6787361</v>
       </c>
       <c r="S97" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10268,22 +10268,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129364482</v>
+        <v>129367647</v>
       </c>
       <c r="B98" t="n">
-        <v>78798</v>
+        <v>79043</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10291,37 +10291,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>419803</v>
+        <v>419817</v>
       </c>
       <c r="R98" t="n">
-        <v>6787361</v>
+        <v>6787255</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10365,12 +10365,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -10380,7 +10380,7 @@
         <v>129364480</v>
       </c>
       <c r="B99" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>129364498</v>
       </c>
       <c r="B100" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>129357076</v>
       </c>
       <c r="B101" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>129367659</v>
       </c>
       <c r="B102" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>129357044</v>
       </c>
       <c r="B103" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10865,7 +10865,7 @@
         <v>129367636</v>
       </c>
       <c r="B104" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>129364488</v>
       </c>
       <c r="B105" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>129357057</v>
       </c>
       <c r="B106" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>129357061</v>
       </c>
       <c r="B107" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>129367644</v>
       </c>
       <c r="B108" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11347,54 +11347,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129364478</v>
+        <v>129357054</v>
       </c>
       <c r="B109" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>419796</v>
+        <v>419849</v>
       </c>
       <c r="R109" t="n">
-        <v>6787321</v>
+        <v>6787800</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11435,29 +11426,28 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129367638</v>
+        <v>129357070</v>
       </c>
       <c r="B110" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11485,17 +11475,17 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>419681</v>
+        <v>419795</v>
       </c>
       <c r="R110" t="n">
-        <v>6787728</v>
+        <v>6787392</v>
       </c>
       <c r="S110" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11539,22 +11529,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129357054</v>
+        <v>129357085</v>
       </c>
       <c r="B111" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11586,10 +11576,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>419849</v>
+        <v>419821</v>
       </c>
       <c r="R111" t="n">
-        <v>6787800</v>
+        <v>6787310</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11648,10 +11638,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129357070</v>
+        <v>129357072</v>
       </c>
       <c r="B112" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11683,10 +11673,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>419795</v>
+        <v>419808</v>
       </c>
       <c r="R112" t="n">
-        <v>6787392</v>
+        <v>6787365</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11745,10 +11735,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129357085</v>
+        <v>129357063</v>
       </c>
       <c r="B113" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11780,10 +11770,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>419821</v>
+        <v>419686</v>
       </c>
       <c r="R113" t="n">
-        <v>6787310</v>
+        <v>6787449</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11842,10 +11832,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129367637</v>
+        <v>129367638</v>
       </c>
       <c r="B114" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11877,10 +11867,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>419724</v>
+        <v>419681</v>
       </c>
       <c r="R114" t="n">
-        <v>6787653</v>
+        <v>6787728</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -11939,10 +11929,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129357072</v>
+        <v>129367637</v>
       </c>
       <c r="B115" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11970,17 +11960,17 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>419808</v>
+        <v>419724</v>
       </c>
       <c r="R115" t="n">
-        <v>6787365</v>
+        <v>6787653</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12024,57 +12014,66 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129357063</v>
+        <v>129364478</v>
       </c>
       <c r="B116" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>419686</v>
+        <v>419796</v>
       </c>
       <c r="R116" t="n">
-        <v>6787449</v>
+        <v>6787321</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12115,28 +12114,29 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129367633</v>
+        <v>129357062</v>
       </c>
       <c r="B117" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12164,17 +12164,17 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>419775</v>
+        <v>419682</v>
       </c>
       <c r="R117" t="n">
-        <v>6787415</v>
+        <v>6787459</v>
       </c>
       <c r="S117" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12218,22 +12218,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129357062</v>
+        <v>129367633</v>
       </c>
       <c r="B118" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12261,17 +12261,17 @@
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>419682</v>
+        <v>419775</v>
       </c>
       <c r="R118" t="n">
-        <v>6787459</v>
+        <v>6787415</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12315,12 +12315,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
@@ -12330,7 +12330,7 @@
         <v>129364468</v>
       </c>
       <c r="B119" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>129364466</v>
       </c>
       <c r="B120" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12521,10 +12521,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129367640</v>
+        <v>129364487</v>
       </c>
       <c r="B121" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12552,17 +12552,17 @@
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>419596</v>
+        <v>419795</v>
       </c>
       <c r="R121" t="n">
-        <v>6787765</v>
+        <v>6787306</v>
       </c>
       <c r="S121" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -12606,22 +12606,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129357068</v>
+        <v>129367640</v>
       </c>
       <c r="B122" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12649,17 +12649,17 @@
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>419749</v>
+        <v>419596</v>
       </c>
       <c r="R122" t="n">
-        <v>6787397</v>
+        <v>6787765</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -12703,12 +12703,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -12718,7 +12718,7 @@
         <v>129357043</v>
       </c>
       <c r="B123" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12815,7 +12815,7 @@
         <v>129357049</v>
       </c>
       <c r="B124" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12909,10 +12909,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129364487</v>
+        <v>129357068</v>
       </c>
       <c r="B125" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12944,10 +12944,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>419795</v>
+        <v>419749</v>
       </c>
       <c r="R125" t="n">
-        <v>6787306</v>
+        <v>6787397</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12994,12 +12994,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
@@ -13009,7 +13009,7 @@
         <v>129357037</v>
       </c>
       <c r="B126" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>129367625</v>
       </c>
       <c r="B127" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13200,10 +13200,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129357074</v>
+        <v>129367634</v>
       </c>
       <c r="B128" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13231,17 +13231,17 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>419796</v>
+        <v>419740</v>
       </c>
       <c r="R128" t="n">
-        <v>6787322</v>
+        <v>6787429</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13285,22 +13285,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129357055</v>
+        <v>129357074</v>
       </c>
       <c r="B129" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13332,10 +13332,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>419856</v>
+        <v>419796</v>
       </c>
       <c r="R129" t="n">
-        <v>6787798</v>
+        <v>6787322</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13394,10 +13394,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129367634</v>
+        <v>129357055</v>
       </c>
       <c r="B130" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13425,17 +13425,17 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>419740</v>
+        <v>419856</v>
       </c>
       <c r="R130" t="n">
-        <v>6787429</v>
+        <v>6787798</v>
       </c>
       <c r="S130" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13479,12 +13479,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>

--- a/artfynd/A 46306-2025 artfynd.xlsx
+++ b/artfynd/A 46306-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129351432</v>
       </c>
       <c r="B2" t="n">
-        <v>90613</v>
+        <v>90619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129351454</v>
       </c>
       <c r="B3" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129351453</v>
       </c>
       <c r="B4" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129351428</v>
       </c>
       <c r="B5" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129351478</v>
       </c>
       <c r="B6" t="n">
-        <v>78736</v>
+        <v>78741</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129351437</v>
+        <v>129351430</v>
       </c>
       <c r="B7" t="n">
-        <v>78827</v>
+        <v>79694</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>419820</v>
+        <v>419777</v>
       </c>
       <c r="R7" t="n">
-        <v>6787246</v>
+        <v>6787296</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129351430</v>
+        <v>129351437</v>
       </c>
       <c r="B8" t="n">
-        <v>79689</v>
+        <v>78832</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>419777</v>
+        <v>419820</v>
       </c>
       <c r="R8" t="n">
-        <v>6787296</v>
+        <v>6787246</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,7 +1427,7 @@
         <v>129351444</v>
       </c>
       <c r="B9" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>129351449</v>
       </c>
       <c r="B10" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>129351443</v>
       </c>
       <c r="B11" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>129351447</v>
       </c>
       <c r="B12" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>129351435</v>
       </c>
       <c r="B13" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>129351446</v>
       </c>
       <c r="B14" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129351441</v>
+        <v>129351479</v>
       </c>
       <c r="B15" t="n">
-        <v>79070</v>
+        <v>78741</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>419804</v>
+        <v>419670</v>
       </c>
       <c r="R15" t="n">
-        <v>6787364</v>
+        <v>6787628</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129351436</v>
+        <v>129351441</v>
       </c>
       <c r="B16" t="n">
-        <v>78827</v>
+        <v>79075</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>419772</v>
+        <v>419804</v>
       </c>
       <c r="R16" t="n">
-        <v>6787332</v>
+        <v>6787364</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129351479</v>
+        <v>129351436</v>
       </c>
       <c r="B17" t="n">
-        <v>78736</v>
+        <v>78832</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>419670</v>
+        <v>419772</v>
       </c>
       <c r="R17" t="n">
-        <v>6787628</v>
+        <v>6787332</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2390,7 +2390,7 @@
         <v>129351448</v>
       </c>
       <c r="B18" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>129351450</v>
       </c>
       <c r="B19" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>129351429</v>
       </c>
       <c r="B20" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>129351480</v>
       </c>
       <c r="B21" t="n">
-        <v>78736</v>
+        <v>78741</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>129351431</v>
       </c>
       <c r="B22" t="n">
-        <v>79660</v>
+        <v>79665</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>129351445</v>
       </c>
       <c r="B23" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>129351452</v>
       </c>
       <c r="B24" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>129351442</v>
       </c>
       <c r="B25" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>129351434</v>
       </c>
       <c r="B26" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>129351427</v>
       </c>
       <c r="B27" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>129367646</v>
       </c>
       <c r="B28" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>129357130</v>
       </c>
       <c r="B29" t="n">
-        <v>78078</v>
+        <v>78083</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3651,10 +3651,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129357082</v>
+        <v>129367642</v>
       </c>
       <c r="B30" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3682,17 +3682,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>419807</v>
+        <v>419675</v>
       </c>
       <c r="R30" t="n">
-        <v>6787361</v>
+        <v>6787516</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3736,22 +3736,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129357064</v>
+        <v>129367643</v>
       </c>
       <c r="B31" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3779,17 +3779,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>419697</v>
+        <v>419668</v>
       </c>
       <c r="R31" t="n">
-        <v>6787431</v>
+        <v>6787515</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3833,22 +3833,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129367642</v>
+        <v>129357064</v>
       </c>
       <c r="B32" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3876,17 +3876,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>419675</v>
+        <v>419697</v>
       </c>
       <c r="R32" t="n">
-        <v>6787516</v>
+        <v>6787431</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3930,60 +3930,69 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129367643</v>
+        <v>129364476</v>
       </c>
       <c r="B33" t="n">
-        <v>79070</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>419668</v>
+        <v>419720</v>
       </c>
       <c r="R33" t="n">
-        <v>6787515</v>
+        <v>6787656</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4021,72 +4030,64 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129364476</v>
+        <v>129357082</v>
       </c>
       <c r="B34" t="n">
-        <v>8450</v>
+        <v>79075</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>419720</v>
+        <v>419807</v>
       </c>
       <c r="R34" t="n">
-        <v>6787656</v>
+        <v>6787361</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4127,19 +4128,18 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4149,7 +4149,7 @@
         <v>129357051</v>
       </c>
       <c r="B35" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>129367648</v>
       </c>
       <c r="B36" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4340,10 +4340,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129364461</v>
+        <v>129367618</v>
       </c>
       <c r="B37" t="n">
-        <v>79689</v>
+        <v>78833</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4351,37 +4351,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>419639</v>
+        <v>419635</v>
       </c>
       <c r="R37" t="n">
-        <v>6787642</v>
+        <v>6787658</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4425,22 +4425,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129367618</v>
+        <v>129364461</v>
       </c>
       <c r="B38" t="n">
-        <v>78828</v>
+        <v>79694</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4448,37 +4448,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>419635</v>
+        <v>419639</v>
       </c>
       <c r="R38" t="n">
-        <v>6787658</v>
+        <v>6787642</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4522,22 +4522,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129367604</v>
+        <v>129357067</v>
       </c>
       <c r="B39" t="n">
-        <v>79660</v>
+        <v>79075</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4545,37 +4545,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>419620</v>
+        <v>419791</v>
       </c>
       <c r="R39" t="n">
-        <v>6787769</v>
+        <v>6787358</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4619,22 +4619,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129357067</v>
+        <v>129357075</v>
       </c>
       <c r="B40" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4666,10 +4666,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>419791</v>
+        <v>419809</v>
       </c>
       <c r="R40" t="n">
-        <v>6787358</v>
+        <v>6787307</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4728,10 +4728,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129357075</v>
+        <v>129367604</v>
       </c>
       <c r="B41" t="n">
-        <v>79070</v>
+        <v>79665</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4739,37 +4739,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>419809</v>
+        <v>419620</v>
       </c>
       <c r="R41" t="n">
-        <v>6787307</v>
+        <v>6787769</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4813,12 +4813,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4828,7 +4828,7 @@
         <v>129364500</v>
       </c>
       <c r="B42" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4922,10 +4922,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129357083</v>
+        <v>129367649</v>
       </c>
       <c r="B43" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4953,17 +4953,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>419799</v>
+        <v>419830</v>
       </c>
       <c r="R43" t="n">
-        <v>6787352</v>
+        <v>6787264</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5007,22 +5007,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129367649</v>
+        <v>129367650</v>
       </c>
       <c r="B44" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>419830</v>
+        <v>419833</v>
       </c>
       <c r="R44" t="n">
-        <v>6787264</v>
+        <v>6787235</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5116,10 +5116,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129357086</v>
+        <v>129357122</v>
       </c>
       <c r="B45" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5151,10 +5151,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>419825</v>
+        <v>419905</v>
       </c>
       <c r="R45" t="n">
-        <v>6787284</v>
+        <v>6787672</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5195,6 +5195,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5213,10 +5214,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129357122</v>
+        <v>129357086</v>
       </c>
       <c r="B46" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5248,10 +5249,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>419905</v>
+        <v>419825</v>
       </c>
       <c r="R46" t="n">
-        <v>6787672</v>
+        <v>6787284</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5292,7 +5293,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5311,10 +5311,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129367624</v>
+        <v>129367630</v>
       </c>
       <c r="B47" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>419802</v>
+        <v>419783</v>
       </c>
       <c r="R47" t="n">
-        <v>6787354</v>
+        <v>6787407</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5411,7 +5411,7 @@
         <v>129357047</v>
       </c>
       <c r="B48" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5505,10 +5505,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129367650</v>
+        <v>129367624</v>
       </c>
       <c r="B49" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5540,10 +5540,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>419833</v>
+        <v>419802</v>
       </c>
       <c r="R49" t="n">
-        <v>6787235</v>
+        <v>6787354</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5602,10 +5602,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129367630</v>
+        <v>129357083</v>
       </c>
       <c r="B50" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5633,17 +5633,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>419783</v>
+        <v>419799</v>
       </c>
       <c r="R50" t="n">
-        <v>6787407</v>
+        <v>6787352</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5687,12 +5687,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -5702,7 +5702,7 @@
         <v>129364462</v>
       </c>
       <c r="B51" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>129367602</v>
       </c>
       <c r="B52" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5893,10 +5893,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129357077</v>
+        <v>129367635</v>
       </c>
       <c r="B53" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5924,17 +5924,17 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>419815</v>
+        <v>419731</v>
       </c>
       <c r="R53" t="n">
-        <v>6787331</v>
+        <v>6787436</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5978,22 +5978,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129357089</v>
+        <v>129357078</v>
       </c>
       <c r="B54" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>419843</v>
+        <v>419813</v>
       </c>
       <c r="R54" t="n">
-        <v>6787218</v>
+        <v>6787347</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6087,10 +6087,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129357078</v>
+        <v>129367629</v>
       </c>
       <c r="B55" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6118,17 +6118,17 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>419813</v>
+        <v>419786</v>
       </c>
       <c r="R55" t="n">
-        <v>6787347</v>
+        <v>6787405</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6172,22 +6172,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129367635</v>
+        <v>129357089</v>
       </c>
       <c r="B56" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6215,17 +6215,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>419731</v>
+        <v>419843</v>
       </c>
       <c r="R56" t="n">
-        <v>6787436</v>
+        <v>6787218</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6269,22 +6269,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129367629</v>
+        <v>129357077</v>
       </c>
       <c r="B57" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6312,17 +6312,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>419786</v>
+        <v>419815</v>
       </c>
       <c r="R57" t="n">
-        <v>6787405</v>
+        <v>6787331</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6366,22 +6366,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129367603</v>
+        <v>129364464</v>
       </c>
       <c r="B58" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6409,17 +6409,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>419817</v>
+        <v>419679</v>
       </c>
       <c r="R58" t="n">
-        <v>6787314</v>
+        <v>6787475</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6463,22 +6463,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129364464</v>
+        <v>129367603</v>
       </c>
       <c r="B59" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6506,17 +6506,17 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>419679</v>
+        <v>419817</v>
       </c>
       <c r="R59" t="n">
-        <v>6787475</v>
+        <v>6787314</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6560,12 +6560,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6679,10 +6679,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129364485</v>
+        <v>129367628</v>
       </c>
       <c r="B61" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6710,17 +6710,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>419678</v>
+        <v>419795</v>
       </c>
       <c r="R61" t="n">
-        <v>6787476</v>
+        <v>6787387</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6764,22 +6764,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129357065</v>
+        <v>129357069</v>
       </c>
       <c r="B62" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6811,10 +6811,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>419776</v>
+        <v>419782</v>
       </c>
       <c r="R62" t="n">
-        <v>6787371</v>
+        <v>6787403</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6873,10 +6873,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129357069</v>
+        <v>129357065</v>
       </c>
       <c r="B63" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6908,10 +6908,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>419782</v>
+        <v>419776</v>
       </c>
       <c r="R63" t="n">
-        <v>6787403</v>
+        <v>6787371</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6970,10 +6970,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129357058</v>
+        <v>129364485</v>
       </c>
       <c r="B64" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7005,10 +7005,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>419892</v>
+        <v>419678</v>
       </c>
       <c r="R64" t="n">
-        <v>6787687</v>
+        <v>6787476</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7055,22 +7055,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129357053</v>
+        <v>129357058</v>
       </c>
       <c r="B65" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7102,10 +7102,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>419835</v>
+        <v>419892</v>
       </c>
       <c r="R65" t="n">
-        <v>6787789</v>
+        <v>6787687</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7164,10 +7164,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129367628</v>
+        <v>129357053</v>
       </c>
       <c r="B66" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7195,17 +7195,17 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>419795</v>
+        <v>419835</v>
       </c>
       <c r="R66" t="n">
-        <v>6787387</v>
+        <v>6787789</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7249,22 +7249,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129357081</v>
+        <v>129357084</v>
       </c>
       <c r="B67" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7296,10 +7296,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>419810</v>
+        <v>419816</v>
       </c>
       <c r="R67" t="n">
-        <v>6787369</v>
+        <v>6787364</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7358,10 +7358,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129357084</v>
+        <v>129357081</v>
       </c>
       <c r="B68" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7393,10 +7393,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>419816</v>
+        <v>419810</v>
       </c>
       <c r="R68" t="n">
-        <v>6787364</v>
+        <v>6787369</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7455,10 +7455,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129357080</v>
+        <v>129357046</v>
       </c>
       <c r="B69" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7490,10 +7490,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>419805</v>
+        <v>419742</v>
       </c>
       <c r="R69" t="n">
-        <v>6787361</v>
+        <v>6787432</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7552,10 +7552,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129357046</v>
+        <v>129357080</v>
       </c>
       <c r="B70" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7587,10 +7587,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>419742</v>
+        <v>419805</v>
       </c>
       <c r="R70" t="n">
-        <v>6787432</v>
+        <v>6787361</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7649,10 +7649,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129367601</v>
+        <v>129357060</v>
       </c>
       <c r="B71" t="n">
-        <v>79689</v>
+        <v>79075</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7660,37 +7660,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>419818</v>
+        <v>419924</v>
       </c>
       <c r="R71" t="n">
-        <v>6787250</v>
+        <v>6787672</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7734,12 +7734,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -7749,7 +7749,7 @@
         <v>129357052</v>
       </c>
       <c r="B72" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7843,10 +7843,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129357060</v>
+        <v>129367601</v>
       </c>
       <c r="B73" t="n">
-        <v>79070</v>
+        <v>79694</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7854,37 +7854,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>419924</v>
+        <v>419818</v>
       </c>
       <c r="R73" t="n">
-        <v>6787672</v>
+        <v>6787250</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7928,22 +7928,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129367617</v>
+        <v>129367641</v>
       </c>
       <c r="B74" t="n">
-        <v>78828</v>
+        <v>79075</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7951,21 +7951,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7975,10 +7975,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>419617</v>
+        <v>419590</v>
       </c>
       <c r="R74" t="n">
-        <v>6787770</v>
+        <v>6787769</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8037,10 +8037,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129364502</v>
+        <v>129367599</v>
       </c>
       <c r="B75" t="n">
-        <v>78078</v>
+        <v>79694</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8048,37 +8048,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>419821</v>
+        <v>419693</v>
       </c>
       <c r="R75" t="n">
-        <v>6787289</v>
+        <v>6787442</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8122,22 +8122,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129367599</v>
+        <v>129364502</v>
       </c>
       <c r="B76" t="n">
-        <v>79689</v>
+        <v>78083</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8145,37 +8145,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>419693</v>
+        <v>419821</v>
       </c>
       <c r="R76" t="n">
-        <v>6787442</v>
+        <v>6787289</v>
       </c>
       <c r="S76" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8219,22 +8219,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129367641</v>
+        <v>129367617</v>
       </c>
       <c r="B77" t="n">
-        <v>79070</v>
+        <v>78833</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8242,21 +8242,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>419590</v>
+        <v>419617</v>
       </c>
       <c r="R77" t="n">
-        <v>6787769</v>
+        <v>6787770</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8331,7 +8331,7 @@
         <v>129367639</v>
       </c>
       <c r="B78" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>129367626</v>
       </c>
       <c r="B79" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8522,10 +8522,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129357087</v>
+        <v>129357045</v>
       </c>
       <c r="B80" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8557,10 +8557,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>419820</v>
+        <v>419746</v>
       </c>
       <c r="R80" t="n">
-        <v>6787283</v>
+        <v>6787424</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8622,7 +8622,7 @@
         <v>129357066</v>
       </c>
       <c r="B81" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8716,10 +8716,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129357045</v>
+        <v>129357087</v>
       </c>
       <c r="B82" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8751,10 +8751,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>419746</v>
+        <v>419820</v>
       </c>
       <c r="R82" t="n">
-        <v>6787424</v>
+        <v>6787283</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8813,10 +8813,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129367605</v>
+        <v>129367598</v>
       </c>
       <c r="B83" t="n">
-        <v>79660</v>
+        <v>79694</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8824,21 +8824,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8848,10 +8848,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>419682</v>
+        <v>419671</v>
       </c>
       <c r="R83" t="n">
-        <v>6787451</v>
+        <v>6787459</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -8910,10 +8910,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129367606</v>
+        <v>129357036</v>
       </c>
       <c r="B84" t="n">
-        <v>79660</v>
+        <v>79694</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8921,37 +8921,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>419820</v>
+        <v>419822</v>
       </c>
       <c r="R84" t="n">
-        <v>6787294</v>
+        <v>6787802</v>
       </c>
       <c r="S84" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8995,22 +8995,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129367645</v>
+        <v>129367600</v>
       </c>
       <c r="B85" t="n">
-        <v>79070</v>
+        <v>79694</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9018,21 +9018,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9042,10 +9042,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>419775</v>
+        <v>419801</v>
       </c>
       <c r="R85" t="n">
-        <v>6787376</v>
+        <v>6787284</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9104,10 +9104,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129367598</v>
+        <v>129357039</v>
       </c>
       <c r="B86" t="n">
-        <v>79689</v>
+        <v>57732</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9115,37 +9115,49 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>419671</v>
+        <v>419783</v>
       </c>
       <c r="R86" t="n">
-        <v>6787459</v>
+        <v>6787400</v>
       </c>
       <c r="S86" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9189,22 +9201,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129357036</v>
+        <v>129367627</v>
       </c>
       <c r="B87" t="n">
-        <v>79689</v>
+        <v>79075</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9212,37 +9224,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>419822</v>
+        <v>419795</v>
       </c>
       <c r="R87" t="n">
-        <v>6787802</v>
+        <v>6787371</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9286,22 +9298,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129367600</v>
+        <v>129357088</v>
       </c>
       <c r="B88" t="n">
-        <v>79689</v>
+        <v>79075</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9309,37 +9321,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>419801</v>
+        <v>419827</v>
       </c>
       <c r="R88" t="n">
-        <v>6787284</v>
+        <v>6787267</v>
       </c>
       <c r="S88" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9383,22 +9395,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129367627</v>
+        <v>129367645</v>
       </c>
       <c r="B89" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9430,10 +9442,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>419795</v>
+        <v>419775</v>
       </c>
       <c r="R89" t="n">
-        <v>6787371</v>
+        <v>6787376</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9495,7 +9507,7 @@
         <v>129357050</v>
       </c>
       <c r="B90" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9589,10 +9601,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129357088</v>
+        <v>129367605</v>
       </c>
       <c r="B91" t="n">
-        <v>79070</v>
+        <v>79665</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9600,37 +9612,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>419827</v>
+        <v>419682</v>
       </c>
       <c r="R91" t="n">
-        <v>6787267</v>
+        <v>6787451</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9674,22 +9686,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129357039</v>
+        <v>129367606</v>
       </c>
       <c r="B92" t="n">
-        <v>57727</v>
+        <v>79665</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9697,49 +9709,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>419783</v>
+        <v>419820</v>
       </c>
       <c r="R92" t="n">
-        <v>6787400</v>
+        <v>6787294</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9783,22 +9783,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129357073</v>
+        <v>129367631</v>
       </c>
       <c r="B93" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9826,17 +9826,17 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>419806</v>
+        <v>419777</v>
       </c>
       <c r="R93" t="n">
-        <v>6787347</v>
+        <v>6787409</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9880,22 +9880,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129357056</v>
+        <v>129357073</v>
       </c>
       <c r="B94" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9927,10 +9927,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>419863</v>
+        <v>419806</v>
       </c>
       <c r="R94" t="n">
-        <v>6787786</v>
+        <v>6787347</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9989,10 +9989,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129364480</v>
+        <v>129357079</v>
       </c>
       <c r="B95" t="n">
-        <v>78827</v>
+        <v>79075</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10000,21 +10000,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10024,10 +10024,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>419678</v>
+        <v>419814</v>
       </c>
       <c r="R95" t="n">
-        <v>6787641</v>
+        <v>6787354</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10074,22 +10074,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129364482</v>
+        <v>129367647</v>
       </c>
       <c r="B96" t="n">
-        <v>78827</v>
+        <v>79075</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10097,37 +10097,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>419803</v>
+        <v>419817</v>
       </c>
       <c r="R96" t="n">
-        <v>6787361</v>
+        <v>6787255</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10171,22 +10171,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129357079</v>
+        <v>129357056</v>
       </c>
       <c r="B97" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10218,10 +10218,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>419814</v>
+        <v>419863</v>
       </c>
       <c r="R97" t="n">
-        <v>6787354</v>
+        <v>6787786</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10280,10 +10280,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129367631</v>
+        <v>129364482</v>
       </c>
       <c r="B98" t="n">
-        <v>79070</v>
+        <v>78832</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10291,37 +10291,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>419777</v>
+        <v>419803</v>
       </c>
       <c r="R98" t="n">
-        <v>6787409</v>
+        <v>6787361</v>
       </c>
       <c r="S98" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10365,22 +10365,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129367647</v>
+        <v>129364480</v>
       </c>
       <c r="B99" t="n">
-        <v>79070</v>
+        <v>78832</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10388,37 +10388,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>419817</v>
+        <v>419678</v>
       </c>
       <c r="R99" t="n">
-        <v>6787255</v>
+        <v>6787641</v>
       </c>
       <c r="S99" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10462,44 +10462,44 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129357076</v>
+        <v>129364498</v>
       </c>
       <c r="B100" t="n">
-        <v>79070</v>
+        <v>92869</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10509,10 +10509,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>419818</v>
+        <v>419705</v>
       </c>
       <c r="R100" t="n">
-        <v>6787293</v>
+        <v>6787663</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10559,44 +10559,44 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129364498</v>
+        <v>129357076</v>
       </c>
       <c r="B101" t="n">
-        <v>92863</v>
+        <v>79075</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10606,10 +10606,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>419705</v>
+        <v>419818</v>
       </c>
       <c r="R101" t="n">
-        <v>6787663</v>
+        <v>6787293</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10656,12 +10656,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -10671,7 +10671,7 @@
         <v>129367659</v>
       </c>
       <c r="B102" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>129367636</v>
       </c>
       <c r="B103" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10865,7 +10865,7 @@
         <v>129357044</v>
       </c>
       <c r="B104" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10959,10 +10959,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129367644</v>
+        <v>129364488</v>
       </c>
       <c r="B105" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10990,17 +10990,17 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>419667</v>
+        <v>419829</v>
       </c>
       <c r="R105" t="n">
-        <v>6787466</v>
+        <v>6787260</v>
       </c>
       <c r="S105" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11044,22 +11044,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129364488</v>
+        <v>129357057</v>
       </c>
       <c r="B106" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11091,10 +11091,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>419829</v>
+        <v>419865</v>
       </c>
       <c r="R106" t="n">
-        <v>6787260</v>
+        <v>6787760</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11141,12 +11141,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -11156,7 +11156,7 @@
         <v>129357061</v>
       </c>
       <c r="B107" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11250,10 +11250,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129357057</v>
+        <v>129367644</v>
       </c>
       <c r="B108" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11281,17 +11281,17 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>419865</v>
+        <v>419667</v>
       </c>
       <c r="R108" t="n">
-        <v>6787760</v>
+        <v>6787466</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11335,69 +11335,60 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129364478</v>
+        <v>129367638</v>
       </c>
       <c r="B109" t="n">
-        <v>8450</v>
+        <v>79075</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>419796</v>
+        <v>419681</v>
       </c>
       <c r="R109" t="n">
-        <v>6787321</v>
+        <v>6787728</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11435,29 +11426,28 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129357063</v>
+        <v>129357054</v>
       </c>
       <c r="B110" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11489,10 +11479,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>419686</v>
+        <v>419849</v>
       </c>
       <c r="R110" t="n">
-        <v>6787449</v>
+        <v>6787800</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11551,10 +11541,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129357072</v>
+        <v>129357070</v>
       </c>
       <c r="B111" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11586,10 +11576,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>419808</v>
+        <v>419795</v>
       </c>
       <c r="R111" t="n">
-        <v>6787365</v>
+        <v>6787392</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11648,10 +11638,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129357085</v>
+        <v>129367637</v>
       </c>
       <c r="B112" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11679,17 +11669,17 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>419821</v>
+        <v>419724</v>
       </c>
       <c r="R112" t="n">
-        <v>6787310</v>
+        <v>6787653</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11733,22 +11723,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129357054</v>
+        <v>129357072</v>
       </c>
       <c r="B113" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11780,10 +11770,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>419849</v>
+        <v>419808</v>
       </c>
       <c r="R113" t="n">
-        <v>6787800</v>
+        <v>6787365</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11842,10 +11832,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129357070</v>
+        <v>129357063</v>
       </c>
       <c r="B114" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11877,10 +11867,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>419795</v>
+        <v>419686</v>
       </c>
       <c r="R114" t="n">
-        <v>6787392</v>
+        <v>6787449</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11939,10 +11929,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129367638</v>
+        <v>129357085</v>
       </c>
       <c r="B115" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11970,17 +11960,17 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>419681</v>
+        <v>419821</v>
       </c>
       <c r="R115" t="n">
-        <v>6787728</v>
+        <v>6787310</v>
       </c>
       <c r="S115" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12024,60 +12014,69 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129367637</v>
+        <v>129364478</v>
       </c>
       <c r="B116" t="n">
-        <v>79070</v>
+        <v>8450</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>419724</v>
+        <v>419796</v>
       </c>
       <c r="R116" t="n">
-        <v>6787653</v>
+        <v>6787321</v>
       </c>
       <c r="S116" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12115,28 +12114,29 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129357062</v>
+        <v>129367633</v>
       </c>
       <c r="B117" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12164,17 +12164,17 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>419682</v>
+        <v>419775</v>
       </c>
       <c r="R117" t="n">
-        <v>6787459</v>
+        <v>6787415</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12218,22 +12218,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129367633</v>
+        <v>129364466</v>
       </c>
       <c r="B118" t="n">
-        <v>79070</v>
+        <v>79694</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12241,37 +12241,37 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>419775</v>
+        <v>419796</v>
       </c>
       <c r="R118" t="n">
-        <v>6787415</v>
+        <v>6787321</v>
       </c>
       <c r="S118" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12315,22 +12315,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129364466</v>
+        <v>129364468</v>
       </c>
       <c r="B119" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12362,10 +12362,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>419796</v>
+        <v>419802</v>
       </c>
       <c r="R119" t="n">
-        <v>6787321</v>
+        <v>6787354</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12424,10 +12424,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129364468</v>
+        <v>129357062</v>
       </c>
       <c r="B120" t="n">
-        <v>79689</v>
+        <v>79075</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12435,21 +12435,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12459,10 +12459,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>419802</v>
+        <v>419682</v>
       </c>
       <c r="R120" t="n">
-        <v>6787354</v>
+        <v>6787459</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12509,22 +12509,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129357049</v>
+        <v>129357037</v>
       </c>
       <c r="B121" t="n">
-        <v>79070</v>
+        <v>79665</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12532,21 +12532,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12556,10 +12556,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>419707</v>
+        <v>419822</v>
       </c>
       <c r="R121" t="n">
-        <v>6787641</v>
+        <v>6787799</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12618,10 +12618,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129367640</v>
+        <v>129357049</v>
       </c>
       <c r="B122" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12649,17 +12649,17 @@
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>419596</v>
+        <v>419707</v>
       </c>
       <c r="R122" t="n">
-        <v>6787765</v>
+        <v>6787641</v>
       </c>
       <c r="S122" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -12703,12 +12703,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -12718,7 +12718,7 @@
         <v>129364487</v>
       </c>
       <c r="B123" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12812,10 +12812,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129357043</v>
+        <v>129367640</v>
       </c>
       <c r="B124" t="n">
-        <v>78827</v>
+        <v>79075</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12823,37 +12823,37 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>419806</v>
+        <v>419596</v>
       </c>
       <c r="R124" t="n">
-        <v>6787355</v>
+        <v>6787765</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -12897,22 +12897,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129357068</v>
+        <v>129357043</v>
       </c>
       <c r="B125" t="n">
-        <v>79070</v>
+        <v>78832</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12920,21 +12920,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12944,10 +12944,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>419749</v>
+        <v>419806</v>
       </c>
       <c r="R125" t="n">
-        <v>6787397</v>
+        <v>6787355</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13006,10 +13006,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129357037</v>
+        <v>129357068</v>
       </c>
       <c r="B126" t="n">
-        <v>79660</v>
+        <v>79075</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13017,21 +13017,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13041,10 +13041,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>419822</v>
+        <v>419749</v>
       </c>
       <c r="R126" t="n">
-        <v>6787799</v>
+        <v>6787397</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13103,10 +13103,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129357055</v>
+        <v>129367625</v>
       </c>
       <c r="B127" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13134,17 +13134,17 @@
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>419856</v>
+        <v>419800</v>
       </c>
       <c r="R127" t="n">
-        <v>6787798</v>
+        <v>6787361</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13188,22 +13188,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129357074</v>
+        <v>129357055</v>
       </c>
       <c r="B128" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13235,10 +13235,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>419796</v>
+        <v>419856</v>
       </c>
       <c r="R128" t="n">
-        <v>6787322</v>
+        <v>6787798</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13297,10 +13297,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129367625</v>
+        <v>129367634</v>
       </c>
       <c r="B129" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13332,10 +13332,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>419800</v>
+        <v>419740</v>
       </c>
       <c r="R129" t="n">
-        <v>6787361</v>
+        <v>6787429</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -13394,10 +13394,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129367634</v>
+        <v>129357074</v>
       </c>
       <c r="B130" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13425,17 +13425,17 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>419740</v>
+        <v>419796</v>
       </c>
       <c r="R130" t="n">
-        <v>6787429</v>
+        <v>6787322</v>
       </c>
       <c r="S130" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13479,12 +13479,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
@@ -13494,7 +13494,7 @@
         <v>129367597</v>
       </c>
       <c r="B131" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>129367588</v>
       </c>
       <c r="B132" t="n">
-        <v>78078</v>
+        <v>78083</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13698,7 +13698,7 @@
         <v>129367608</v>
       </c>
       <c r="B133" t="n">
-        <v>90613</v>
+        <v>90619</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>

--- a/artfynd/A 46306-2025 artfynd.xlsx
+++ b/artfynd/A 46306-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129351432</v>
       </c>
       <c r="B2" t="n">
-        <v>90619</v>
+        <v>90620</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129351454</v>
       </c>
       <c r="B3" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129351453</v>
       </c>
       <c r="B4" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129351428</v>
       </c>
       <c r="B5" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129351478</v>
       </c>
       <c r="B6" t="n">
-        <v>78741</v>
+        <v>78742</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>129351430</v>
       </c>
       <c r="B7" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129351437</v>
       </c>
       <c r="B8" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>129351444</v>
       </c>
       <c r="B9" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>129351449</v>
       </c>
       <c r="B10" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>129351443</v>
       </c>
       <c r="B11" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>129351447</v>
       </c>
       <c r="B12" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129351435</v>
+        <v>129351446</v>
       </c>
       <c r="B13" t="n">
-        <v>78832</v>
+        <v>79076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>419754</v>
+        <v>419743</v>
       </c>
       <c r="R13" t="n">
-        <v>6787358</v>
+        <v>6787432</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129351446</v>
+        <v>129351435</v>
       </c>
       <c r="B14" t="n">
-        <v>79075</v>
+        <v>78833</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>419743</v>
+        <v>419754</v>
       </c>
       <c r="R14" t="n">
-        <v>6787432</v>
+        <v>6787358</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,7 +2069,7 @@
         <v>129351479</v>
       </c>
       <c r="B15" t="n">
-        <v>78741</v>
+        <v>78742</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>129351441</v>
       </c>
       <c r="B16" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>129351436</v>
       </c>
       <c r="B17" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>129351448</v>
       </c>
       <c r="B18" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>129351450</v>
       </c>
       <c r="B19" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>129351429</v>
       </c>
       <c r="B20" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129351480</v>
+        <v>129351431</v>
       </c>
       <c r="B21" t="n">
-        <v>78741</v>
+        <v>79666</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>419635</v>
+        <v>419608</v>
       </c>
       <c r="R21" t="n">
-        <v>6787627</v>
+        <v>6787699</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129351431</v>
+        <v>129351480</v>
       </c>
       <c r="B22" t="n">
-        <v>79665</v>
+        <v>78742</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,21 +2826,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>419608</v>
+        <v>419635</v>
       </c>
       <c r="R22" t="n">
-        <v>6787699</v>
+        <v>6787627</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2925,7 +2925,7 @@
         <v>129351445</v>
       </c>
       <c r="B23" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>129351452</v>
       </c>
       <c r="B24" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>129351442</v>
       </c>
       <c r="B25" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>129351434</v>
       </c>
       <c r="B26" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>129351427</v>
       </c>
       <c r="B27" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>129367646</v>
       </c>
       <c r="B28" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>129357130</v>
       </c>
       <c r="B29" t="n">
-        <v>78083</v>
+        <v>78084</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>129367642</v>
       </c>
       <c r="B30" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>129367643</v>
       </c>
       <c r="B31" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>129357064</v>
       </c>
       <c r="B32" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3942,54 +3942,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129364476</v>
+        <v>129357082</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>419720</v>
+        <v>419807</v>
       </c>
       <c r="R33" t="n">
-        <v>6787656</v>
+        <v>6787361</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4030,64 +4021,72 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129357082</v>
+        <v>129364476</v>
       </c>
       <c r="B34" t="n">
-        <v>79075</v>
+        <v>8450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>419807</v>
+        <v>419720</v>
       </c>
       <c r="R34" t="n">
-        <v>6787361</v>
+        <v>6787656</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4128,18 +4127,19 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4149,7 +4149,7 @@
         <v>129357051</v>
       </c>
       <c r="B35" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>129367648</v>
       </c>
       <c r="B36" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4340,10 +4340,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129367618</v>
+        <v>129364461</v>
       </c>
       <c r="B37" t="n">
-        <v>78833</v>
+        <v>79695</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4351,37 +4351,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>419635</v>
+        <v>419639</v>
       </c>
       <c r="R37" t="n">
-        <v>6787658</v>
+        <v>6787642</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4425,22 +4425,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129364461</v>
+        <v>129367618</v>
       </c>
       <c r="B38" t="n">
-        <v>79694</v>
+        <v>78834</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4448,37 +4448,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>419639</v>
+        <v>419635</v>
       </c>
       <c r="R38" t="n">
-        <v>6787642</v>
+        <v>6787658</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4522,22 +4522,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129357067</v>
+        <v>129357075</v>
       </c>
       <c r="B39" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4569,10 +4569,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>419791</v>
+        <v>419809</v>
       </c>
       <c r="R39" t="n">
-        <v>6787358</v>
+        <v>6787307</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4631,10 +4631,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129357075</v>
+        <v>129367604</v>
       </c>
       <c r="B40" t="n">
-        <v>79075</v>
+        <v>79666</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4642,37 +4642,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>419809</v>
+        <v>419620</v>
       </c>
       <c r="R40" t="n">
-        <v>6787307</v>
+        <v>6787769</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4716,22 +4716,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129367604</v>
+        <v>129357067</v>
       </c>
       <c r="B41" t="n">
-        <v>79665</v>
+        <v>79076</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4739,37 +4739,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>419620</v>
+        <v>419791</v>
       </c>
       <c r="R41" t="n">
-        <v>6787769</v>
+        <v>6787358</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4813,12 +4813,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4828,7 +4828,7 @@
         <v>129364500</v>
       </c>
       <c r="B42" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>129367649</v>
       </c>
       <c r="B43" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5019,10 +5019,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129367650</v>
+        <v>129357047</v>
       </c>
       <c r="B44" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5050,17 +5050,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>419833</v>
+        <v>419732</v>
       </c>
       <c r="R44" t="n">
-        <v>6787235</v>
+        <v>6787619</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5104,22 +5104,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129357122</v>
+        <v>129367650</v>
       </c>
       <c r="B45" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5147,17 +5147,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>419905</v>
+        <v>419833</v>
       </c>
       <c r="R45" t="n">
-        <v>6787672</v>
+        <v>6787235</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5195,29 +5195,28 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129357086</v>
+        <v>129367624</v>
       </c>
       <c r="B46" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5245,17 +5244,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>419825</v>
+        <v>419802</v>
       </c>
       <c r="R46" t="n">
-        <v>6787284</v>
+        <v>6787354</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5299,22 +5298,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129367630</v>
+        <v>129357122</v>
       </c>
       <c r="B47" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5342,17 +5341,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>419783</v>
+        <v>419905</v>
       </c>
       <c r="R47" t="n">
-        <v>6787407</v>
+        <v>6787672</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5390,28 +5389,29 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129357047</v>
+        <v>129357086</v>
       </c>
       <c r="B48" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5443,10 +5443,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>419732</v>
+        <v>419825</v>
       </c>
       <c r="R48" t="n">
-        <v>6787619</v>
+        <v>6787284</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5505,10 +5505,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129367624</v>
+        <v>129357083</v>
       </c>
       <c r="B49" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5536,17 +5536,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>419802</v>
+        <v>419799</v>
       </c>
       <c r="R49" t="n">
-        <v>6787354</v>
+        <v>6787352</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5590,22 +5590,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129357083</v>
+        <v>129367630</v>
       </c>
       <c r="B50" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5633,17 +5633,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>419799</v>
+        <v>419783</v>
       </c>
       <c r="R50" t="n">
-        <v>6787352</v>
+        <v>6787407</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5687,22 +5687,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129364462</v>
+        <v>129367602</v>
       </c>
       <c r="B51" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5730,17 +5730,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>419648</v>
+        <v>419592</v>
       </c>
       <c r="R51" t="n">
-        <v>6787500</v>
+        <v>6787771</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5784,22 +5784,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129367602</v>
+        <v>129364462</v>
       </c>
       <c r="B52" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5827,17 +5827,17 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>419592</v>
+        <v>419648</v>
       </c>
       <c r="R52" t="n">
-        <v>6787771</v>
+        <v>6787500</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5881,12 +5881,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -5896,7 +5896,7 @@
         <v>129367635</v>
       </c>
       <c r="B53" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>129357078</v>
       </c>
       <c r="B54" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>129367629</v>
       </c>
       <c r="B55" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6184,10 +6184,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129357089</v>
+        <v>129357077</v>
       </c>
       <c r="B56" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6219,10 +6219,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>419843</v>
+        <v>419815</v>
       </c>
       <c r="R56" t="n">
-        <v>6787218</v>
+        <v>6787331</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6281,10 +6281,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129357077</v>
+        <v>129357089</v>
       </c>
       <c r="B57" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6316,10 +6316,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>419815</v>
+        <v>419843</v>
       </c>
       <c r="R57" t="n">
-        <v>6787331</v>
+        <v>6787218</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6381,7 +6381,7 @@
         <v>129364464</v>
       </c>
       <c r="B58" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         <v>129367603</v>
       </c>
       <c r="B59" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6572,54 +6572,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129357042</v>
+        <v>129357058</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>419822</v>
+        <v>419892</v>
       </c>
       <c r="R60" t="n">
-        <v>6787322</v>
+        <v>6787687</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6660,7 +6651,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6679,10 +6669,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129367628</v>
+        <v>129357053</v>
       </c>
       <c r="B61" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6710,17 +6700,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>419795</v>
+        <v>419835</v>
       </c>
       <c r="R61" t="n">
-        <v>6787387</v>
+        <v>6787789</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6764,22 +6754,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129357069</v>
+        <v>129367628</v>
       </c>
       <c r="B62" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6807,17 +6797,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>419782</v>
+        <v>419795</v>
       </c>
       <c r="R62" t="n">
-        <v>6787403</v>
+        <v>6787387</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6861,22 +6851,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129357065</v>
+        <v>129357069</v>
       </c>
       <c r="B63" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6908,10 +6898,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>419776</v>
+        <v>419782</v>
       </c>
       <c r="R63" t="n">
-        <v>6787371</v>
+        <v>6787403</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6970,10 +6960,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129364485</v>
+        <v>129357065</v>
       </c>
       <c r="B64" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7005,10 +6995,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>419678</v>
+        <v>419776</v>
       </c>
       <c r="R64" t="n">
-        <v>6787476</v>
+        <v>6787371</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7055,22 +7045,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129357058</v>
+        <v>129364485</v>
       </c>
       <c r="B65" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7102,10 +7092,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>419892</v>
+        <v>419678</v>
       </c>
       <c r="R65" t="n">
-        <v>6787687</v>
+        <v>6787476</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7152,57 +7142,66 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129357053</v>
+        <v>129357042</v>
       </c>
       <c r="B66" t="n">
-        <v>79075</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>419835</v>
+        <v>419822</v>
       </c>
       <c r="R66" t="n">
-        <v>6787789</v>
+        <v>6787322</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7243,6 +7242,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7264,7 +7264,7 @@
         <v>129357084</v>
       </c>
       <c r="B67" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>129357081</v>
       </c>
       <c r="B68" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>129357046</v>
       </c>
       <c r="B69" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>129357080</v>
       </c>
       <c r="B70" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7649,10 +7649,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129357060</v>
+        <v>129367601</v>
       </c>
       <c r="B71" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7660,37 +7660,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>419924</v>
+        <v>419818</v>
       </c>
       <c r="R71" t="n">
-        <v>6787672</v>
+        <v>6787250</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7734,22 +7734,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129357052</v>
+        <v>129357060</v>
       </c>
       <c r="B72" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7781,10 +7781,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>419810</v>
+        <v>419924</v>
       </c>
       <c r="R72" t="n">
-        <v>6787834</v>
+        <v>6787672</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7843,10 +7843,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129367601</v>
+        <v>129357052</v>
       </c>
       <c r="B73" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7854,37 +7854,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>419818</v>
+        <v>419810</v>
       </c>
       <c r="R73" t="n">
-        <v>6787250</v>
+        <v>6787834</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7928,12 +7928,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -7943,7 +7943,7 @@
         <v>129367641</v>
       </c>
       <c r="B74" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8037,10 +8037,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129367599</v>
+        <v>129367639</v>
       </c>
       <c r="B75" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8048,21 +8048,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8072,10 +8072,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>419693</v>
+        <v>419672</v>
       </c>
       <c r="R75" t="n">
-        <v>6787442</v>
+        <v>6787734</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8134,10 +8134,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129364502</v>
+        <v>129367626</v>
       </c>
       <c r="B76" t="n">
-        <v>78083</v>
+        <v>79076</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8145,37 +8145,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>419821</v>
+        <v>419797</v>
       </c>
       <c r="R76" t="n">
-        <v>6787289</v>
+        <v>6787364</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8219,22 +8219,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129367617</v>
+        <v>129364502</v>
       </c>
       <c r="B77" t="n">
-        <v>78833</v>
+        <v>78084</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8242,37 +8242,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>419617</v>
+        <v>419821</v>
       </c>
       <c r="R77" t="n">
-        <v>6787770</v>
+        <v>6787289</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8316,22 +8316,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129367639</v>
+        <v>129367599</v>
       </c>
       <c r="B78" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8339,21 +8339,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8363,10 +8363,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>419672</v>
+        <v>419693</v>
       </c>
       <c r="R78" t="n">
-        <v>6787734</v>
+        <v>6787442</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8425,10 +8425,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129367626</v>
+        <v>129367617</v>
       </c>
       <c r="B79" t="n">
-        <v>79075</v>
+        <v>78834</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8436,21 +8436,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8460,10 +8460,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>419797</v>
+        <v>419617</v>
       </c>
       <c r="R79" t="n">
-        <v>6787364</v>
+        <v>6787770</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8525,7 +8525,7 @@
         <v>129357045</v>
       </c>
       <c r="B80" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>129357066</v>
       </c>
       <c r="B81" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>129357087</v>
       </c>
       <c r="B82" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8813,10 +8813,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129367598</v>
+        <v>129367645</v>
       </c>
       <c r="B83" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8824,21 +8824,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8848,10 +8848,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>419671</v>
+        <v>419775</v>
       </c>
       <c r="R83" t="n">
-        <v>6787459</v>
+        <v>6787376</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -8910,10 +8910,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129357036</v>
+        <v>129357050</v>
       </c>
       <c r="B84" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8921,21 +8921,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8945,10 +8945,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>419822</v>
+        <v>419683</v>
       </c>
       <c r="R84" t="n">
-        <v>6787802</v>
+        <v>6787695</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9007,10 +9007,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129367600</v>
+        <v>129367627</v>
       </c>
       <c r="B85" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9018,21 +9018,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9042,10 +9042,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>419801</v>
+        <v>419795</v>
       </c>
       <c r="R85" t="n">
-        <v>6787284</v>
+        <v>6787371</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9104,10 +9104,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129357039</v>
+        <v>129357088</v>
       </c>
       <c r="B86" t="n">
-        <v>57732</v>
+        <v>79076</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9115,46 +9115,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>419783</v>
+        <v>419827</v>
       </c>
       <c r="R86" t="n">
-        <v>6787400</v>
+        <v>6787267</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9213,10 +9201,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129367627</v>
+        <v>129357036</v>
       </c>
       <c r="B87" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9224,37 +9212,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>419795</v>
+        <v>419822</v>
       </c>
       <c r="R87" t="n">
-        <v>6787371</v>
+        <v>6787802</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9298,22 +9286,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129357088</v>
+        <v>129367598</v>
       </c>
       <c r="B88" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9321,37 +9309,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>419827</v>
+        <v>419671</v>
       </c>
       <c r="R88" t="n">
-        <v>6787267</v>
+        <v>6787459</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9395,22 +9383,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129367645</v>
+        <v>129367600</v>
       </c>
       <c r="B89" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9418,21 +9406,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9442,10 +9430,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>419775</v>
+        <v>419801</v>
       </c>
       <c r="R89" t="n">
-        <v>6787376</v>
+        <v>6787284</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9504,10 +9492,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129357050</v>
+        <v>129357039</v>
       </c>
       <c r="B90" t="n">
-        <v>79075</v>
+        <v>57733</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9515,34 +9503,46 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>419683</v>
+        <v>419783</v>
       </c>
       <c r="R90" t="n">
-        <v>6787695</v>
+        <v>6787400</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9604,7 +9604,7 @@
         <v>129367605</v>
       </c>
       <c r="B91" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9701,7 +9701,7 @@
         <v>129367606</v>
       </c>
       <c r="B92" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>129367631</v>
       </c>
       <c r="B93" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>129357073</v>
       </c>
       <c r="B94" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>129357079</v>
       </c>
       <c r="B95" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>129367647</v>
       </c>
       <c r="B96" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>129357056</v>
       </c>
       <c r="B97" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         <v>129364482</v>
       </c>
       <c r="B98" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>129364480</v>
       </c>
       <c r="B99" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10474,32 +10474,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129364498</v>
+        <v>129357076</v>
       </c>
       <c r="B100" t="n">
-        <v>92869</v>
+        <v>79076</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10509,10 +10509,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>419705</v>
+        <v>419818</v>
       </c>
       <c r="R100" t="n">
-        <v>6787663</v>
+        <v>6787293</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10559,44 +10559,44 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129357076</v>
+        <v>129364498</v>
       </c>
       <c r="B101" t="n">
-        <v>79075</v>
+        <v>92870</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10606,10 +10606,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>419818</v>
+        <v>419705</v>
       </c>
       <c r="R101" t="n">
-        <v>6787293</v>
+        <v>6787663</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10656,22 +10656,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129367659</v>
+        <v>129357044</v>
       </c>
       <c r="B102" t="n">
-        <v>79075</v>
+        <v>78833</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10679,37 +10679,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>419692</v>
+        <v>419817</v>
       </c>
       <c r="R102" t="n">
-        <v>6787475</v>
+        <v>6787353</v>
       </c>
       <c r="S102" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10753,22 +10753,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129367636</v>
+        <v>129367659</v>
       </c>
       <c r="B103" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10800,10 +10800,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>419729</v>
+        <v>419692</v>
       </c>
       <c r="R103" t="n">
-        <v>6787620</v>
+        <v>6787475</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -10862,10 +10862,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129357044</v>
+        <v>129367636</v>
       </c>
       <c r="B104" t="n">
-        <v>78832</v>
+        <v>79076</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10873,37 +10873,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>419817</v>
+        <v>419729</v>
       </c>
       <c r="R104" t="n">
-        <v>6787353</v>
+        <v>6787620</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10947,12 +10947,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -10962,7 +10962,7 @@
         <v>129364488</v>
       </c>
       <c r="B105" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>129357057</v>
       </c>
       <c r="B106" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>129357061</v>
       </c>
       <c r="B107" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>129367644</v>
       </c>
       <c r="B108" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>129367638</v>
       </c>
       <c r="B109" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>129357054</v>
       </c>
       <c r="B110" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>129357070</v>
       </c>
       <c r="B111" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11638,10 +11638,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129367637</v>
+        <v>129357085</v>
       </c>
       <c r="B112" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11669,17 +11669,17 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>419724</v>
+        <v>419821</v>
       </c>
       <c r="R112" t="n">
-        <v>6787653</v>
+        <v>6787310</v>
       </c>
       <c r="S112" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11723,22 +11723,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129357072</v>
+        <v>129367637</v>
       </c>
       <c r="B113" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11766,17 +11766,17 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>419808</v>
+        <v>419724</v>
       </c>
       <c r="R113" t="n">
-        <v>6787365</v>
+        <v>6787653</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11820,22 +11820,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129357063</v>
+        <v>129357072</v>
       </c>
       <c r="B114" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11867,10 +11867,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>419686</v>
+        <v>419808</v>
       </c>
       <c r="R114" t="n">
-        <v>6787449</v>
+        <v>6787365</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11929,10 +11929,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129357085</v>
+        <v>129357063</v>
       </c>
       <c r="B115" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>419821</v>
+        <v>419686</v>
       </c>
       <c r="R115" t="n">
-        <v>6787310</v>
+        <v>6787449</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12136,7 +12136,7 @@
         <v>129367633</v>
       </c>
       <c r="B117" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12230,10 +12230,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129364466</v>
+        <v>129357062</v>
       </c>
       <c r="B118" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12241,21 +12241,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12265,10 +12265,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>419796</v>
+        <v>419682</v>
       </c>
       <c r="R118" t="n">
-        <v>6787321</v>
+        <v>6787459</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12315,12 +12315,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
@@ -12330,7 +12330,7 @@
         <v>129364468</v>
       </c>
       <c r="B119" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12424,10 +12424,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129357062</v>
+        <v>129364466</v>
       </c>
       <c r="B120" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12435,21 +12435,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12459,10 +12459,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>419682</v>
+        <v>419796</v>
       </c>
       <c r="R120" t="n">
-        <v>6787459</v>
+        <v>6787321</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12509,12 +12509,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -12524,7 +12524,7 @@
         <v>129357037</v>
       </c>
       <c r="B121" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12618,10 +12618,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129357049</v>
+        <v>129357043</v>
       </c>
       <c r="B122" t="n">
-        <v>79075</v>
+        <v>78833</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12629,21 +12629,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12653,10 +12653,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>419707</v>
+        <v>419806</v>
       </c>
       <c r="R122" t="n">
-        <v>6787641</v>
+        <v>6787355</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12715,10 +12715,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129364487</v>
+        <v>129357049</v>
       </c>
       <c r="B123" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12750,10 +12750,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>419795</v>
+        <v>419707</v>
       </c>
       <c r="R123" t="n">
-        <v>6787306</v>
+        <v>6787641</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12800,22 +12800,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129367640</v>
+        <v>129364487</v>
       </c>
       <c r="B124" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12843,17 +12843,17 @@
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>419596</v>
+        <v>419795</v>
       </c>
       <c r="R124" t="n">
-        <v>6787765</v>
+        <v>6787306</v>
       </c>
       <c r="S124" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -12897,22 +12897,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129357043</v>
+        <v>129367640</v>
       </c>
       <c r="B125" t="n">
-        <v>78832</v>
+        <v>79076</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12920,37 +12920,37 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>419806</v>
+        <v>419596</v>
       </c>
       <c r="R125" t="n">
-        <v>6787355</v>
+        <v>6787765</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -12994,12 +12994,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
@@ -13009,7 +13009,7 @@
         <v>129357068</v>
       </c>
       <c r="B126" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>129367625</v>
       </c>
       <c r="B127" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13200,10 +13200,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129357055</v>
+        <v>129357074</v>
       </c>
       <c r="B128" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13235,10 +13235,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>419856</v>
+        <v>419796</v>
       </c>
       <c r="R128" t="n">
-        <v>6787798</v>
+        <v>6787322</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13297,10 +13297,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129367634</v>
+        <v>129357055</v>
       </c>
       <c r="B129" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13328,17 +13328,17 @@
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>419740</v>
+        <v>419856</v>
       </c>
       <c r="R129" t="n">
-        <v>6787429</v>
+        <v>6787798</v>
       </c>
       <c r="S129" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13382,22 +13382,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129357074</v>
+        <v>129367634</v>
       </c>
       <c r="B130" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13425,17 +13425,17 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>419796</v>
+        <v>419740</v>
       </c>
       <c r="R130" t="n">
-        <v>6787322</v>
+        <v>6787429</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13479,12 +13479,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
@@ -13494,7 +13494,7 @@
         <v>129367597</v>
       </c>
       <c r="B131" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>129367588</v>
       </c>
       <c r="B132" t="n">
-        <v>78083</v>
+        <v>78084</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13698,7 +13698,7 @@
         <v>129367608</v>
       </c>
       <c r="B133" t="n">
-        <v>90619</v>
+        <v>90620</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>

--- a/artfynd/A 46306-2025 artfynd.xlsx
+++ b/artfynd/A 46306-2025 artfynd.xlsx
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129351446</v>
+        <v>129351435</v>
       </c>
       <c r="B13" t="n">
-        <v>79076</v>
+        <v>78833</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>419743</v>
+        <v>419754</v>
       </c>
       <c r="R13" t="n">
-        <v>6787432</v>
+        <v>6787358</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129351435</v>
+        <v>129351446</v>
       </c>
       <c r="B14" t="n">
-        <v>78833</v>
+        <v>79076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>419754</v>
+        <v>419743</v>
       </c>
       <c r="R14" t="n">
-        <v>6787358</v>
+        <v>6787432</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -4534,32 +4534,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129357075</v>
+        <v>129364500</v>
       </c>
       <c r="B39" t="n">
-        <v>79076</v>
+        <v>92870</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4569,10 +4569,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>419809</v>
+        <v>419672</v>
       </c>
       <c r="R39" t="n">
-        <v>6787307</v>
+        <v>6787747</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4619,12 +4619,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4825,32 +4825,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129364500</v>
+        <v>129357075</v>
       </c>
       <c r="B42" t="n">
-        <v>92870</v>
+        <v>79076</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4860,10 +4860,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>419672</v>
+        <v>419809</v>
       </c>
       <c r="R42" t="n">
-        <v>6787747</v>
+        <v>6787307</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4910,12 +4910,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5893,10 +5893,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129367635</v>
+        <v>129364464</v>
       </c>
       <c r="B53" t="n">
-        <v>79076</v>
+        <v>79695</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5904,37 +5904,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>419731</v>
+        <v>419679</v>
       </c>
       <c r="R53" t="n">
-        <v>6787436</v>
+        <v>6787475</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5978,22 +5978,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129357078</v>
+        <v>129367603</v>
       </c>
       <c r="B54" t="n">
-        <v>79076</v>
+        <v>79695</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6001,37 +6001,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>419813</v>
+        <v>419817</v>
       </c>
       <c r="R54" t="n">
-        <v>6787347</v>
+        <v>6787314</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6075,19 +6075,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129367629</v>
+        <v>129367635</v>
       </c>
       <c r="B55" t="n">
         <v>79076</v>
@@ -6122,10 +6122,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>419786</v>
+        <v>419731</v>
       </c>
       <c r="R55" t="n">
-        <v>6787405</v>
+        <v>6787436</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6184,7 +6184,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129357077</v>
+        <v>129357078</v>
       </c>
       <c r="B56" t="n">
         <v>79076</v>
@@ -6219,10 +6219,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>419815</v>
+        <v>419813</v>
       </c>
       <c r="R56" t="n">
-        <v>6787331</v>
+        <v>6787347</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6281,7 +6281,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129357089</v>
+        <v>129367629</v>
       </c>
       <c r="B57" t="n">
         <v>79076</v>
@@ -6312,17 +6312,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>419843</v>
+        <v>419786</v>
       </c>
       <c r="R57" t="n">
-        <v>6787218</v>
+        <v>6787405</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6366,22 +6366,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129364464</v>
+        <v>129357077</v>
       </c>
       <c r="B58" t="n">
-        <v>79695</v>
+        <v>79076</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6389,21 +6389,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6413,10 +6413,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>419679</v>
+        <v>419815</v>
       </c>
       <c r="R58" t="n">
-        <v>6787475</v>
+        <v>6787331</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6463,22 +6463,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129367603</v>
+        <v>129357089</v>
       </c>
       <c r="B59" t="n">
-        <v>79695</v>
+        <v>79076</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6486,37 +6486,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>419817</v>
+        <v>419843</v>
       </c>
       <c r="R59" t="n">
-        <v>6787314</v>
+        <v>6787218</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6560,12 +6560,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7649,10 +7649,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129367601</v>
+        <v>129357060</v>
       </c>
       <c r="B71" t="n">
-        <v>79695</v>
+        <v>79076</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7660,37 +7660,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>419818</v>
+        <v>419924</v>
       </c>
       <c r="R71" t="n">
-        <v>6787250</v>
+        <v>6787672</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7734,19 +7734,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129357060</v>
+        <v>129357052</v>
       </c>
       <c r="B72" t="n">
         <v>79076</v>
@@ -7781,10 +7781,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>419924</v>
+        <v>419810</v>
       </c>
       <c r="R72" t="n">
-        <v>6787672</v>
+        <v>6787834</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7843,10 +7843,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129357052</v>
+        <v>129367601</v>
       </c>
       <c r="B73" t="n">
-        <v>79076</v>
+        <v>79695</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7854,37 +7854,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>419810</v>
+        <v>419818</v>
       </c>
       <c r="R73" t="n">
-        <v>6787834</v>
+        <v>6787250</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7928,22 +7928,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129367641</v>
+        <v>129367617</v>
       </c>
       <c r="B74" t="n">
-        <v>79076</v>
+        <v>78834</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7951,21 +7951,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7975,10 +7975,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>419590</v>
+        <v>419617</v>
       </c>
       <c r="R74" t="n">
-        <v>6787769</v>
+        <v>6787770</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8037,10 +8037,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129367639</v>
+        <v>129364502</v>
       </c>
       <c r="B75" t="n">
-        <v>79076</v>
+        <v>78084</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8048,37 +8048,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>419672</v>
+        <v>419821</v>
       </c>
       <c r="R75" t="n">
-        <v>6787734</v>
+        <v>6787289</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8122,22 +8122,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129367626</v>
+        <v>129367599</v>
       </c>
       <c r="B76" t="n">
-        <v>79076</v>
+        <v>79695</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8145,21 +8145,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8169,10 +8169,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>419797</v>
+        <v>419693</v>
       </c>
       <c r="R76" t="n">
-        <v>6787364</v>
+        <v>6787442</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8231,10 +8231,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129364502</v>
+        <v>129367641</v>
       </c>
       <c r="B77" t="n">
-        <v>78084</v>
+        <v>79076</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8242,37 +8242,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>419821</v>
+        <v>419590</v>
       </c>
       <c r="R77" t="n">
-        <v>6787289</v>
+        <v>6787769</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8316,22 +8316,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129367599</v>
+        <v>129367639</v>
       </c>
       <c r="B78" t="n">
-        <v>79695</v>
+        <v>79076</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8339,21 +8339,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8363,10 +8363,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>419693</v>
+        <v>419672</v>
       </c>
       <c r="R78" t="n">
-        <v>6787442</v>
+        <v>6787734</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8425,10 +8425,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129367617</v>
+        <v>129367626</v>
       </c>
       <c r="B79" t="n">
-        <v>78834</v>
+        <v>79076</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8436,21 +8436,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8460,10 +8460,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>419617</v>
+        <v>419797</v>
       </c>
       <c r="R79" t="n">
-        <v>6787770</v>
+        <v>6787364</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -12521,10 +12521,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129357037</v>
+        <v>129357049</v>
       </c>
       <c r="B121" t="n">
-        <v>79666</v>
+        <v>79076</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12532,21 +12532,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12556,10 +12556,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>419822</v>
+        <v>419707</v>
       </c>
       <c r="R121" t="n">
-        <v>6787799</v>
+        <v>6787641</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12618,10 +12618,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129357043</v>
+        <v>129364487</v>
       </c>
       <c r="B122" t="n">
-        <v>78833</v>
+        <v>79076</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12629,21 +12629,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12653,10 +12653,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>419806</v>
+        <v>419795</v>
       </c>
       <c r="R122" t="n">
-        <v>6787355</v>
+        <v>6787306</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12703,19 +12703,19 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129357049</v>
+        <v>129367640</v>
       </c>
       <c r="B123" t="n">
         <v>79076</v>
@@ -12746,17 +12746,17 @@
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>419707</v>
+        <v>419596</v>
       </c>
       <c r="R123" t="n">
-        <v>6787641</v>
+        <v>6787765</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -12800,19 +12800,19 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129364487</v>
+        <v>129357068</v>
       </c>
       <c r="B124" t="n">
         <v>79076</v>
@@ -12847,10 +12847,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>419795</v>
+        <v>419749</v>
       </c>
       <c r="R124" t="n">
-        <v>6787306</v>
+        <v>6787397</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12897,22 +12897,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129367640</v>
+        <v>129357043</v>
       </c>
       <c r="B125" t="n">
-        <v>79076</v>
+        <v>78833</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12920,37 +12920,37 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>419596</v>
+        <v>419806</v>
       </c>
       <c r="R125" t="n">
-        <v>6787765</v>
+        <v>6787355</v>
       </c>
       <c r="S125" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -12994,22 +12994,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129357068</v>
+        <v>129357037</v>
       </c>
       <c r="B126" t="n">
-        <v>79076</v>
+        <v>79666</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13017,21 +13017,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13041,10 +13041,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>419749</v>
+        <v>419822</v>
       </c>
       <c r="R126" t="n">
-        <v>6787397</v>
+        <v>6787799</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>

--- a/artfynd/A 46306-2025 artfynd.xlsx
+++ b/artfynd/A 46306-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129351432</v>
       </c>
       <c r="B2" t="n">
-        <v>90620</v>
+        <v>90625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129351454</v>
       </c>
       <c r="B3" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129351453</v>
+        <v>129351428</v>
       </c>
       <c r="B4" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,7 +927,7 @@
         <v>419742</v>
       </c>
       <c r="R4" t="n">
-        <v>6787381</v>
+        <v>6787389</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129351428</v>
+        <v>129351453</v>
       </c>
       <c r="B5" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1034,7 +1034,7 @@
         <v>419742</v>
       </c>
       <c r="R5" t="n">
-        <v>6787389</v>
+        <v>6787381</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1106,7 @@
         <v>129351478</v>
       </c>
       <c r="B6" t="n">
-        <v>78742</v>
+        <v>78747</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>129351430</v>
       </c>
       <c r="B7" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129351437</v>
       </c>
       <c r="B8" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>129351444</v>
       </c>
       <c r="B9" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>129351449</v>
       </c>
       <c r="B10" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>129351443</v>
       </c>
       <c r="B11" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>129351447</v>
       </c>
       <c r="B12" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>129351435</v>
       </c>
       <c r="B13" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>129351446</v>
       </c>
       <c r="B14" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>129351479</v>
       </c>
       <c r="B15" t="n">
-        <v>78742</v>
+        <v>78747</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>129351441</v>
       </c>
       <c r="B16" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>129351436</v>
       </c>
       <c r="B17" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>129351448</v>
       </c>
       <c r="B18" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>129351450</v>
       </c>
       <c r="B19" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>129351429</v>
       </c>
       <c r="B20" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>129351431</v>
       </c>
       <c r="B21" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>129351480</v>
       </c>
       <c r="B22" t="n">
-        <v>78742</v>
+        <v>78747</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>129351445</v>
       </c>
       <c r="B23" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>129351452</v>
       </c>
       <c r="B24" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129351442</v>
+        <v>129351434</v>
       </c>
       <c r="B25" t="n">
-        <v>79076</v>
+        <v>78838</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3147,21 +3147,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>419761</v>
+        <v>419726</v>
       </c>
       <c r="R25" t="n">
-        <v>6787419</v>
+        <v>6787666</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,10 +3243,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129351434</v>
+        <v>129351442</v>
       </c>
       <c r="B26" t="n">
-        <v>78833</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3254,21 +3254,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>419726</v>
+        <v>419761</v>
       </c>
       <c r="R26" t="n">
-        <v>6787666</v>
+        <v>6787419</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3353,7 +3353,7 @@
         <v>129351427</v>
       </c>
       <c r="B27" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3457,10 +3457,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129367646</v>
+        <v>129357130</v>
       </c>
       <c r="B28" t="n">
-        <v>79076</v>
+        <v>78089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3468,37 +3468,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>419784</v>
+        <v>419740</v>
       </c>
       <c r="R28" t="n">
-        <v>6787357</v>
+        <v>6787448</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3542,22 +3542,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129357130</v>
+        <v>129367646</v>
       </c>
       <c r="B29" t="n">
-        <v>78084</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3565,37 +3565,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>419740</v>
+        <v>419784</v>
       </c>
       <c r="R29" t="n">
-        <v>6787448</v>
+        <v>6787357</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3639,12 +3639,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3654,7 +3654,7 @@
         <v>129367642</v>
       </c>
       <c r="B30" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>129367643</v>
       </c>
       <c r="B31" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>129357064</v>
       </c>
       <c r="B32" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>129357082</v>
       </c>
       <c r="B33" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>129357051</v>
       </c>
       <c r="B35" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4243,10 +4243,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129367648</v>
+        <v>129364461</v>
       </c>
       <c r="B36" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4254,37 +4254,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>419821</v>
+        <v>419639</v>
       </c>
       <c r="R36" t="n">
-        <v>6787260</v>
+        <v>6787642</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4328,22 +4328,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129364461</v>
+        <v>129367648</v>
       </c>
       <c r="B37" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4351,37 +4351,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>419639</v>
+        <v>419821</v>
       </c>
       <c r="R37" t="n">
-        <v>6787642</v>
+        <v>6787260</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4425,12 +4425,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4440,7 +4440,7 @@
         <v>129367618</v>
       </c>
       <c r="B38" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4534,32 +4534,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129364500</v>
+        <v>129357075</v>
       </c>
       <c r="B39" t="n">
-        <v>92870</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4569,10 +4569,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>419672</v>
+        <v>419809</v>
       </c>
       <c r="R39" t="n">
-        <v>6787747</v>
+        <v>6787307</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4619,60 +4619,60 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129367604</v>
+        <v>129364500</v>
       </c>
       <c r="B40" t="n">
-        <v>79666</v>
+        <v>92875</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>419620</v>
+        <v>419672</v>
       </c>
       <c r="R40" t="n">
-        <v>6787769</v>
+        <v>6787747</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4716,12 +4716,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4731,7 +4731,7 @@
         <v>129357067</v>
       </c>
       <c r="B41" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4825,10 +4825,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129357075</v>
+        <v>129367604</v>
       </c>
       <c r="B42" t="n">
-        <v>79076</v>
+        <v>79671</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4836,37 +4836,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>419809</v>
+        <v>419620</v>
       </c>
       <c r="R42" t="n">
-        <v>6787307</v>
+        <v>6787769</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4910,22 +4910,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129367649</v>
+        <v>129367624</v>
       </c>
       <c r="B43" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>419830</v>
+        <v>419802</v>
       </c>
       <c r="R43" t="n">
-        <v>6787264</v>
+        <v>6787354</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5019,10 +5019,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129357047</v>
+        <v>129367630</v>
       </c>
       <c r="B44" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5050,17 +5050,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>419732</v>
+        <v>419783</v>
       </c>
       <c r="R44" t="n">
-        <v>6787619</v>
+        <v>6787407</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5104,22 +5104,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129367650</v>
+        <v>129367602</v>
       </c>
       <c r="B45" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5127,21 +5127,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5151,10 +5151,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>419833</v>
+        <v>419592</v>
       </c>
       <c r="R45" t="n">
-        <v>6787235</v>
+        <v>6787771</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5206,17 +5206,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129367624</v>
+        <v>129357047</v>
       </c>
       <c r="B46" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5244,17 +5244,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>419802</v>
+        <v>419732</v>
       </c>
       <c r="R46" t="n">
-        <v>6787354</v>
+        <v>6787619</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5298,22 +5298,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129357122</v>
+        <v>129367650</v>
       </c>
       <c r="B47" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5341,17 +5341,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>419905</v>
+        <v>419833</v>
       </c>
       <c r="R47" t="n">
-        <v>6787672</v>
+        <v>6787235</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5389,29 +5389,28 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129357086</v>
+        <v>129364462</v>
       </c>
       <c r="B48" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5419,21 +5418,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5443,10 +5442,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>419825</v>
+        <v>419648</v>
       </c>
       <c r="R48" t="n">
-        <v>6787284</v>
+        <v>6787500</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5493,22 +5492,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129357083</v>
+        <v>129357122</v>
       </c>
       <c r="B49" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5540,10 +5539,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>419799</v>
+        <v>419905</v>
       </c>
       <c r="R49" t="n">
-        <v>6787352</v>
+        <v>6787672</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5584,6 +5583,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5602,10 +5602,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129367630</v>
+        <v>129357086</v>
       </c>
       <c r="B50" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5633,17 +5633,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>419783</v>
+        <v>419825</v>
       </c>
       <c r="R50" t="n">
-        <v>6787407</v>
+        <v>6787284</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5687,22 +5687,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129367602</v>
+        <v>129357083</v>
       </c>
       <c r="B51" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5710,37 +5710,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>419592</v>
+        <v>419799</v>
       </c>
       <c r="R51" t="n">
-        <v>6787771</v>
+        <v>6787352</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5784,22 +5784,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129364462</v>
+        <v>129367649</v>
       </c>
       <c r="B52" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5807,37 +5807,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>419648</v>
+        <v>419830</v>
       </c>
       <c r="R52" t="n">
-        <v>6787500</v>
+        <v>6787264</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5881,22 +5881,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129364464</v>
+        <v>129367635</v>
       </c>
       <c r="B53" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5904,37 +5904,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>419679</v>
+        <v>419731</v>
       </c>
       <c r="R53" t="n">
-        <v>6787475</v>
+        <v>6787436</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5978,22 +5978,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129367603</v>
+        <v>129364464</v>
       </c>
       <c r="B54" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6021,17 +6021,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>419817</v>
+        <v>419679</v>
       </c>
       <c r="R54" t="n">
-        <v>6787314</v>
+        <v>6787475</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6075,22 +6075,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129367635</v>
+        <v>129357078</v>
       </c>
       <c r="B55" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6118,17 +6118,17 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>419731</v>
+        <v>419813</v>
       </c>
       <c r="R55" t="n">
-        <v>6787436</v>
+        <v>6787347</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6172,22 +6172,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129357078</v>
+        <v>129367629</v>
       </c>
       <c r="B56" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6215,17 +6215,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>419813</v>
+        <v>419786</v>
       </c>
       <c r="R56" t="n">
-        <v>6787347</v>
+        <v>6787405</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6269,22 +6269,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129367629</v>
+        <v>129357077</v>
       </c>
       <c r="B57" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6312,17 +6312,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>419786</v>
+        <v>419815</v>
       </c>
       <c r="R57" t="n">
-        <v>6787405</v>
+        <v>6787331</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6366,22 +6366,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129357077</v>
+        <v>129357089</v>
       </c>
       <c r="B58" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6413,10 +6413,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>419815</v>
+        <v>419843</v>
       </c>
       <c r="R58" t="n">
-        <v>6787331</v>
+        <v>6787218</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6475,10 +6475,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129357089</v>
+        <v>129367603</v>
       </c>
       <c r="B59" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6486,37 +6486,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>419843</v>
+        <v>419817</v>
       </c>
       <c r="R59" t="n">
-        <v>6787218</v>
+        <v>6787314</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6560,57 +6560,66 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129357058</v>
+        <v>129357042</v>
       </c>
       <c r="B60" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>419892</v>
+        <v>419822</v>
       </c>
       <c r="R60" t="n">
-        <v>6787687</v>
+        <v>6787322</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6651,6 +6660,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6669,10 +6679,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129357053</v>
+        <v>129367628</v>
       </c>
       <c r="B61" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6700,17 +6710,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>419835</v>
+        <v>419795</v>
       </c>
       <c r="R61" t="n">
-        <v>6787789</v>
+        <v>6787387</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6754,22 +6764,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129367628</v>
+        <v>129357069</v>
       </c>
       <c r="B62" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6797,17 +6807,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>419795</v>
+        <v>419782</v>
       </c>
       <c r="R62" t="n">
-        <v>6787387</v>
+        <v>6787403</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6851,22 +6861,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129357069</v>
+        <v>129357058</v>
       </c>
       <c r="B63" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6898,10 +6908,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>419782</v>
+        <v>419892</v>
       </c>
       <c r="R63" t="n">
-        <v>6787403</v>
+        <v>6787687</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6960,10 +6970,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129357065</v>
+        <v>129357053</v>
       </c>
       <c r="B64" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6995,10 +7005,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>419776</v>
+        <v>419835</v>
       </c>
       <c r="R64" t="n">
-        <v>6787371</v>
+        <v>6787789</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7057,10 +7067,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129364485</v>
+        <v>129357065</v>
       </c>
       <c r="B65" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7092,10 +7102,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>419678</v>
+        <v>419776</v>
       </c>
       <c r="R65" t="n">
-        <v>6787476</v>
+        <v>6787371</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7142,66 +7152,57 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129357042</v>
+        <v>129364485</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>419822</v>
+        <v>419678</v>
       </c>
       <c r="R66" t="n">
-        <v>6787322</v>
+        <v>6787476</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7242,19 +7243,18 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7264,7 +7264,7 @@
         <v>129357084</v>
       </c>
       <c r="B67" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>129357081</v>
       </c>
       <c r="B68" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>129357046</v>
       </c>
       <c r="B69" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>129357080</v>
       </c>
       <c r="B70" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>129357060</v>
       </c>
       <c r="B71" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7746,10 +7746,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129357052</v>
+        <v>129367601</v>
       </c>
       <c r="B72" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7757,37 +7757,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>419810</v>
+        <v>419818</v>
       </c>
       <c r="R72" t="n">
-        <v>6787834</v>
+        <v>6787250</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7831,22 +7831,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129367601</v>
+        <v>129357052</v>
       </c>
       <c r="B73" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7854,37 +7854,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>419818</v>
+        <v>419810</v>
       </c>
       <c r="R73" t="n">
-        <v>6787250</v>
+        <v>6787834</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7928,12 +7928,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -7943,7 +7943,7 @@
         <v>129367617</v>
       </c>
       <c r="B74" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>129364502</v>
       </c>
       <c r="B75" t="n">
-        <v>78084</v>
+        <v>78089</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8134,10 +8134,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129367599</v>
+        <v>129367641</v>
       </c>
       <c r="B76" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8145,21 +8145,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8169,10 +8169,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>419693</v>
+        <v>419590</v>
       </c>
       <c r="R76" t="n">
-        <v>6787442</v>
+        <v>6787769</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8231,10 +8231,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129367641</v>
+        <v>129367639</v>
       </c>
       <c r="B77" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>419590</v>
+        <v>419672</v>
       </c>
       <c r="R77" t="n">
-        <v>6787769</v>
+        <v>6787734</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8328,10 +8328,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129367639</v>
+        <v>129367626</v>
       </c>
       <c r="B78" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8363,10 +8363,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>419672</v>
+        <v>419797</v>
       </c>
       <c r="R78" t="n">
-        <v>6787734</v>
+        <v>6787364</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8425,10 +8425,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129367626</v>
+        <v>129367599</v>
       </c>
       <c r="B79" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8436,21 +8436,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8460,10 +8460,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>419797</v>
+        <v>419693</v>
       </c>
       <c r="R79" t="n">
-        <v>6787364</v>
+        <v>6787442</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8515,7 +8515,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8525,7 +8525,7 @@
         <v>129357045</v>
       </c>
       <c r="B80" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>129357066</v>
       </c>
       <c r="B81" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>129357087</v>
       </c>
       <c r="B82" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8813,10 +8813,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129367645</v>
+        <v>129367598</v>
       </c>
       <c r="B83" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8824,21 +8824,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8848,10 +8848,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>419775</v>
+        <v>419671</v>
       </c>
       <c r="R83" t="n">
-        <v>6787376</v>
+        <v>6787459</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -8903,17 +8903,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129357050</v>
+        <v>129357036</v>
       </c>
       <c r="B84" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8921,21 +8921,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8945,10 +8945,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>419683</v>
+        <v>419822</v>
       </c>
       <c r="R84" t="n">
-        <v>6787695</v>
+        <v>6787802</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9010,7 +9010,7 @@
         <v>129367627</v>
       </c>
       <c r="B85" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9104,10 +9104,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129357088</v>
+        <v>129357039</v>
       </c>
       <c r="B86" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9115,34 +9115,46 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>419827</v>
+        <v>419783</v>
       </c>
       <c r="R86" t="n">
-        <v>6787267</v>
+        <v>6787400</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9201,10 +9213,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129357036</v>
+        <v>129367645</v>
       </c>
       <c r="B87" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9212,37 +9224,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>419822</v>
+        <v>419775</v>
       </c>
       <c r="R87" t="n">
-        <v>6787802</v>
+        <v>6787376</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9286,22 +9298,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129367598</v>
+        <v>129357050</v>
       </c>
       <c r="B88" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9309,37 +9321,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>419671</v>
+        <v>419683</v>
       </c>
       <c r="R88" t="n">
-        <v>6787459</v>
+        <v>6787695</v>
       </c>
       <c r="S88" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9383,22 +9395,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129367600</v>
+        <v>129357088</v>
       </c>
       <c r="B89" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9406,37 +9418,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>419801</v>
+        <v>419827</v>
       </c>
       <c r="R89" t="n">
-        <v>6787284</v>
+        <v>6787267</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9480,22 +9492,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129357039</v>
+        <v>129367600</v>
       </c>
       <c r="B90" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9503,49 +9515,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>419783</v>
+        <v>419801</v>
       </c>
       <c r="R90" t="n">
-        <v>6787400</v>
+        <v>6787284</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9589,12 +9589,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -9604,7 +9604,7 @@
         <v>129367605</v>
       </c>
       <c r="B91" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -9701,7 +9701,7 @@
         <v>129367606</v>
       </c>
       <c r="B92" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9788,17 +9788,17 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129367631</v>
+        <v>129357073</v>
       </c>
       <c r="B93" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9826,17 +9826,17 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>419777</v>
+        <v>419806</v>
       </c>
       <c r="R93" t="n">
-        <v>6787409</v>
+        <v>6787347</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9880,22 +9880,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129357073</v>
+        <v>129357079</v>
       </c>
       <c r="B94" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9927,10 +9927,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>419806</v>
+        <v>419814</v>
       </c>
       <c r="R94" t="n">
-        <v>6787347</v>
+        <v>6787354</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9989,10 +9989,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129357079</v>
+        <v>129364482</v>
       </c>
       <c r="B95" t="n">
-        <v>79076</v>
+        <v>78838</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10000,21 +10000,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10024,10 +10024,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>419814</v>
+        <v>419803</v>
       </c>
       <c r="R95" t="n">
-        <v>6787354</v>
+        <v>6787361</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10074,12 +10074,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -10089,7 +10089,7 @@
         <v>129367647</v>
       </c>
       <c r="B96" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>129357056</v>
       </c>
       <c r="B97" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10280,10 +10280,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129364482</v>
+        <v>129364480</v>
       </c>
       <c r="B98" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10315,10 +10315,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>419803</v>
+        <v>419678</v>
       </c>
       <c r="R98" t="n">
-        <v>6787361</v>
+        <v>6787641</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10377,10 +10377,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129364480</v>
+        <v>129367631</v>
       </c>
       <c r="B99" t="n">
-        <v>78833</v>
+        <v>79081</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10388,37 +10388,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>419678</v>
+        <v>419777</v>
       </c>
       <c r="R99" t="n">
-        <v>6787641</v>
+        <v>6787409</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10462,44 +10462,44 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129357076</v>
+        <v>129364498</v>
       </c>
       <c r="B100" t="n">
-        <v>79076</v>
+        <v>92875</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10509,10 +10509,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>419818</v>
+        <v>419705</v>
       </c>
       <c r="R100" t="n">
-        <v>6787293</v>
+        <v>6787663</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10559,44 +10559,44 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129364498</v>
+        <v>129357076</v>
       </c>
       <c r="B101" t="n">
-        <v>92870</v>
+        <v>79081</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10606,10 +10606,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>419705</v>
+        <v>419818</v>
       </c>
       <c r="R101" t="n">
-        <v>6787663</v>
+        <v>6787293</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10656,22 +10656,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129357044</v>
+        <v>129367659</v>
       </c>
       <c r="B102" t="n">
-        <v>78833</v>
+        <v>79081</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10679,37 +10679,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>419817</v>
+        <v>419692</v>
       </c>
       <c r="R102" t="n">
-        <v>6787353</v>
+        <v>6787475</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10753,22 +10753,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129367659</v>
+        <v>129357044</v>
       </c>
       <c r="B103" t="n">
-        <v>79076</v>
+        <v>78838</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10776,37 +10776,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>419692</v>
+        <v>419817</v>
       </c>
       <c r="R103" t="n">
-        <v>6787475</v>
+        <v>6787353</v>
       </c>
       <c r="S103" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10850,12 +10850,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -10865,7 +10865,7 @@
         <v>129367636</v>
       </c>
       <c r="B104" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10959,10 +10959,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129364488</v>
+        <v>129367644</v>
       </c>
       <c r="B105" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10990,17 +10990,17 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>419829</v>
+        <v>419667</v>
       </c>
       <c r="R105" t="n">
-        <v>6787260</v>
+        <v>6787466</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11044,22 +11044,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129357057</v>
+        <v>129364488</v>
       </c>
       <c r="B106" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11091,10 +11091,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>419865</v>
+        <v>419829</v>
       </c>
       <c r="R106" t="n">
-        <v>6787760</v>
+        <v>6787260</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11141,22 +11141,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129357061</v>
+        <v>129357057</v>
       </c>
       <c r="B107" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11188,10 +11188,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>419929</v>
+        <v>419865</v>
       </c>
       <c r="R107" t="n">
-        <v>6787653</v>
+        <v>6787760</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11250,10 +11250,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129367644</v>
+        <v>129357061</v>
       </c>
       <c r="B108" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11281,17 +11281,17 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>419667</v>
+        <v>419929</v>
       </c>
       <c r="R108" t="n">
-        <v>6787466</v>
+        <v>6787653</v>
       </c>
       <c r="S108" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11335,12 +11335,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -11350,7 +11350,7 @@
         <v>129367638</v>
       </c>
       <c r="B109" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>129357054</v>
       </c>
       <c r="B110" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11541,10 +11541,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129357070</v>
+        <v>129367637</v>
       </c>
       <c r="B111" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11572,17 +11572,17 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>419795</v>
+        <v>419724</v>
       </c>
       <c r="R111" t="n">
-        <v>6787392</v>
+        <v>6787653</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11626,57 +11626,66 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129357085</v>
+        <v>129364478</v>
       </c>
       <c r="B112" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>419821</v>
+        <v>419796</v>
       </c>
       <c r="R112" t="n">
-        <v>6787310</v>
+        <v>6787321</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11717,28 +11726,29 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129367637</v>
+        <v>129357070</v>
       </c>
       <c r="B113" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11766,17 +11776,17 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>419724</v>
+        <v>419795</v>
       </c>
       <c r="R113" t="n">
-        <v>6787653</v>
+        <v>6787392</v>
       </c>
       <c r="S113" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11820,22 +11830,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129357072</v>
+        <v>129357085</v>
       </c>
       <c r="B114" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11867,10 +11877,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>419808</v>
+        <v>419821</v>
       </c>
       <c r="R114" t="n">
-        <v>6787365</v>
+        <v>6787310</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11929,10 +11939,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129357063</v>
+        <v>129357072</v>
       </c>
       <c r="B115" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11964,10 +11974,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>419686</v>
+        <v>419808</v>
       </c>
       <c r="R115" t="n">
-        <v>6787449</v>
+        <v>6787365</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12026,54 +12036,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129364478</v>
+        <v>129357063</v>
       </c>
       <c r="B116" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>419796</v>
+        <v>419686</v>
       </c>
       <c r="R116" t="n">
-        <v>6787321</v>
+        <v>6787449</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12114,19 +12115,18 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -12136,7 +12136,7 @@
         <v>129367633</v>
       </c>
       <c r="B117" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12233,7 +12233,7 @@
         <v>129357062</v>
       </c>
       <c r="B118" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>129364468</v>
       </c>
       <c r="B119" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>129364466</v>
       </c>
       <c r="B120" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>129357049</v>
       </c>
       <c r="B121" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>129364487</v>
       </c>
       <c r="B122" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>129367640</v>
       </c>
       <c r="B123" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12812,10 +12812,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129357068</v>
+        <v>129357043</v>
       </c>
       <c r="B124" t="n">
-        <v>79076</v>
+        <v>78838</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12823,21 +12823,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12847,10 +12847,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>419749</v>
+        <v>419806</v>
       </c>
       <c r="R124" t="n">
-        <v>6787397</v>
+        <v>6787355</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12909,10 +12909,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129357043</v>
+        <v>129357068</v>
       </c>
       <c r="B125" t="n">
-        <v>78833</v>
+        <v>79081</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12920,21 +12920,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12944,10 +12944,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>419806</v>
+        <v>419749</v>
       </c>
       <c r="R125" t="n">
-        <v>6787355</v>
+        <v>6787397</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13009,7 +13009,7 @@
         <v>129357037</v>
       </c>
       <c r="B126" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13103,10 +13103,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129367625</v>
+        <v>129367634</v>
       </c>
       <c r="B127" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13138,10 +13138,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>419800</v>
+        <v>419740</v>
       </c>
       <c r="R127" t="n">
-        <v>6787361</v>
+        <v>6787429</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -13200,10 +13200,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129357074</v>
+        <v>129367625</v>
       </c>
       <c r="B128" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13231,17 +13231,17 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>419796</v>
+        <v>419800</v>
       </c>
       <c r="R128" t="n">
-        <v>6787322</v>
+        <v>6787361</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13285,22 +13285,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129357055</v>
+        <v>129357074</v>
       </c>
       <c r="B129" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13332,10 +13332,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>419856</v>
+        <v>419796</v>
       </c>
       <c r="R129" t="n">
-        <v>6787798</v>
+        <v>6787322</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13394,10 +13394,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129367634</v>
+        <v>129357055</v>
       </c>
       <c r="B130" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13425,17 +13425,17 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>419740</v>
+        <v>419856</v>
       </c>
       <c r="R130" t="n">
-        <v>6787429</v>
+        <v>6787798</v>
       </c>
       <c r="S130" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13479,12 +13479,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
@@ -13494,7 +13494,7 @@
         <v>129367597</v>
       </c>
       <c r="B131" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
@@ -13600,7 +13600,7 @@
         <v>129367588</v>
       </c>
       <c r="B132" t="n">
-        <v>78084</v>
+        <v>78089</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13698,7 +13698,7 @@
         <v>129367608</v>
       </c>
       <c r="B133" t="n">
-        <v>90620</v>
+        <v>90625</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>

--- a/artfynd/A 46306-2025 artfynd.xlsx
+++ b/artfynd/A 46306-2025 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129351428</v>
+        <v>129351453</v>
       </c>
       <c r="B4" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,7 +927,7 @@
         <v>419742</v>
       </c>
       <c r="R4" t="n">
-        <v>6787389</v>
+        <v>6787381</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129351453</v>
+        <v>129351428</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1034,7 +1034,7 @@
         <v>419742</v>
       </c>
       <c r="R5" t="n">
-        <v>6787381</v>
+        <v>6787389</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -3457,10 +3457,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129357130</v>
+        <v>129367646</v>
       </c>
       <c r="B28" t="n">
-        <v>78089</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3468,37 +3468,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>419740</v>
+        <v>419784</v>
       </c>
       <c r="R28" t="n">
-        <v>6787448</v>
+        <v>6787357</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3542,22 +3542,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129367646</v>
+        <v>129357130</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>78089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3565,37 +3565,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>419784</v>
+        <v>419740</v>
       </c>
       <c r="R29" t="n">
-        <v>6787357</v>
+        <v>6787448</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3639,60 +3639,69 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129367642</v>
+        <v>129364476</v>
       </c>
       <c r="B30" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>419675</v>
+        <v>419720</v>
       </c>
       <c r="R30" t="n">
-        <v>6787516</v>
+        <v>6787656</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3730,25 +3739,26 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129367643</v>
+        <v>129367642</v>
       </c>
       <c r="B31" t="n">
         <v>79081</v>
@@ -3783,10 +3793,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>419668</v>
+        <v>419675</v>
       </c>
       <c r="R31" t="n">
-        <v>6787515</v>
+        <v>6787516</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3845,7 +3855,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129357064</v>
+        <v>129367643</v>
       </c>
       <c r="B32" t="n">
         <v>79081</v>
@@ -3876,17 +3886,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>419697</v>
+        <v>419668</v>
       </c>
       <c r="R32" t="n">
-        <v>6787431</v>
+        <v>6787515</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3930,19 +3940,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129357082</v>
+        <v>129357064</v>
       </c>
       <c r="B33" t="n">
         <v>79081</v>
@@ -3977,10 +3987,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>419807</v>
+        <v>419697</v>
       </c>
       <c r="R33" t="n">
-        <v>6787361</v>
+        <v>6787431</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4039,54 +4049,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129364476</v>
+        <v>129357082</v>
       </c>
       <c r="B34" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>419720</v>
+        <v>419807</v>
       </c>
       <c r="R34" t="n">
-        <v>6787656</v>
+        <v>6787361</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4127,29 +4128,28 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129357051</v>
+        <v>129367618</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4157,37 +4157,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>419703</v>
+        <v>419635</v>
       </c>
       <c r="R35" t="n">
-        <v>6787692</v>
+        <v>6787658</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4231,22 +4231,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129364461</v>
+        <v>129357051</v>
       </c>
       <c r="B36" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4254,21 +4254,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4278,10 +4278,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>419639</v>
+        <v>419703</v>
       </c>
       <c r="R36" t="n">
-        <v>6787642</v>
+        <v>6787692</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4328,22 +4328,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129367648</v>
+        <v>129364461</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4351,37 +4351,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>419821</v>
+        <v>419639</v>
       </c>
       <c r="R37" t="n">
-        <v>6787260</v>
+        <v>6787642</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4425,22 +4425,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129367618</v>
+        <v>129367648</v>
       </c>
       <c r="B38" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4448,21 +4448,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4472,10 +4472,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>419635</v>
+        <v>419821</v>
       </c>
       <c r="R38" t="n">
-        <v>6787658</v>
+        <v>6787260</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129357075</v>
+        <v>129357067</v>
       </c>
       <c r="B39" t="n">
         <v>79081</v>
@@ -4569,10 +4569,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>419809</v>
+        <v>419791</v>
       </c>
       <c r="R39" t="n">
-        <v>6787307</v>
+        <v>6787358</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4631,32 +4631,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129364500</v>
+        <v>129357075</v>
       </c>
       <c r="B40" t="n">
-        <v>92875</v>
+        <v>79081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4666,10 +4666,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>419672</v>
+        <v>419809</v>
       </c>
       <c r="R40" t="n">
-        <v>6787747</v>
+        <v>6787307</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4716,44 +4716,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129357067</v>
+        <v>129364500</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>92875</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4763,10 +4763,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>419791</v>
+        <v>419672</v>
       </c>
       <c r="R41" t="n">
-        <v>6787358</v>
+        <v>6787747</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4813,12 +4813,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4915,17 +4915,17 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129367624</v>
+        <v>129367602</v>
       </c>
       <c r="B43" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4933,21 +4933,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>419802</v>
+        <v>419592</v>
       </c>
       <c r="R43" t="n">
-        <v>6787354</v>
+        <v>6787771</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5019,7 +5019,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129367630</v>
+        <v>129367649</v>
       </c>
       <c r="B44" t="n">
         <v>79081</v>
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>419783</v>
+        <v>419830</v>
       </c>
       <c r="R44" t="n">
-        <v>6787407</v>
+        <v>6787264</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5116,10 +5116,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129367602</v>
+        <v>129357047</v>
       </c>
       <c r="B45" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5127,37 +5127,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>419592</v>
+        <v>419732</v>
       </c>
       <c r="R45" t="n">
-        <v>6787771</v>
+        <v>6787619</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5201,19 +5201,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129357047</v>
+        <v>129367650</v>
       </c>
       <c r="B46" t="n">
         <v>79081</v>
@@ -5244,17 +5244,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>419732</v>
+        <v>419833</v>
       </c>
       <c r="R46" t="n">
-        <v>6787619</v>
+        <v>6787235</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5298,22 +5298,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129367650</v>
+        <v>129364462</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5321,37 +5321,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>419833</v>
+        <v>419648</v>
       </c>
       <c r="R47" t="n">
-        <v>6787235</v>
+        <v>6787500</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5395,22 +5395,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129364462</v>
+        <v>129367624</v>
       </c>
       <c r="B48" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5418,37 +5418,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>419648</v>
+        <v>419802</v>
       </c>
       <c r="R48" t="n">
-        <v>6787500</v>
+        <v>6787354</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5492,12 +5492,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5796,7 +5796,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129367649</v>
+        <v>129367630</v>
       </c>
       <c r="B52" t="n">
         <v>79081</v>
@@ -5831,10 +5831,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>419830</v>
+        <v>419783</v>
       </c>
       <c r="R52" t="n">
-        <v>6787264</v>
+        <v>6787407</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6565,7 +6565,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6679,7 +6679,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129367628</v>
+        <v>129357058</v>
       </c>
       <c r="B61" t="n">
         <v>79081</v>
@@ -6710,17 +6710,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>419795</v>
+        <v>419892</v>
       </c>
       <c r="R61" t="n">
-        <v>6787387</v>
+        <v>6787687</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6764,19 +6764,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129357069</v>
+        <v>129357053</v>
       </c>
       <c r="B62" t="n">
         <v>79081</v>
@@ -6811,10 +6811,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>419782</v>
+        <v>419835</v>
       </c>
       <c r="R62" t="n">
-        <v>6787403</v>
+        <v>6787789</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6873,7 +6873,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129357058</v>
+        <v>129367628</v>
       </c>
       <c r="B63" t="n">
         <v>79081</v>
@@ -6904,17 +6904,17 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>419892</v>
+        <v>419795</v>
       </c>
       <c r="R63" t="n">
-        <v>6787687</v>
+        <v>6787387</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6958,19 +6958,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129357053</v>
+        <v>129357069</v>
       </c>
       <c r="B64" t="n">
         <v>79081</v>
@@ -7005,10 +7005,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>419835</v>
+        <v>419782</v>
       </c>
       <c r="R64" t="n">
-        <v>6787789</v>
+        <v>6787403</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7746,10 +7746,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129367601</v>
+        <v>129357052</v>
       </c>
       <c r="B72" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7757,37 +7757,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>419818</v>
+        <v>419810</v>
       </c>
       <c r="R72" t="n">
-        <v>6787250</v>
+        <v>6787834</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7831,22 +7831,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129357052</v>
+        <v>129367601</v>
       </c>
       <c r="B73" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7854,37 +7854,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>419810</v>
+        <v>419818</v>
       </c>
       <c r="R73" t="n">
-        <v>6787834</v>
+        <v>6787250</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7928,22 +7928,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129367617</v>
+        <v>129367641</v>
       </c>
       <c r="B74" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7951,21 +7951,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7975,10 +7975,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>419617</v>
+        <v>419590</v>
       </c>
       <c r="R74" t="n">
-        <v>6787770</v>
+        <v>6787769</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8037,10 +8037,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129364502</v>
+        <v>129367639</v>
       </c>
       <c r="B75" t="n">
-        <v>78089</v>
+        <v>79081</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8048,37 +8048,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>419821</v>
+        <v>419672</v>
       </c>
       <c r="R75" t="n">
-        <v>6787289</v>
+        <v>6787734</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8122,19 +8122,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129367641</v>
+        <v>129367626</v>
       </c>
       <c r="B76" t="n">
         <v>79081</v>
@@ -8169,10 +8169,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>419590</v>
+        <v>419797</v>
       </c>
       <c r="R76" t="n">
-        <v>6787769</v>
+        <v>6787364</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8231,10 +8231,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129367639</v>
+        <v>129367599</v>
       </c>
       <c r="B77" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8242,21 +8242,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>419672</v>
+        <v>419693</v>
       </c>
       <c r="R77" t="n">
-        <v>6787734</v>
+        <v>6787442</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8328,10 +8328,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129367626</v>
+        <v>129364502</v>
       </c>
       <c r="B78" t="n">
-        <v>79081</v>
+        <v>78089</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8339,37 +8339,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>419797</v>
+        <v>419821</v>
       </c>
       <c r="R78" t="n">
-        <v>6787364</v>
+        <v>6787289</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8413,22 +8413,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129367599</v>
+        <v>129367617</v>
       </c>
       <c r="B79" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8436,21 +8436,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8460,10 +8460,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>419693</v>
+        <v>419617</v>
       </c>
       <c r="R79" t="n">
-        <v>6787442</v>
+        <v>6787770</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8515,7 +8515,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8813,7 +8813,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129367598</v>
+        <v>129357036</v>
       </c>
       <c r="B83" t="n">
         <v>79700</v>
@@ -8844,17 +8844,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>419671</v>
+        <v>419822</v>
       </c>
       <c r="R83" t="n">
-        <v>6787459</v>
+        <v>6787802</v>
       </c>
       <c r="S83" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8898,22 +8898,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129357036</v>
+        <v>129367645</v>
       </c>
       <c r="B84" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8921,37 +8921,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>419822</v>
+        <v>419775</v>
       </c>
       <c r="R84" t="n">
-        <v>6787802</v>
+        <v>6787376</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8995,19 +8995,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129367627</v>
+        <v>129357050</v>
       </c>
       <c r="B85" t="n">
         <v>79081</v>
@@ -9038,17 +9038,17 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>419795</v>
+        <v>419683</v>
       </c>
       <c r="R85" t="n">
-        <v>6787371</v>
+        <v>6787695</v>
       </c>
       <c r="S85" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9092,22 +9092,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129357039</v>
+        <v>129367627</v>
       </c>
       <c r="B86" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9115,49 +9115,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>419783</v>
+        <v>419795</v>
       </c>
       <c r="R86" t="n">
-        <v>6787400</v>
+        <v>6787371</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9201,22 +9189,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129367645</v>
+        <v>129367598</v>
       </c>
       <c r="B87" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9224,21 +9212,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9248,10 +9236,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>419775</v>
+        <v>419671</v>
       </c>
       <c r="R87" t="n">
-        <v>6787376</v>
+        <v>6787459</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9310,7 +9298,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129357050</v>
+        <v>129357088</v>
       </c>
       <c r="B88" t="n">
         <v>79081</v>
@@ -9345,10 +9333,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>419683</v>
+        <v>419827</v>
       </c>
       <c r="R88" t="n">
-        <v>6787695</v>
+        <v>6787267</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9407,10 +9395,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129357088</v>
+        <v>129367605</v>
       </c>
       <c r="B89" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9418,37 +9406,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>419827</v>
+        <v>419682</v>
       </c>
       <c r="R89" t="n">
-        <v>6787267</v>
+        <v>6787451</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9492,22 +9480,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129367600</v>
+        <v>129367606</v>
       </c>
       <c r="B90" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9515,21 +9503,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9539,10 +9527,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>419801</v>
+        <v>419820</v>
       </c>
       <c r="R90" t="n">
-        <v>6787284</v>
+        <v>6787294</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -9594,17 +9582,17 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129367605</v>
+        <v>129357039</v>
       </c>
       <c r="B91" t="n">
-        <v>79671</v>
+        <v>57733</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9612,37 +9600,49 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>419682</v>
+        <v>419783</v>
       </c>
       <c r="R91" t="n">
-        <v>6787451</v>
+        <v>6787400</v>
       </c>
       <c r="S91" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9686,22 +9686,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129367606</v>
+        <v>129367600</v>
       </c>
       <c r="B92" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9709,21 +9709,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9733,10 +9733,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>419820</v>
+        <v>419801</v>
       </c>
       <c r="R92" t="n">
-        <v>6787294</v>
+        <v>6787284</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -9788,14 +9788,14 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129357073</v>
+        <v>129367631</v>
       </c>
       <c r="B93" t="n">
         <v>79081</v>
@@ -9826,17 +9826,17 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>419806</v>
+        <v>419777</v>
       </c>
       <c r="R93" t="n">
-        <v>6787347</v>
+        <v>6787409</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9880,19 +9880,19 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129357079</v>
+        <v>129357073</v>
       </c>
       <c r="B94" t="n">
         <v>79081</v>
@@ -9927,10 +9927,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>419814</v>
+        <v>419806</v>
       </c>
       <c r="R94" t="n">
-        <v>6787354</v>
+        <v>6787347</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9989,10 +9989,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129364482</v>
+        <v>129357079</v>
       </c>
       <c r="B95" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10000,21 +10000,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10024,10 +10024,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>419803</v>
+        <v>419814</v>
       </c>
       <c r="R95" t="n">
-        <v>6787361</v>
+        <v>6787354</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10074,22 +10074,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129367647</v>
+        <v>129364482</v>
       </c>
       <c r="B96" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10097,37 +10097,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>419817</v>
+        <v>419803</v>
       </c>
       <c r="R96" t="n">
-        <v>6787255</v>
+        <v>6787361</v>
       </c>
       <c r="S96" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10171,19 +10171,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129357056</v>
+        <v>129367647</v>
       </c>
       <c r="B97" t="n">
         <v>79081</v>
@@ -10214,17 +10214,17 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>419863</v>
+        <v>419817</v>
       </c>
       <c r="R97" t="n">
-        <v>6787786</v>
+        <v>6787255</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10268,22 +10268,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129364480</v>
+        <v>129357056</v>
       </c>
       <c r="B98" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10291,21 +10291,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10315,10 +10315,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>419678</v>
+        <v>419863</v>
       </c>
       <c r="R98" t="n">
-        <v>6787641</v>
+        <v>6787786</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10365,22 +10365,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129367631</v>
+        <v>129364480</v>
       </c>
       <c r="B99" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10388,37 +10388,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>419777</v>
+        <v>419678</v>
       </c>
       <c r="R99" t="n">
-        <v>6787409</v>
+        <v>6787641</v>
       </c>
       <c r="S99" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10462,44 +10462,44 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129364498</v>
+        <v>129357076</v>
       </c>
       <c r="B100" t="n">
-        <v>92875</v>
+        <v>79081</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10509,10 +10509,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>419705</v>
+        <v>419818</v>
       </c>
       <c r="R100" t="n">
-        <v>6787663</v>
+        <v>6787293</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10559,44 +10559,44 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129357076</v>
+        <v>129364498</v>
       </c>
       <c r="B101" t="n">
-        <v>79081</v>
+        <v>92875</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10606,10 +10606,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>419818</v>
+        <v>419705</v>
       </c>
       <c r="R101" t="n">
-        <v>6787293</v>
+        <v>6787663</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10656,12 +10656,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -10758,7 +10758,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -10959,7 +10959,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129367644</v>
+        <v>129364488</v>
       </c>
       <c r="B105" t="n">
         <v>79081</v>
@@ -10990,17 +10990,17 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>419667</v>
+        <v>419829</v>
       </c>
       <c r="R105" t="n">
-        <v>6787466</v>
+        <v>6787260</v>
       </c>
       <c r="S105" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11044,19 +11044,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129364488</v>
+        <v>129357057</v>
       </c>
       <c r="B106" t="n">
         <v>79081</v>
@@ -11091,10 +11091,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>419829</v>
+        <v>419865</v>
       </c>
       <c r="R106" t="n">
-        <v>6787260</v>
+        <v>6787760</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11141,19 +11141,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129357057</v>
+        <v>129357061</v>
       </c>
       <c r="B107" t="n">
         <v>79081</v>
@@ -11188,10 +11188,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>419865</v>
+        <v>419929</v>
       </c>
       <c r="R107" t="n">
-        <v>6787760</v>
+        <v>6787653</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11250,7 +11250,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129357061</v>
+        <v>129367644</v>
       </c>
       <c r="B108" t="n">
         <v>79081</v>
@@ -11281,17 +11281,17 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>419929</v>
+        <v>419667</v>
       </c>
       <c r="R108" t="n">
-        <v>6787653</v>
+        <v>6787466</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11335,60 +11335,69 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129367638</v>
+        <v>129364478</v>
       </c>
       <c r="B109" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>419681</v>
+        <v>419796</v>
       </c>
       <c r="R109" t="n">
-        <v>6787728</v>
+        <v>6787321</v>
       </c>
       <c r="S109" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11426,25 +11435,26 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129357054</v>
+        <v>129367638</v>
       </c>
       <c r="B110" t="n">
         <v>79081</v>
@@ -11475,17 +11485,17 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>419849</v>
+        <v>419681</v>
       </c>
       <c r="R110" t="n">
-        <v>6787800</v>
+        <v>6787728</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11529,19 +11539,19 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129367637</v>
+        <v>129357054</v>
       </c>
       <c r="B111" t="n">
         <v>79081</v>
@@ -11572,17 +11582,17 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>419724</v>
+        <v>419849</v>
       </c>
       <c r="R111" t="n">
-        <v>6787653</v>
+        <v>6787800</v>
       </c>
       <c r="S111" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11626,66 +11636,57 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129364478</v>
+        <v>129357070</v>
       </c>
       <c r="B112" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>419796</v>
+        <v>419795</v>
       </c>
       <c r="R112" t="n">
-        <v>6787321</v>
+        <v>6787392</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11726,26 +11727,25 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129357070</v>
+        <v>129357085</v>
       </c>
       <c r="B113" t="n">
         <v>79081</v>
@@ -11780,10 +11780,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>419795</v>
+        <v>419821</v>
       </c>
       <c r="R113" t="n">
-        <v>6787392</v>
+        <v>6787310</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11842,7 +11842,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129357085</v>
+        <v>129367637</v>
       </c>
       <c r="B114" t="n">
         <v>79081</v>
@@ -11873,17 +11873,17 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>419821</v>
+        <v>419724</v>
       </c>
       <c r="R114" t="n">
-        <v>6787310</v>
+        <v>6787653</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11927,12 +11927,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -12230,10 +12230,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129357062</v>
+        <v>129364466</v>
       </c>
       <c r="B118" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12241,21 +12241,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12265,10 +12265,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>419682</v>
+        <v>419796</v>
       </c>
       <c r="R118" t="n">
-        <v>6787459</v>
+        <v>6787321</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12315,22 +12315,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129364468</v>
+        <v>129357062</v>
       </c>
       <c r="B119" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12338,21 +12338,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12362,10 +12362,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>419802</v>
+        <v>419682</v>
       </c>
       <c r="R119" t="n">
-        <v>6787354</v>
+        <v>6787459</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12412,19 +12412,19 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129364466</v>
+        <v>129364468</v>
       </c>
       <c r="B120" t="n">
         <v>79700</v>
@@ -12459,10 +12459,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>419796</v>
+        <v>419802</v>
       </c>
       <c r="R120" t="n">
-        <v>6787321</v>
+        <v>6787354</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12521,10 +12521,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129357049</v>
+        <v>129357037</v>
       </c>
       <c r="B121" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12532,21 +12532,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12556,10 +12556,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>419707</v>
+        <v>419822</v>
       </c>
       <c r="R121" t="n">
-        <v>6787641</v>
+        <v>6787799</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12618,7 +12618,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129364487</v>
+        <v>129357049</v>
       </c>
       <c r="B122" t="n">
         <v>79081</v>
@@ -12653,10 +12653,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>419795</v>
+        <v>419707</v>
       </c>
       <c r="R122" t="n">
-        <v>6787306</v>
+        <v>6787641</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12703,19 +12703,19 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129367640</v>
+        <v>129364487</v>
       </c>
       <c r="B123" t="n">
         <v>79081</v>
@@ -12746,17 +12746,17 @@
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>419596</v>
+        <v>419795</v>
       </c>
       <c r="R123" t="n">
-        <v>6787765</v>
+        <v>6787306</v>
       </c>
       <c r="S123" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -12800,22 +12800,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129357043</v>
+        <v>129367640</v>
       </c>
       <c r="B124" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12823,37 +12823,37 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>419806</v>
+        <v>419596</v>
       </c>
       <c r="R124" t="n">
-        <v>6787355</v>
+        <v>6787765</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -12897,22 +12897,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129357068</v>
+        <v>129357043</v>
       </c>
       <c r="B125" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12920,21 +12920,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12944,10 +12944,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>419749</v>
+        <v>419806</v>
       </c>
       <c r="R125" t="n">
-        <v>6787397</v>
+        <v>6787355</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13006,10 +13006,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129357037</v>
+        <v>129357068</v>
       </c>
       <c r="B126" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13017,21 +13017,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13041,10 +13041,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>419822</v>
+        <v>419749</v>
       </c>
       <c r="R126" t="n">
-        <v>6787799</v>
+        <v>6787397</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13103,7 +13103,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129367634</v>
+        <v>129367625</v>
       </c>
       <c r="B127" t="n">
         <v>79081</v>
@@ -13138,10 +13138,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>419740</v>
+        <v>419800</v>
       </c>
       <c r="R127" t="n">
-        <v>6787429</v>
+        <v>6787361</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -13200,7 +13200,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129367625</v>
+        <v>129357074</v>
       </c>
       <c r="B128" t="n">
         <v>79081</v>
@@ -13231,17 +13231,17 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>419800</v>
+        <v>419796</v>
       </c>
       <c r="R128" t="n">
-        <v>6787361</v>
+        <v>6787322</v>
       </c>
       <c r="S128" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13285,19 +13285,19 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129357074</v>
+        <v>129357055</v>
       </c>
       <c r="B129" t="n">
         <v>79081</v>
@@ -13332,10 +13332,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>419796</v>
+        <v>419856</v>
       </c>
       <c r="R129" t="n">
-        <v>6787322</v>
+        <v>6787798</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13394,7 +13394,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129357055</v>
+        <v>129367634</v>
       </c>
       <c r="B130" t="n">
         <v>79081</v>
@@ -13425,17 +13425,17 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>419856</v>
+        <v>419740</v>
       </c>
       <c r="R130" t="n">
-        <v>6787798</v>
+        <v>6787429</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13479,12 +13479,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
@@ -13590,7 +13590,7 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>

--- a/artfynd/A 46306-2025 artfynd.xlsx
+++ b/artfynd/A 46306-2025 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129351453</v>
+        <v>129351428</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,7 +927,7 @@
         <v>419742</v>
       </c>
       <c r="R4" t="n">
-        <v>6787381</v>
+        <v>6787389</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129351428</v>
+        <v>129351453</v>
       </c>
       <c r="B5" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1034,7 +1034,7 @@
         <v>419742</v>
       </c>
       <c r="R5" t="n">
-        <v>6787389</v>
+        <v>6787381</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129351479</v>
+        <v>129351436</v>
       </c>
       <c r="B15" t="n">
-        <v>78747</v>
+        <v>78838</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>419670</v>
+        <v>419772</v>
       </c>
       <c r="R15" t="n">
-        <v>6787628</v>
+        <v>6787332</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129351441</v>
+        <v>129351479</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>78747</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>419804</v>
+        <v>419670</v>
       </c>
       <c r="R16" t="n">
-        <v>6787364</v>
+        <v>6787628</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129351436</v>
+        <v>129351441</v>
       </c>
       <c r="B17" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>419772</v>
+        <v>419804</v>
       </c>
       <c r="R17" t="n">
-        <v>6787332</v>
+        <v>6787364</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129351431</v>
+        <v>129351480</v>
       </c>
       <c r="B21" t="n">
-        <v>79671</v>
+        <v>78747</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>419608</v>
+        <v>419635</v>
       </c>
       <c r="R21" t="n">
-        <v>6787699</v>
+        <v>6787627</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129351480</v>
+        <v>129351431</v>
       </c>
       <c r="B22" t="n">
-        <v>78747</v>
+        <v>79671</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,21 +2826,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>419635</v>
+        <v>419608</v>
       </c>
       <c r="R22" t="n">
-        <v>6787627</v>
+        <v>6787699</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3243,10 +3243,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129351442</v>
+        <v>129351427</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3254,21 +3254,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>419761</v>
+        <v>419606</v>
       </c>
       <c r="R26" t="n">
-        <v>6787419</v>
+        <v>6787701</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129351427</v>
+        <v>129351442</v>
       </c>
       <c r="B27" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3361,21 +3361,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>419606</v>
+        <v>419761</v>
       </c>
       <c r="R27" t="n">
-        <v>6787701</v>
+        <v>6787419</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,10 +3457,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129367646</v>
+        <v>129357130</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>78089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3468,37 +3468,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>419784</v>
+        <v>419740</v>
       </c>
       <c r="R28" t="n">
-        <v>6787357</v>
+        <v>6787448</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3542,22 +3542,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129357130</v>
+        <v>129367646</v>
       </c>
       <c r="B29" t="n">
-        <v>78089</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3565,37 +3565,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>419740</v>
+        <v>419784</v>
       </c>
       <c r="R29" t="n">
-        <v>6787448</v>
+        <v>6787357</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3639,69 +3639,60 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129364476</v>
+        <v>129367642</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>419720</v>
+        <v>419675</v>
       </c>
       <c r="R30" t="n">
-        <v>6787656</v>
+        <v>6787516</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3739,26 +3730,25 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129367642</v>
+        <v>129367643</v>
       </c>
       <c r="B31" t="n">
         <v>79081</v>
@@ -3793,10 +3783,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>419675</v>
+        <v>419668</v>
       </c>
       <c r="R31" t="n">
-        <v>6787516</v>
+        <v>6787515</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3855,7 +3845,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129367643</v>
+        <v>129357064</v>
       </c>
       <c r="B32" t="n">
         <v>79081</v>
@@ -3886,17 +3876,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>419668</v>
+        <v>419697</v>
       </c>
       <c r="R32" t="n">
-        <v>6787515</v>
+        <v>6787431</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3940,19 +3930,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129357064</v>
+        <v>129357082</v>
       </c>
       <c r="B33" t="n">
         <v>79081</v>
@@ -3987,10 +3977,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>419697</v>
+        <v>419807</v>
       </c>
       <c r="R33" t="n">
-        <v>6787431</v>
+        <v>6787361</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4049,45 +4039,54 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129357082</v>
+        <v>129364476</v>
       </c>
       <c r="B34" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>419807</v>
+        <v>419720</v>
       </c>
       <c r="R34" t="n">
-        <v>6787361</v>
+        <v>6787656</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4128,28 +4127,29 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129367618</v>
+        <v>129357051</v>
       </c>
       <c r="B35" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4157,37 +4157,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>419635</v>
+        <v>419703</v>
       </c>
       <c r="R35" t="n">
-        <v>6787658</v>
+        <v>6787692</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4231,19 +4231,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129357051</v>
+        <v>129367648</v>
       </c>
       <c r="B36" t="n">
         <v>79081</v>
@@ -4274,17 +4274,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>419703</v>
+        <v>419821</v>
       </c>
       <c r="R36" t="n">
-        <v>6787692</v>
+        <v>6787260</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4328,22 +4328,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129364461</v>
+        <v>129367618</v>
       </c>
       <c r="B37" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4351,37 +4351,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>419639</v>
+        <v>419635</v>
       </c>
       <c r="R37" t="n">
-        <v>6787642</v>
+        <v>6787658</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4425,22 +4425,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129367648</v>
+        <v>129364461</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4448,37 +4448,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>419821</v>
+        <v>419639</v>
       </c>
       <c r="R38" t="n">
-        <v>6787260</v>
+        <v>6787642</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4522,44 +4522,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129357067</v>
+        <v>129364500</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>92875</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4569,10 +4569,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>419791</v>
+        <v>419672</v>
       </c>
       <c r="R39" t="n">
-        <v>6787358</v>
+        <v>6787747</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4619,19 +4619,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129357075</v>
+        <v>129357067</v>
       </c>
       <c r="B40" t="n">
         <v>79081</v>
@@ -4666,10 +4666,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>419809</v>
+        <v>419791</v>
       </c>
       <c r="R40" t="n">
-        <v>6787307</v>
+        <v>6787358</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4728,32 +4728,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129364500</v>
+        <v>129357075</v>
       </c>
       <c r="B41" t="n">
-        <v>92875</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4763,10 +4763,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>419672</v>
+        <v>419809</v>
       </c>
       <c r="R41" t="n">
-        <v>6787747</v>
+        <v>6787307</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4813,12 +4813,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4922,10 +4922,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129367602</v>
+        <v>129367649</v>
       </c>
       <c r="B43" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4933,21 +4933,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>419592</v>
+        <v>419830</v>
       </c>
       <c r="R43" t="n">
-        <v>6787771</v>
+        <v>6787264</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5019,7 +5019,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129367649</v>
+        <v>129357047</v>
       </c>
       <c r="B44" t="n">
         <v>79081</v>
@@ -5050,17 +5050,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>419830</v>
+        <v>419732</v>
       </c>
       <c r="R44" t="n">
-        <v>6787264</v>
+        <v>6787619</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5104,19 +5104,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129357047</v>
+        <v>129367650</v>
       </c>
       <c r="B45" t="n">
         <v>79081</v>
@@ -5147,17 +5147,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>419732</v>
+        <v>419833</v>
       </c>
       <c r="R45" t="n">
-        <v>6787619</v>
+        <v>6787235</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5201,19 +5201,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129367650</v>
+        <v>129367624</v>
       </c>
       <c r="B46" t="n">
         <v>79081</v>
@@ -5248,10 +5248,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>419833</v>
+        <v>419802</v>
       </c>
       <c r="R46" t="n">
-        <v>6787235</v>
+        <v>6787354</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5310,10 +5310,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129364462</v>
+        <v>129357122</v>
       </c>
       <c r="B47" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5321,21 +5321,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>419648</v>
+        <v>419905</v>
       </c>
       <c r="R47" t="n">
-        <v>6787500</v>
+        <v>6787672</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5389,25 +5389,26 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129367624</v>
+        <v>129357086</v>
       </c>
       <c r="B48" t="n">
         <v>79081</v>
@@ -5438,17 +5439,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>419802</v>
+        <v>419825</v>
       </c>
       <c r="R48" t="n">
-        <v>6787354</v>
+        <v>6787284</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5492,19 +5493,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129357122</v>
+        <v>129357083</v>
       </c>
       <c r="B49" t="n">
         <v>79081</v>
@@ -5539,10 +5540,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>419905</v>
+        <v>419799</v>
       </c>
       <c r="R49" t="n">
-        <v>6787672</v>
+        <v>6787352</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5583,7 +5584,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5602,7 +5602,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129357086</v>
+        <v>129367630</v>
       </c>
       <c r="B50" t="n">
         <v>79081</v>
@@ -5633,17 +5633,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>419825</v>
+        <v>419783</v>
       </c>
       <c r="R50" t="n">
-        <v>6787284</v>
+        <v>6787407</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5687,22 +5687,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129357083</v>
+        <v>129367602</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5710,37 +5710,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>419799</v>
+        <v>419592</v>
       </c>
       <c r="R51" t="n">
-        <v>6787352</v>
+        <v>6787771</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5784,22 +5784,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129367630</v>
+        <v>129364462</v>
       </c>
       <c r="B52" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5807,37 +5807,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>419783</v>
+        <v>419648</v>
       </c>
       <c r="R52" t="n">
-        <v>6787407</v>
+        <v>6787500</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5881,22 +5881,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129367635</v>
+        <v>129364464</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5904,37 +5904,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>419731</v>
+        <v>419679</v>
       </c>
       <c r="R53" t="n">
-        <v>6787436</v>
+        <v>6787475</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5978,19 +5978,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129364464</v>
+        <v>129367603</v>
       </c>
       <c r="B54" t="n">
         <v>79700</v>
@@ -6021,17 +6021,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>419679</v>
+        <v>419817</v>
       </c>
       <c r="R54" t="n">
-        <v>6787475</v>
+        <v>6787314</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6075,19 +6075,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129357078</v>
+        <v>129367635</v>
       </c>
       <c r="B55" t="n">
         <v>79081</v>
@@ -6118,17 +6118,17 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>419813</v>
+        <v>419731</v>
       </c>
       <c r="R55" t="n">
-        <v>6787347</v>
+        <v>6787436</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6172,19 +6172,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129367629</v>
+        <v>129357078</v>
       </c>
       <c r="B56" t="n">
         <v>79081</v>
@@ -6215,17 +6215,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>419786</v>
+        <v>419813</v>
       </c>
       <c r="R56" t="n">
-        <v>6787405</v>
+        <v>6787347</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6269,19 +6269,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129357077</v>
+        <v>129367629</v>
       </c>
       <c r="B57" t="n">
         <v>79081</v>
@@ -6312,17 +6312,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>419815</v>
+        <v>419786</v>
       </c>
       <c r="R57" t="n">
-        <v>6787331</v>
+        <v>6787405</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6366,19 +6366,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129357089</v>
+        <v>129357077</v>
       </c>
       <c r="B58" t="n">
         <v>79081</v>
@@ -6413,10 +6413,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>419843</v>
+        <v>419815</v>
       </c>
       <c r="R58" t="n">
-        <v>6787218</v>
+        <v>6787331</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6475,10 +6475,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129367603</v>
+        <v>129357089</v>
       </c>
       <c r="B59" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6486,37 +6486,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>419817</v>
+        <v>419843</v>
       </c>
       <c r="R59" t="n">
-        <v>6787314</v>
+        <v>6787218</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6560,66 +6560,57 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129357042</v>
+        <v>129357058</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>419822</v>
+        <v>419892</v>
       </c>
       <c r="R60" t="n">
-        <v>6787322</v>
+        <v>6787687</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6660,7 +6651,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6679,7 +6669,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129357058</v>
+        <v>129357053</v>
       </c>
       <c r="B61" t="n">
         <v>79081</v>
@@ -6714,10 +6704,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>419892</v>
+        <v>419835</v>
       </c>
       <c r="R61" t="n">
-        <v>6787687</v>
+        <v>6787789</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6776,7 +6766,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129357053</v>
+        <v>129367628</v>
       </c>
       <c r="B62" t="n">
         <v>79081</v>
@@ -6807,17 +6797,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>419835</v>
+        <v>419795</v>
       </c>
       <c r="R62" t="n">
-        <v>6787789</v>
+        <v>6787387</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6861,19 +6851,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129367628</v>
+        <v>129357069</v>
       </c>
       <c r="B63" t="n">
         <v>79081</v>
@@ -6904,17 +6894,17 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>419795</v>
+        <v>419782</v>
       </c>
       <c r="R63" t="n">
-        <v>6787387</v>
+        <v>6787403</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6958,19 +6948,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129357069</v>
+        <v>129357065</v>
       </c>
       <c r="B64" t="n">
         <v>79081</v>
@@ -7005,10 +6995,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>419782</v>
+        <v>419776</v>
       </c>
       <c r="R64" t="n">
-        <v>6787403</v>
+        <v>6787371</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7067,7 +7057,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129357065</v>
+        <v>129364485</v>
       </c>
       <c r="B65" t="n">
         <v>79081</v>
@@ -7102,10 +7092,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>419776</v>
+        <v>419678</v>
       </c>
       <c r="R65" t="n">
-        <v>6787371</v>
+        <v>6787476</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7152,57 +7142,66 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129364485</v>
+        <v>129357042</v>
       </c>
       <c r="B66" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>419678</v>
+        <v>419822</v>
       </c>
       <c r="R66" t="n">
-        <v>6787476</v>
+        <v>6787322</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7243,18 +7242,19 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7649,10 +7649,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129357060</v>
+        <v>129367601</v>
       </c>
       <c r="B71" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7660,37 +7660,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>419924</v>
+        <v>419818</v>
       </c>
       <c r="R71" t="n">
-        <v>6787672</v>
+        <v>6787250</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7734,19 +7734,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129357052</v>
+        <v>129357060</v>
       </c>
       <c r="B72" t="n">
         <v>79081</v>
@@ -7781,10 +7781,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>419810</v>
+        <v>419924</v>
       </c>
       <c r="R72" t="n">
-        <v>6787834</v>
+        <v>6787672</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7843,10 +7843,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129367601</v>
+        <v>129357052</v>
       </c>
       <c r="B73" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7854,37 +7854,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>419818</v>
+        <v>419810</v>
       </c>
       <c r="R73" t="n">
-        <v>6787250</v>
+        <v>6787834</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7928,22 +7928,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129367641</v>
+        <v>129364502</v>
       </c>
       <c r="B74" t="n">
-        <v>79081</v>
+        <v>78089</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7951,37 +7951,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>419590</v>
+        <v>419821</v>
       </c>
       <c r="R74" t="n">
-        <v>6787769</v>
+        <v>6787289</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8025,22 +8025,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129367639</v>
+        <v>129367617</v>
       </c>
       <c r="B75" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8048,21 +8048,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8072,10 +8072,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>419672</v>
+        <v>419617</v>
       </c>
       <c r="R75" t="n">
-        <v>6787734</v>
+        <v>6787770</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8134,10 +8134,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129367626</v>
+        <v>129367599</v>
       </c>
       <c r="B76" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8145,21 +8145,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8169,10 +8169,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>419797</v>
+        <v>419693</v>
       </c>
       <c r="R76" t="n">
-        <v>6787364</v>
+        <v>6787442</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8231,10 +8231,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129367599</v>
+        <v>129367641</v>
       </c>
       <c r="B77" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8242,21 +8242,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>419693</v>
+        <v>419590</v>
       </c>
       <c r="R77" t="n">
-        <v>6787442</v>
+        <v>6787769</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8328,10 +8328,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129364502</v>
+        <v>129367639</v>
       </c>
       <c r="B78" t="n">
-        <v>78089</v>
+        <v>79081</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8339,37 +8339,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>419821</v>
+        <v>419672</v>
       </c>
       <c r="R78" t="n">
-        <v>6787289</v>
+        <v>6787734</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8413,22 +8413,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129367617</v>
+        <v>129367626</v>
       </c>
       <c r="B79" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8436,21 +8436,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8460,10 +8460,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>419617</v>
+        <v>419797</v>
       </c>
       <c r="R79" t="n">
-        <v>6787770</v>
+        <v>6787364</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8910,10 +8910,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129367645</v>
+        <v>129367598</v>
       </c>
       <c r="B84" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8921,21 +8921,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8945,10 +8945,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>419775</v>
+        <v>419671</v>
       </c>
       <c r="R84" t="n">
-        <v>6787376</v>
+        <v>6787459</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9007,10 +9007,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129357050</v>
+        <v>129367600</v>
       </c>
       <c r="B85" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9018,37 +9018,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>419683</v>
+        <v>419801</v>
       </c>
       <c r="R85" t="n">
-        <v>6787695</v>
+        <v>6787284</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9092,19 +9092,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129367627</v>
+        <v>129367645</v>
       </c>
       <c r="B86" t="n">
         <v>79081</v>
@@ -9139,10 +9139,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>419795</v>
+        <v>419775</v>
       </c>
       <c r="R86" t="n">
-        <v>6787371</v>
+        <v>6787376</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9201,10 +9201,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129367598</v>
+        <v>129357050</v>
       </c>
       <c r="B87" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9212,37 +9212,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>419671</v>
+        <v>419683</v>
       </c>
       <c r="R87" t="n">
-        <v>6787459</v>
+        <v>6787695</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9286,19 +9286,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129357088</v>
+        <v>129367627</v>
       </c>
       <c r="B88" t="n">
         <v>79081</v>
@@ -9329,17 +9329,17 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>419827</v>
+        <v>419795</v>
       </c>
       <c r="R88" t="n">
-        <v>6787267</v>
+        <v>6787371</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9383,22 +9383,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129367605</v>
+        <v>129357088</v>
       </c>
       <c r="B89" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9406,37 +9406,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>419682</v>
+        <v>419827</v>
       </c>
       <c r="R89" t="n">
-        <v>6787451</v>
+        <v>6787267</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9480,22 +9480,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129367606</v>
+        <v>129357039</v>
       </c>
       <c r="B90" t="n">
-        <v>79671</v>
+        <v>57733</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9503,37 +9503,49 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>419820</v>
+        <v>419783</v>
       </c>
       <c r="R90" t="n">
-        <v>6787294</v>
+        <v>6787400</v>
       </c>
       <c r="S90" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9577,22 +9589,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129357039</v>
+        <v>129367605</v>
       </c>
       <c r="B91" t="n">
-        <v>57733</v>
+        <v>79671</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9600,49 +9612,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>419783</v>
+        <v>419682</v>
       </c>
       <c r="R91" t="n">
-        <v>6787400</v>
+        <v>6787451</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9686,22 +9686,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129367600</v>
+        <v>129367606</v>
       </c>
       <c r="B92" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9709,21 +9709,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9733,10 +9733,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>419801</v>
+        <v>419820</v>
       </c>
       <c r="R92" t="n">
-        <v>6787284</v>
+        <v>6787294</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -9795,10 +9795,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129367631</v>
+        <v>129364482</v>
       </c>
       <c r="B93" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9806,37 +9806,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>419777</v>
+        <v>419803</v>
       </c>
       <c r="R93" t="n">
-        <v>6787409</v>
+        <v>6787361</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9880,22 +9880,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129357073</v>
+        <v>129364480</v>
       </c>
       <c r="B94" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9903,21 +9903,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9927,10 +9927,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>419806</v>
+        <v>419678</v>
       </c>
       <c r="R94" t="n">
-        <v>6787347</v>
+        <v>6787641</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9977,19 +9977,19 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129357079</v>
+        <v>129367631</v>
       </c>
       <c r="B95" t="n">
         <v>79081</v>
@@ -10020,17 +10020,17 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>419814</v>
+        <v>419777</v>
       </c>
       <c r="R95" t="n">
-        <v>6787354</v>
+        <v>6787409</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10074,22 +10074,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129364482</v>
+        <v>129357073</v>
       </c>
       <c r="B96" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10097,21 +10097,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10121,10 +10121,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>419803</v>
+        <v>419806</v>
       </c>
       <c r="R96" t="n">
-        <v>6787361</v>
+        <v>6787347</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10171,19 +10171,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129367647</v>
+        <v>129357079</v>
       </c>
       <c r="B97" t="n">
         <v>79081</v>
@@ -10214,17 +10214,17 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>419817</v>
+        <v>419814</v>
       </c>
       <c r="R97" t="n">
-        <v>6787255</v>
+        <v>6787354</v>
       </c>
       <c r="S97" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10268,19 +10268,19 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129357056</v>
+        <v>129367647</v>
       </c>
       <c r="B98" t="n">
         <v>79081</v>
@@ -10311,17 +10311,17 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>419863</v>
+        <v>419817</v>
       </c>
       <c r="R98" t="n">
-        <v>6787786</v>
+        <v>6787255</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10365,22 +10365,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129364480</v>
+        <v>129357056</v>
       </c>
       <c r="B99" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10388,21 +10388,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10412,10 +10412,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>419678</v>
+        <v>419863</v>
       </c>
       <c r="R99" t="n">
-        <v>6787641</v>
+        <v>6787786</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10462,12 +10462,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -10668,10 +10668,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129367659</v>
+        <v>129357044</v>
       </c>
       <c r="B102" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10679,37 +10679,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>419692</v>
+        <v>419817</v>
       </c>
       <c r="R102" t="n">
-        <v>6787475</v>
+        <v>6787353</v>
       </c>
       <c r="S102" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10753,22 +10753,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129357044</v>
+        <v>129367659</v>
       </c>
       <c r="B103" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10776,37 +10776,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>419817</v>
+        <v>419692</v>
       </c>
       <c r="R103" t="n">
-        <v>6787353</v>
+        <v>6787475</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10850,12 +10850,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -11347,57 +11347,48 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129364478</v>
+        <v>129367638</v>
       </c>
       <c r="B109" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>419796</v>
+        <v>419681</v>
       </c>
       <c r="R109" t="n">
-        <v>6787321</v>
+        <v>6787728</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11435,26 +11426,25 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129367638</v>
+        <v>129357054</v>
       </c>
       <c r="B110" t="n">
         <v>79081</v>
@@ -11485,17 +11475,17 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>419681</v>
+        <v>419849</v>
       </c>
       <c r="R110" t="n">
-        <v>6787728</v>
+        <v>6787800</v>
       </c>
       <c r="S110" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11539,19 +11529,19 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129357054</v>
+        <v>129357085</v>
       </c>
       <c r="B111" t="n">
         <v>79081</v>
@@ -11586,10 +11576,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>419849</v>
+        <v>419821</v>
       </c>
       <c r="R111" t="n">
-        <v>6787800</v>
+        <v>6787310</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11648,7 +11638,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129357070</v>
+        <v>129367637</v>
       </c>
       <c r="B112" t="n">
         <v>79081</v>
@@ -11679,17 +11669,17 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>419795</v>
+        <v>419724</v>
       </c>
       <c r="R112" t="n">
-        <v>6787392</v>
+        <v>6787653</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11733,19 +11723,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129357085</v>
+        <v>129357072</v>
       </c>
       <c r="B113" t="n">
         <v>79081</v>
@@ -11780,10 +11770,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>419821</v>
+        <v>419808</v>
       </c>
       <c r="R113" t="n">
-        <v>6787310</v>
+        <v>6787365</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11842,7 +11832,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129367637</v>
+        <v>129357063</v>
       </c>
       <c r="B114" t="n">
         <v>79081</v>
@@ -11873,17 +11863,17 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>419724</v>
+        <v>419686</v>
       </c>
       <c r="R114" t="n">
-        <v>6787653</v>
+        <v>6787449</v>
       </c>
       <c r="S114" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11927,19 +11917,19 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129357072</v>
+        <v>129357070</v>
       </c>
       <c r="B115" t="n">
         <v>79081</v>
@@ -11974,10 +11964,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>419808</v>
+        <v>419795</v>
       </c>
       <c r="R115" t="n">
-        <v>6787365</v>
+        <v>6787392</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12036,45 +12026,54 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129357063</v>
+        <v>129364478</v>
       </c>
       <c r="B116" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>419686</v>
+        <v>419796</v>
       </c>
       <c r="R116" t="n">
-        <v>6787449</v>
+        <v>6787321</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12115,28 +12114,29 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129367633</v>
+        <v>129364468</v>
       </c>
       <c r="B117" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12144,37 +12144,37 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>419775</v>
+        <v>419802</v>
       </c>
       <c r="R117" t="n">
-        <v>6787415</v>
+        <v>6787354</v>
       </c>
       <c r="S117" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12218,12 +12218,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -12327,7 +12327,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129357062</v>
+        <v>129367633</v>
       </c>
       <c r="B119" t="n">
         <v>79081</v>
@@ -12358,17 +12358,17 @@
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>419682</v>
+        <v>419775</v>
       </c>
       <c r="R119" t="n">
-        <v>6787459</v>
+        <v>6787415</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12412,22 +12412,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129364468</v>
+        <v>129357062</v>
       </c>
       <c r="B120" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12435,21 +12435,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12459,10 +12459,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>419802</v>
+        <v>419682</v>
       </c>
       <c r="R120" t="n">
-        <v>6787354</v>
+        <v>6787459</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12509,22 +12509,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129357037</v>
+        <v>129357043</v>
       </c>
       <c r="B121" t="n">
-        <v>79671</v>
+        <v>78838</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12532,21 +12532,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12556,10 +12556,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>419822</v>
+        <v>419806</v>
       </c>
       <c r="R121" t="n">
-        <v>6787799</v>
+        <v>6787355</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12909,10 +12909,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129357043</v>
+        <v>129357068</v>
       </c>
       <c r="B125" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12920,21 +12920,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12944,10 +12944,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>419806</v>
+        <v>419749</v>
       </c>
       <c r="R125" t="n">
-        <v>6787355</v>
+        <v>6787397</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13006,10 +13006,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129357068</v>
+        <v>129357037</v>
       </c>
       <c r="B126" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13017,21 +13017,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13041,10 +13041,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>419749</v>
+        <v>419822</v>
       </c>
       <c r="R126" t="n">
-        <v>6787397</v>
+        <v>6787799</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>

--- a/artfynd/A 46306-2025 artfynd.xlsx
+++ b/artfynd/A 46306-2025 artfynd.xlsx
@@ -3457,10 +3457,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129357130</v>
+        <v>129367646</v>
       </c>
       <c r="B28" t="n">
-        <v>78089</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3468,37 +3468,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>419740</v>
+        <v>419784</v>
       </c>
       <c r="R28" t="n">
-        <v>6787448</v>
+        <v>6787357</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3542,22 +3542,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129367646</v>
+        <v>129357130</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>78089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3565,37 +3565,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>419784</v>
+        <v>419740</v>
       </c>
       <c r="R29" t="n">
-        <v>6787357</v>
+        <v>6787448</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3639,12 +3639,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3845,7 +3845,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129357064</v>
+        <v>129357082</v>
       </c>
       <c r="B32" t="n">
         <v>79081</v>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>419697</v>
+        <v>419807</v>
       </c>
       <c r="R32" t="n">
-        <v>6787431</v>
+        <v>6787361</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3942,7 +3942,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129357082</v>
+        <v>129357064</v>
       </c>
       <c r="B33" t="n">
         <v>79081</v>
@@ -3977,10 +3977,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>419807</v>
+        <v>419697</v>
       </c>
       <c r="R33" t="n">
-        <v>6787361</v>
+        <v>6787431</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4243,10 +4243,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129367648</v>
+        <v>129364461</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4254,37 +4254,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>419821</v>
+        <v>419639</v>
       </c>
       <c r="R36" t="n">
-        <v>6787260</v>
+        <v>6787642</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4328,22 +4328,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129367618</v>
+        <v>129367648</v>
       </c>
       <c r="B37" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4351,21 +4351,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4375,10 +4375,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>419635</v>
+        <v>419821</v>
       </c>
       <c r="R37" t="n">
-        <v>6787658</v>
+        <v>6787260</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4437,10 +4437,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129364461</v>
+        <v>129367618</v>
       </c>
       <c r="B38" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4448,37 +4448,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>419639</v>
+        <v>419635</v>
       </c>
       <c r="R38" t="n">
-        <v>6787642</v>
+        <v>6787658</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4522,12 +4522,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4922,10 +4922,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129367649</v>
+        <v>129367602</v>
       </c>
       <c r="B43" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4933,21 +4933,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>419830</v>
+        <v>419592</v>
       </c>
       <c r="R43" t="n">
-        <v>6787264</v>
+        <v>6787771</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5019,7 +5019,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129357047</v>
+        <v>129367649</v>
       </c>
       <c r="B44" t="n">
         <v>79081</v>
@@ -5050,17 +5050,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>419732</v>
+        <v>419830</v>
       </c>
       <c r="R44" t="n">
-        <v>6787619</v>
+        <v>6787264</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5104,19 +5104,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129367650</v>
+        <v>129357047</v>
       </c>
       <c r="B45" t="n">
         <v>79081</v>
@@ -5147,17 +5147,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>419833</v>
+        <v>419732</v>
       </c>
       <c r="R45" t="n">
-        <v>6787235</v>
+        <v>6787619</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5201,19 +5201,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129367624</v>
+        <v>129367650</v>
       </c>
       <c r="B46" t="n">
         <v>79081</v>
@@ -5248,10 +5248,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>419802</v>
+        <v>419833</v>
       </c>
       <c r="R46" t="n">
-        <v>6787354</v>
+        <v>6787235</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5310,10 +5310,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129357122</v>
+        <v>129364462</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5321,21 +5321,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>419905</v>
+        <v>419648</v>
       </c>
       <c r="R47" t="n">
-        <v>6787672</v>
+        <v>6787500</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5389,26 +5389,25 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129357086</v>
+        <v>129367624</v>
       </c>
       <c r="B48" t="n">
         <v>79081</v>
@@ -5439,17 +5438,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>419825</v>
+        <v>419802</v>
       </c>
       <c r="R48" t="n">
-        <v>6787284</v>
+        <v>6787354</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5493,19 +5492,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129357083</v>
+        <v>129357122</v>
       </c>
       <c r="B49" t="n">
         <v>79081</v>
@@ -5540,10 +5539,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>419799</v>
+        <v>419905</v>
       </c>
       <c r="R49" t="n">
-        <v>6787352</v>
+        <v>6787672</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5584,6 +5583,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5602,7 +5602,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129367630</v>
+        <v>129357086</v>
       </c>
       <c r="B50" t="n">
         <v>79081</v>
@@ -5633,17 +5633,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>419783</v>
+        <v>419825</v>
       </c>
       <c r="R50" t="n">
-        <v>6787407</v>
+        <v>6787284</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5687,22 +5687,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129367602</v>
+        <v>129357083</v>
       </c>
       <c r="B51" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5710,37 +5710,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>419592</v>
+        <v>419799</v>
       </c>
       <c r="R51" t="n">
-        <v>6787771</v>
+        <v>6787352</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5784,22 +5784,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129364462</v>
+        <v>129367630</v>
       </c>
       <c r="B52" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5807,37 +5807,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>419648</v>
+        <v>419783</v>
       </c>
       <c r="R52" t="n">
-        <v>6787500</v>
+        <v>6787407</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5881,22 +5881,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129364464</v>
+        <v>129367635</v>
       </c>
       <c r="B53" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5904,37 +5904,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>419679</v>
+        <v>419731</v>
       </c>
       <c r="R53" t="n">
-        <v>6787475</v>
+        <v>6787436</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5978,19 +5978,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129367603</v>
+        <v>129364464</v>
       </c>
       <c r="B54" t="n">
         <v>79700</v>
@@ -6021,17 +6021,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>419817</v>
+        <v>419679</v>
       </c>
       <c r="R54" t="n">
-        <v>6787314</v>
+        <v>6787475</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6075,19 +6075,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129367635</v>
+        <v>129357078</v>
       </c>
       <c r="B55" t="n">
         <v>79081</v>
@@ -6118,17 +6118,17 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>419731</v>
+        <v>419813</v>
       </c>
       <c r="R55" t="n">
-        <v>6787436</v>
+        <v>6787347</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6172,19 +6172,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129357078</v>
+        <v>129367629</v>
       </c>
       <c r="B56" t="n">
         <v>79081</v>
@@ -6215,17 +6215,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>419813</v>
+        <v>419786</v>
       </c>
       <c r="R56" t="n">
-        <v>6787347</v>
+        <v>6787405</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6269,19 +6269,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129367629</v>
+        <v>129357077</v>
       </c>
       <c r="B57" t="n">
         <v>79081</v>
@@ -6312,17 +6312,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>419786</v>
+        <v>419815</v>
       </c>
       <c r="R57" t="n">
-        <v>6787405</v>
+        <v>6787331</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6366,19 +6366,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129357077</v>
+        <v>129357089</v>
       </c>
       <c r="B58" t="n">
         <v>79081</v>
@@ -6413,10 +6413,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>419815</v>
+        <v>419843</v>
       </c>
       <c r="R58" t="n">
-        <v>6787331</v>
+        <v>6787218</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6475,10 +6475,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129357089</v>
+        <v>129367603</v>
       </c>
       <c r="B59" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6486,37 +6486,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>419843</v>
+        <v>419817</v>
       </c>
       <c r="R59" t="n">
-        <v>6787218</v>
+        <v>6787314</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6560,19 +6560,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129357058</v>
+        <v>129364485</v>
       </c>
       <c r="B60" t="n">
         <v>79081</v>
@@ -6607,10 +6607,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>419892</v>
+        <v>419678</v>
       </c>
       <c r="R60" t="n">
-        <v>6787687</v>
+        <v>6787476</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6657,19 +6657,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129357053</v>
+        <v>129357058</v>
       </c>
       <c r="B61" t="n">
         <v>79081</v>
@@ -6704,10 +6704,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>419835</v>
+        <v>419892</v>
       </c>
       <c r="R61" t="n">
-        <v>6787789</v>
+        <v>6787687</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6766,7 +6766,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129367628</v>
+        <v>129357053</v>
       </c>
       <c r="B62" t="n">
         <v>79081</v>
@@ -6797,17 +6797,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>419795</v>
+        <v>419835</v>
       </c>
       <c r="R62" t="n">
-        <v>6787387</v>
+        <v>6787789</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6851,19 +6851,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129357069</v>
+        <v>129367628</v>
       </c>
       <c r="B63" t="n">
         <v>79081</v>
@@ -6894,17 +6894,17 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>419782</v>
+        <v>419795</v>
       </c>
       <c r="R63" t="n">
-        <v>6787403</v>
+        <v>6787387</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6948,19 +6948,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129357065</v>
+        <v>129357069</v>
       </c>
       <c r="B64" t="n">
         <v>79081</v>
@@ -6995,10 +6995,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>419776</v>
+        <v>419782</v>
       </c>
       <c r="R64" t="n">
-        <v>6787371</v>
+        <v>6787403</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7057,7 +7057,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129364485</v>
+        <v>129357065</v>
       </c>
       <c r="B65" t="n">
         <v>79081</v>
@@ -7092,10 +7092,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>419678</v>
+        <v>419776</v>
       </c>
       <c r="R65" t="n">
-        <v>6787476</v>
+        <v>6787371</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7142,12 +7142,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7261,7 +7261,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129357084</v>
+        <v>129357081</v>
       </c>
       <c r="B67" t="n">
         <v>79081</v>
@@ -7296,10 +7296,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>419816</v>
+        <v>419810</v>
       </c>
       <c r="R67" t="n">
-        <v>6787364</v>
+        <v>6787369</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7358,7 +7358,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129357081</v>
+        <v>129357080</v>
       </c>
       <c r="B68" t="n">
         <v>79081</v>
@@ -7393,10 +7393,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>419810</v>
+        <v>419805</v>
       </c>
       <c r="R68" t="n">
-        <v>6787369</v>
+        <v>6787361</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7455,7 +7455,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129357046</v>
+        <v>129357084</v>
       </c>
       <c r="B69" t="n">
         <v>79081</v>
@@ -7490,10 +7490,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>419742</v>
+        <v>419816</v>
       </c>
       <c r="R69" t="n">
-        <v>6787432</v>
+        <v>6787364</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7552,7 +7552,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129357080</v>
+        <v>129357046</v>
       </c>
       <c r="B70" t="n">
         <v>79081</v>
@@ -7587,10 +7587,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>419805</v>
+        <v>419742</v>
       </c>
       <c r="R70" t="n">
-        <v>6787361</v>
+        <v>6787432</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7649,10 +7649,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129367601</v>
+        <v>129357060</v>
       </c>
       <c r="B71" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7660,37 +7660,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>419818</v>
+        <v>419924</v>
       </c>
       <c r="R71" t="n">
-        <v>6787250</v>
+        <v>6787672</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7734,19 +7734,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129357060</v>
+        <v>129357052</v>
       </c>
       <c r="B72" t="n">
         <v>79081</v>
@@ -7781,10 +7781,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>419924</v>
+        <v>419810</v>
       </c>
       <c r="R72" t="n">
-        <v>6787672</v>
+        <v>6787834</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7843,10 +7843,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129357052</v>
+        <v>129367601</v>
       </c>
       <c r="B73" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7854,37 +7854,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>419810</v>
+        <v>419818</v>
       </c>
       <c r="R73" t="n">
-        <v>6787834</v>
+        <v>6787250</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7928,22 +7928,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129364502</v>
+        <v>129367641</v>
       </c>
       <c r="B74" t="n">
-        <v>78089</v>
+        <v>79081</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7951,37 +7951,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>419821</v>
+        <v>419590</v>
       </c>
       <c r="R74" t="n">
-        <v>6787289</v>
+        <v>6787769</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8025,22 +8025,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129367617</v>
+        <v>129367639</v>
       </c>
       <c r="B75" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8048,21 +8048,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8072,10 +8072,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>419617</v>
+        <v>419672</v>
       </c>
       <c r="R75" t="n">
-        <v>6787770</v>
+        <v>6787734</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8134,10 +8134,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129367599</v>
+        <v>129367626</v>
       </c>
       <c r="B76" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8145,21 +8145,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8169,10 +8169,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>419693</v>
+        <v>419797</v>
       </c>
       <c r="R76" t="n">
-        <v>6787442</v>
+        <v>6787364</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8231,10 +8231,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129367641</v>
+        <v>129364502</v>
       </c>
       <c r="B77" t="n">
-        <v>79081</v>
+        <v>78089</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8242,37 +8242,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>419590</v>
+        <v>419821</v>
       </c>
       <c r="R77" t="n">
-        <v>6787769</v>
+        <v>6787289</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8316,22 +8316,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129367639</v>
+        <v>129367599</v>
       </c>
       <c r="B78" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8339,21 +8339,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8363,10 +8363,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>419672</v>
+        <v>419693</v>
       </c>
       <c r="R78" t="n">
-        <v>6787734</v>
+        <v>6787442</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8425,10 +8425,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129367626</v>
+        <v>129367617</v>
       </c>
       <c r="B79" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8436,21 +8436,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8460,10 +8460,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>419797</v>
+        <v>419617</v>
       </c>
       <c r="R79" t="n">
-        <v>6787364</v>
+        <v>6787770</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8813,10 +8813,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129357036</v>
+        <v>129357039</v>
       </c>
       <c r="B83" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8824,34 +8824,46 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>419822</v>
+        <v>419783</v>
       </c>
       <c r="R83" t="n">
-        <v>6787802</v>
+        <v>6787400</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8910,10 +8922,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129367598</v>
+        <v>129357050</v>
       </c>
       <c r="B84" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8921,37 +8933,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>419671</v>
+        <v>419683</v>
       </c>
       <c r="R84" t="n">
-        <v>6787459</v>
+        <v>6787695</v>
       </c>
       <c r="S84" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8995,22 +9007,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129367600</v>
+        <v>129367627</v>
       </c>
       <c r="B85" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9018,21 +9030,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9042,10 +9054,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>419801</v>
+        <v>419795</v>
       </c>
       <c r="R85" t="n">
-        <v>6787284</v>
+        <v>6787371</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9104,10 +9116,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129367645</v>
+        <v>129367598</v>
       </c>
       <c r="B86" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9115,21 +9127,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9139,10 +9151,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>419775</v>
+        <v>419671</v>
       </c>
       <c r="R86" t="n">
-        <v>6787376</v>
+        <v>6787459</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9201,7 +9213,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129357050</v>
+        <v>129357088</v>
       </c>
       <c r="B87" t="n">
         <v>79081</v>
@@ -9236,10 +9248,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>419683</v>
+        <v>419827</v>
       </c>
       <c r="R87" t="n">
-        <v>6787695</v>
+        <v>6787267</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9298,10 +9310,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129367627</v>
+        <v>129367600</v>
       </c>
       <c r="B88" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9309,21 +9321,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9333,10 +9345,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>419795</v>
+        <v>419801</v>
       </c>
       <c r="R88" t="n">
-        <v>6787371</v>
+        <v>6787284</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9395,7 +9407,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129357088</v>
+        <v>129367645</v>
       </c>
       <c r="B89" t="n">
         <v>79081</v>
@@ -9426,17 +9438,17 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>419827</v>
+        <v>419775</v>
       </c>
       <c r="R89" t="n">
-        <v>6787267</v>
+        <v>6787376</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9480,22 +9492,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129357039</v>
+        <v>129357036</v>
       </c>
       <c r="B90" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9503,46 +9515,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>419783</v>
+        <v>419822</v>
       </c>
       <c r="R90" t="n">
-        <v>6787400</v>
+        <v>6787802</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9795,10 +9795,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129364482</v>
+        <v>129367631</v>
       </c>
       <c r="B93" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9806,37 +9806,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>419803</v>
+        <v>419777</v>
       </c>
       <c r="R93" t="n">
-        <v>6787361</v>
+        <v>6787409</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9880,22 +9880,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129364480</v>
+        <v>129357073</v>
       </c>
       <c r="B94" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9903,21 +9903,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9927,10 +9927,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>419678</v>
+        <v>419806</v>
       </c>
       <c r="R94" t="n">
-        <v>6787641</v>
+        <v>6787347</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9977,19 +9977,19 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129367631</v>
+        <v>129357079</v>
       </c>
       <c r="B95" t="n">
         <v>79081</v>
@@ -10020,17 +10020,17 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>419777</v>
+        <v>419814</v>
       </c>
       <c r="R95" t="n">
-        <v>6787409</v>
+        <v>6787354</v>
       </c>
       <c r="S95" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10074,22 +10074,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129357073</v>
+        <v>129364482</v>
       </c>
       <c r="B96" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10097,21 +10097,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10121,10 +10121,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>419806</v>
+        <v>419803</v>
       </c>
       <c r="R96" t="n">
-        <v>6787347</v>
+        <v>6787361</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10171,19 +10171,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129357079</v>
+        <v>129367647</v>
       </c>
       <c r="B97" t="n">
         <v>79081</v>
@@ -10214,17 +10214,17 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>419814</v>
+        <v>419817</v>
       </c>
       <c r="R97" t="n">
-        <v>6787354</v>
+        <v>6787255</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10268,22 +10268,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129367647</v>
+        <v>129364480</v>
       </c>
       <c r="B98" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10291,37 +10291,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>419817</v>
+        <v>419678</v>
       </c>
       <c r="R98" t="n">
-        <v>6787255</v>
+        <v>6787641</v>
       </c>
       <c r="S98" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10365,12 +10365,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -10474,32 +10474,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129357076</v>
+        <v>129364498</v>
       </c>
       <c r="B100" t="n">
-        <v>79081</v>
+        <v>92875</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10509,10 +10509,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>419818</v>
+        <v>419705</v>
       </c>
       <c r="R100" t="n">
-        <v>6787293</v>
+        <v>6787663</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10559,44 +10559,44 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129364498</v>
+        <v>129357076</v>
       </c>
       <c r="B101" t="n">
-        <v>92875</v>
+        <v>79081</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10606,10 +10606,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>419705</v>
+        <v>419818</v>
       </c>
       <c r="R101" t="n">
-        <v>6787663</v>
+        <v>6787293</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10656,22 +10656,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129357044</v>
+        <v>129367659</v>
       </c>
       <c r="B102" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10679,37 +10679,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>419817</v>
+        <v>419692</v>
       </c>
       <c r="R102" t="n">
-        <v>6787353</v>
+        <v>6787475</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10753,22 +10753,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129367659</v>
+        <v>129357044</v>
       </c>
       <c r="B103" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10776,37 +10776,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>419692</v>
+        <v>419817</v>
       </c>
       <c r="R103" t="n">
-        <v>6787475</v>
+        <v>6787353</v>
       </c>
       <c r="S103" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10850,12 +10850,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -10959,7 +10959,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129364488</v>
+        <v>129357061</v>
       </c>
       <c r="B105" t="n">
         <v>79081</v>
@@ -10994,10 +10994,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>419829</v>
+        <v>419929</v>
       </c>
       <c r="R105" t="n">
-        <v>6787260</v>
+        <v>6787653</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11044,19 +11044,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129357057</v>
+        <v>129367644</v>
       </c>
       <c r="B106" t="n">
         <v>79081</v>
@@ -11087,17 +11087,17 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>419865</v>
+        <v>419667</v>
       </c>
       <c r="R106" t="n">
-        <v>6787760</v>
+        <v>6787466</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11141,19 +11141,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129357061</v>
+        <v>129364488</v>
       </c>
       <c r="B107" t="n">
         <v>79081</v>
@@ -11188,10 +11188,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>419929</v>
+        <v>419829</v>
       </c>
       <c r="R107" t="n">
-        <v>6787653</v>
+        <v>6787260</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11238,19 +11238,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129367644</v>
+        <v>129357057</v>
       </c>
       <c r="B108" t="n">
         <v>79081</v>
@@ -11281,17 +11281,17 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>419667</v>
+        <v>419865</v>
       </c>
       <c r="R108" t="n">
-        <v>6787466</v>
+        <v>6787760</v>
       </c>
       <c r="S108" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11335,12 +11335,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -11541,7 +11541,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129357085</v>
+        <v>129357070</v>
       </c>
       <c r="B111" t="n">
         <v>79081</v>
@@ -11576,10 +11576,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>419821</v>
+        <v>419795</v>
       </c>
       <c r="R111" t="n">
-        <v>6787310</v>
+        <v>6787392</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11638,7 +11638,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129367637</v>
+        <v>129357085</v>
       </c>
       <c r="B112" t="n">
         <v>79081</v>
@@ -11669,17 +11669,17 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>419724</v>
+        <v>419821</v>
       </c>
       <c r="R112" t="n">
-        <v>6787653</v>
+        <v>6787310</v>
       </c>
       <c r="S112" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11723,19 +11723,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129357072</v>
+        <v>129367637</v>
       </c>
       <c r="B113" t="n">
         <v>79081</v>
@@ -11766,17 +11766,17 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>419808</v>
+        <v>419724</v>
       </c>
       <c r="R113" t="n">
-        <v>6787365</v>
+        <v>6787653</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11820,19 +11820,19 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129357063</v>
+        <v>129357072</v>
       </c>
       <c r="B114" t="n">
         <v>79081</v>
@@ -11867,10 +11867,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>419686</v>
+        <v>419808</v>
       </c>
       <c r="R114" t="n">
-        <v>6787449</v>
+        <v>6787365</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11929,7 +11929,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129357070</v>
+        <v>129357063</v>
       </c>
       <c r="B115" t="n">
         <v>79081</v>
@@ -11964,10 +11964,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>419795</v>
+        <v>419686</v>
       </c>
       <c r="R115" t="n">
-        <v>6787392</v>
+        <v>6787449</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12133,10 +12133,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129364468</v>
+        <v>129367633</v>
       </c>
       <c r="B117" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12144,37 +12144,37 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>419802</v>
+        <v>419775</v>
       </c>
       <c r="R117" t="n">
-        <v>6787354</v>
+        <v>6787415</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12218,19 +12218,19 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129364466</v>
+        <v>129364468</v>
       </c>
       <c r="B118" t="n">
         <v>79700</v>
@@ -12265,10 +12265,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>419796</v>
+        <v>419802</v>
       </c>
       <c r="R118" t="n">
-        <v>6787321</v>
+        <v>6787354</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12327,10 +12327,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129367633</v>
+        <v>129364466</v>
       </c>
       <c r="B119" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12338,37 +12338,37 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>419775</v>
+        <v>419796</v>
       </c>
       <c r="R119" t="n">
-        <v>6787415</v>
+        <v>6787321</v>
       </c>
       <c r="S119" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12412,12 +12412,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
@@ -12521,10 +12521,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129357043</v>
+        <v>129357037</v>
       </c>
       <c r="B121" t="n">
-        <v>78838</v>
+        <v>79671</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12532,21 +12532,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12556,10 +12556,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>419806</v>
+        <v>419822</v>
       </c>
       <c r="R121" t="n">
-        <v>6787355</v>
+        <v>6787799</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12618,7 +12618,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129357049</v>
+        <v>129364487</v>
       </c>
       <c r="B122" t="n">
         <v>79081</v>
@@ -12653,10 +12653,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>419707</v>
+        <v>419795</v>
       </c>
       <c r="R122" t="n">
-        <v>6787641</v>
+        <v>6787306</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12703,19 +12703,19 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129364487</v>
+        <v>129357049</v>
       </c>
       <c r="B123" t="n">
         <v>79081</v>
@@ -12750,10 +12750,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>419795</v>
+        <v>419707</v>
       </c>
       <c r="R123" t="n">
-        <v>6787306</v>
+        <v>6787641</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12800,12 +12800,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
@@ -12909,10 +12909,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129357068</v>
+        <v>129357043</v>
       </c>
       <c r="B125" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12920,21 +12920,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12944,10 +12944,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>419749</v>
+        <v>419806</v>
       </c>
       <c r="R125" t="n">
-        <v>6787397</v>
+        <v>6787355</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13006,10 +13006,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129357037</v>
+        <v>129357068</v>
       </c>
       <c r="B126" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13017,21 +13017,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13041,10 +13041,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>419822</v>
+        <v>419749</v>
       </c>
       <c r="R126" t="n">
-        <v>6787799</v>
+        <v>6787397</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>

--- a/artfynd/A 46306-2025 artfynd.xlsx
+++ b/artfynd/A 46306-2025 artfynd.xlsx
@@ -13494,7 +13494,7 @@
         <v>129367597</v>
       </c>
       <c r="B131" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13698,7 +13698,7 @@
         <v>129367608</v>
       </c>
       <c r="B133" t="n">
-        <v>90625</v>
+        <v>90629</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>

--- a/artfynd/A 46306-2025 artfynd.xlsx
+++ b/artfynd/A 46306-2025 artfynd.xlsx
@@ -13494,7 +13494,7 @@
         <v>129367597</v>
       </c>
       <c r="B131" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13698,7 +13698,7 @@
         <v>129367608</v>
       </c>
       <c r="B133" t="n">
-        <v>90629</v>
+        <v>90631</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
